--- a/artfynd/S 3548-2025 artfynd.xlsx
+++ b/artfynd/S 3548-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ158"/>
+  <dimension ref="A1:AZ160"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10561,52 +10561,48 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>136103383</v>
+        <v>136609571</v>
       </c>
       <c r="B91" t="n">
-        <v>93429</v>
+        <v>93426</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>5449</v>
+        <v>5448</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Svart taggsvamp agg.</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Phellodon niger s.lat.</t>
-        </is>
-      </c>
-      <c r="H91" t="inlineStr"/>
-      <c r="I91" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J91" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>Phellodon melaleucus</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>(Sw. ex Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr"/>
+      <c r="J91" t="inlineStr"/>
       <c r="K91" t="inlineStr"/>
       <c r="N91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Blackstahyttan, Nrk</t>
+          <t>NV Blackstahyttan, Nrk</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>499508</v>
+        <v>499533</v>
       </c>
       <c r="R91" t="n">
-        <v>6580852</v>
+        <v>6580838</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10633,12 +10629,12 @@
       </c>
       <c r="Y91" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10651,70 +10647,72 @@
       <c r="AG91" t="b">
         <v>0</v>
       </c>
-      <c r="AH91" t="inlineStr">
-        <is>
-          <t>Blåbärsbarrskog</t>
-        </is>
-      </c>
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Michael Andersson</t>
+          <t>Erik Göthlin</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Michael Andersson, Toni Berglund</t>
+          <t>Erik Göthlin</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
       <c r="AZ91" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136103383</t>
+          <t>https://artportalen.se/Sighting/136609571</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>96368341</v>
+        <v>136103383</v>
       </c>
       <c r="B92" t="n">
-        <v>91409</v>
+        <v>93429</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>5741</v>
+        <v>5449</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Tjockfotad fingersvamp</t>
+          <t>Svart taggsvamp agg.</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Ramaria flavescens</t>
-        </is>
-      </c>
-      <c r="H92" t="inlineStr">
-        <is>
-          <t>(Schaeff.) R. H. Petersen</t>
-        </is>
-      </c>
-      <c r="I92" t="inlineStr"/>
+          <t>Phellodon niger s.lat.</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr"/>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="K92" t="inlineStr"/>
+      <c r="N92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
           <t>Blackstahyttan, Nrk</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>499465</v>
+        <v>499508</v>
       </c>
       <c r="R92" t="n">
-        <v>6580853</v>
+        <v>6580852</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10741,12 +10739,12 @@
       </c>
       <c r="Y92" t="inlineStr">
         <is>
-          <t>2021-09-27</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
         <is>
-          <t>2021-09-27</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10755,42 +10753,39 @@
       <c r="AE92" t="b">
         <v>0</v>
       </c>
+      <c r="AF92" t="inlineStr"/>
       <c r="AG92" t="b">
         <v>0</v>
       </c>
-      <c r="AI92" t="inlineStr">
-        <is>
-          <t>barrskog</t>
+      <c r="AH92" t="inlineStr">
+        <is>
+          <t>Blåbärsbarrskog</t>
         </is>
       </c>
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Hans Rydberg</t>
+          <t>Michael Andersson</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Hans Rydberg</t>
-        </is>
-      </c>
-      <c r="AY92" t="inlineStr">
-        <is>
-          <t>Länsstyrelsen i Örebro län, inventering</t>
-        </is>
-      </c>
+          <t>Michael Andersson, Toni Berglund</t>
+        </is>
+      </c>
+      <c r="AY92" t="inlineStr"/>
       <c r="AZ92" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/96368341</t>
+          <t>https://artportalen.se/Sighting/136103383</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>136103380</v>
+        <v>96368341</v>
       </c>
       <c r="B93" t="n">
-        <v>91588</v>
+        <v>91409</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10815,28 +10810,17 @@
           <t>(Schaeff.) R. H. Petersen</t>
         </is>
       </c>
-      <c r="I93" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J93" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K93" t="inlineStr"/>
-      <c r="N93" t="inlineStr"/>
+      <c r="I93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
           <t>Blackstahyttan, Nrk</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>499508</v>
+        <v>499465</v>
       </c>
       <c r="R93" t="n">
-        <v>6580852</v>
+        <v>6580853</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10863,12 +10847,12 @@
       </c>
       <c r="Y93" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2021-09-27</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2021-09-27</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10877,39 +10861,42 @@
       <c r="AE93" t="b">
         <v>0</v>
       </c>
-      <c r="AF93" t="inlineStr"/>
       <c r="AG93" t="b">
         <v>0</v>
       </c>
-      <c r="AH93" t="inlineStr">
-        <is>
-          <t>Blåbärsbarrskog</t>
+      <c r="AI93" t="inlineStr">
+        <is>
+          <t>barrskog</t>
         </is>
       </c>
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Michael Andersson</t>
+          <t>Hans Rydberg</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Michael Andersson, Toni Berglund</t>
-        </is>
-      </c>
-      <c r="AY93" t="inlineStr"/>
+          <t>Hans Rydberg</t>
+        </is>
+      </c>
+      <c r="AY93" t="inlineStr">
+        <is>
+          <t>Länsstyrelsen i Örebro län, inventering</t>
+        </is>
+      </c>
       <c r="AZ93" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136103380</t>
+          <t>https://artportalen.se/Sighting/96368341</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>111858050</v>
+        <v>136103380</v>
       </c>
       <c r="B94" t="n">
-        <v>91443</v>
+        <v>91588</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10917,25 +10904,33 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>5754</v>
+        <v>5741</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Gultoppig fingersvamp</t>
+          <t>Tjockfotad fingersvamp</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Ramaria testaceoflava</t>
+          <t>Ramaria flavescens</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Bres.) Corner</t>
-        </is>
-      </c>
-      <c r="I94" t="inlineStr"/>
-      <c r="J94" t="inlineStr"/>
+          <t>(Schaeff.) R. H. Petersen</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K94" t="inlineStr"/>
       <c r="N94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
@@ -10944,10 +10939,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>499481</v>
+        <v>499508</v>
       </c>
       <c r="R94" t="n">
-        <v>6580859</v>
+        <v>6580852</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10974,12 +10969,12 @@
       </c>
       <c r="Y94" t="inlineStr">
         <is>
-          <t>2023-09-02</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
         <is>
-          <t>2023-09-02</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10992,30 +10987,35 @@
       <c r="AG94" t="b">
         <v>0</v>
       </c>
+      <c r="AH94" t="inlineStr">
+        <is>
+          <t>Blåbärsbarrskog</t>
+        </is>
+      </c>
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Toni Berglund</t>
+          <t>Michael Andersson</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Toni Berglund</t>
+          <t>Michael Andersson, Toni Berglund</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
       <c r="AZ94" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/111858050</t>
+          <t>https://artportalen.se/Sighting/136103380</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>88151498</v>
+        <v>111858050</v>
       </c>
       <c r="B95" t="n">
-        <v>93233</v>
+        <v>91443</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11023,37 +11023,40 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>5964</v>
+        <v>5754</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Gultoppig fingersvamp</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Ramaria testaceoflava</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Bres.) Corner</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
+      <c r="J95" t="inlineStr"/>
+      <c r="K95" t="inlineStr"/>
+      <c r="N95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
           <t>Blackstahyttan, Nrk</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>499398</v>
+        <v>499481</v>
       </c>
       <c r="R95" t="n">
-        <v>6580897</v>
+        <v>6580859</v>
       </c>
       <c r="S95" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T95" t="inlineStr">
         <is>
@@ -11077,12 +11080,12 @@
       </c>
       <c r="Y95" t="inlineStr">
         <is>
-          <t>2020-09-23</t>
+          <t>2023-09-02</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
         <is>
-          <t>2020-09-23</t>
+          <t>2023-09-02</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -11095,36 +11098,27 @@
       <c r="AG95" t="b">
         <v>0</v>
       </c>
-      <c r="AI95" t="inlineStr">
-        <is>
-          <t>gammal barrskog</t>
-        </is>
-      </c>
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>Hans Rydberg</t>
+          <t>Toni Berglund</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Hans Rydberg</t>
-        </is>
-      </c>
-      <c r="AY95" t="inlineStr">
-        <is>
-          <t>Länsstyrelsen i Örebro län, inventering</t>
-        </is>
-      </c>
+          <t>Toni Berglund</t>
+        </is>
+      </c>
+      <c r="AY95" t="inlineStr"/>
       <c r="AZ95" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/88151498</t>
+          <t>https://artportalen.se/Sighting/111858050</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>96195240</v>
+        <v>88151498</v>
       </c>
       <c r="B96" t="n">
         <v>93233</v>
@@ -11153,22 +11147,19 @@
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
-      <c r="J96" t="inlineStr"/>
-      <c r="K96" t="inlineStr"/>
-      <c r="N96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
-          <t>Alvars väg, Blackstahyttan, Nrk</t>
+          <t>Blackstahyttan, Nrk</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>499328</v>
+        <v>499398</v>
       </c>
       <c r="R96" t="n">
-        <v>6580771</v>
+        <v>6580897</v>
       </c>
       <c r="S96" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T96" t="inlineStr">
         <is>
@@ -11192,12 +11183,12 @@
       </c>
       <c r="Y96" t="inlineStr">
         <is>
-          <t>2021-09-19</t>
+          <t>2020-09-23</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
         <is>
-          <t>2021-09-19</t>
+          <t>2020-09-23</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -11212,30 +11203,34 @@
       </c>
       <c r="AI96" t="inlineStr">
         <is>
-          <t>gammal kalkbarrskog</t>
+          <t>gammal barrskog</t>
         </is>
       </c>
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>Michael Andersson</t>
+          <t>Hans Rydberg</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Michael Andersson, Toni Berglund</t>
-        </is>
-      </c>
-      <c r="AY96" t="inlineStr"/>
+          <t>Hans Rydberg</t>
+        </is>
+      </c>
+      <c r="AY96" t="inlineStr">
+        <is>
+          <t>Länsstyrelsen i Örebro län, inventering</t>
+        </is>
+      </c>
       <c r="AZ96" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/96195240</t>
+          <t>https://artportalen.se/Sighting/88151498</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>96195935</v>
+        <v>96195240</v>
       </c>
       <c r="B97" t="n">
         <v>93233</v>
@@ -11263,16 +11258,8 @@
           <t>(L.) P.Karst.</t>
         </is>
       </c>
-      <c r="I97" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J97" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+      <c r="I97" t="inlineStr"/>
+      <c r="J97" t="inlineStr"/>
       <c r="K97" t="inlineStr"/>
       <c r="N97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
@@ -11281,10 +11268,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>499353</v>
+        <v>499328</v>
       </c>
       <c r="R97" t="n">
-        <v>6580961</v>
+        <v>6580771</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -11348,13 +11335,13 @@
       <c r="AY97" t="inlineStr"/>
       <c r="AZ97" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/96195935</t>
+          <t>https://artportalen.se/Sighting/96195240</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>96359793</v>
+        <v>96195935</v>
       </c>
       <c r="B98" t="n">
         <v>93233</v>
@@ -11382,8 +11369,16 @@
           <t>(L.) P.Karst.</t>
         </is>
       </c>
-      <c r="I98" t="inlineStr"/>
-      <c r="J98" t="inlineStr"/>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="K98" t="inlineStr"/>
       <c r="N98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
@@ -11392,10 +11387,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>499400</v>
+        <v>499353</v>
       </c>
       <c r="R98" t="n">
-        <v>6580907</v>
+        <v>6580961</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -11442,7 +11437,7 @@
       </c>
       <c r="AI98" t="inlineStr">
         <is>
-          <t>under gran i gammal kalkbarrskog</t>
+          <t>gammal kalkbarrskog</t>
         </is>
       </c>
       <c r="AT98" t="inlineStr"/>
@@ -11459,13 +11454,13 @@
       <c r="AY98" t="inlineStr"/>
       <c r="AZ98" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/96359793</t>
+          <t>https://artportalen.se/Sighting/96195935</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>111858029</v>
+        <v>96359793</v>
       </c>
       <c r="B99" t="n">
         <v>93233</v>
@@ -11499,14 +11494,14 @@
       <c r="N99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
-          <t>Blackstahyttan, Nrk</t>
+          <t>Alvars väg, Blackstahyttan, Nrk</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>499495</v>
+        <v>499400</v>
       </c>
       <c r="R99" t="n">
-        <v>6580849</v>
+        <v>6580907</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -11533,12 +11528,12 @@
       </c>
       <c r="Y99" t="inlineStr">
         <is>
-          <t>2023-09-02</t>
+          <t>2021-09-19</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
         <is>
-          <t>2023-09-02</t>
+          <t>2021-09-19</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -11551,27 +11546,32 @@
       <c r="AG99" t="b">
         <v>0</v>
       </c>
+      <c r="AI99" t="inlineStr">
+        <is>
+          <t>under gran i gammal kalkbarrskog</t>
+        </is>
+      </c>
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Toni Berglund</t>
+          <t>Michael Andersson</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Toni Berglund</t>
+          <t>Michael Andersson, Toni Berglund</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
       <c r="AZ99" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/111858029</t>
+          <t>https://artportalen.se/Sighting/96359793</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>111858049</v>
+        <v>111858029</v>
       </c>
       <c r="B100" t="n">
         <v>93233</v>
@@ -11609,10 +11609,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>499481</v>
+        <v>499495</v>
       </c>
       <c r="R100" t="n">
-        <v>6580859</v>
+        <v>6580849</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11671,13 +11671,13 @@
       <c r="AY100" t="inlineStr"/>
       <c r="AZ100" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/111858049</t>
+          <t>https://artportalen.se/Sighting/111858029</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>128078655</v>
+        <v>111858049</v>
       </c>
       <c r="B101" t="n">
         <v>93233</v>
@@ -11706,19 +11706,22 @@
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
+      <c r="J101" t="inlineStr"/>
+      <c r="K101" t="inlineStr"/>
+      <c r="N101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
-          <t>Alvars väg, Nrk</t>
+          <t>Blackstahyttan, Nrk</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>499400</v>
+        <v>499481</v>
       </c>
       <c r="R101" t="n">
-        <v>6580831</v>
+        <v>6580859</v>
       </c>
       <c r="S101" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T101" t="inlineStr">
         <is>
@@ -11742,22 +11745,12 @@
       </c>
       <c r="Y101" t="inlineStr">
         <is>
-          <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="Z101" t="inlineStr">
-        <is>
-          <t>15:05</t>
+          <t>2023-09-02</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
         <is>
-          <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="AB101" t="inlineStr">
-        <is>
-          <t>15:05</t>
+          <t>2023-09-02</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -11766,30 +11759,31 @@
       <c r="AE101" t="b">
         <v>0</v>
       </c>
+      <c r="AF101" t="inlineStr"/>
       <c r="AG101" t="b">
         <v>0</v>
       </c>
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>Anders Carlberg</t>
+          <t>Toni Berglund</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Toni Berglund, Anders Carlberg</t>
+          <t>Toni Berglund</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
       <c r="AZ101" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128078655</t>
+          <t>https://artportalen.se/Sighting/111858049</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>128078988</v>
+        <v>128078655</v>
       </c>
       <c r="B102" t="n">
         <v>93233</v>
@@ -11824,13 +11818,13 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>499401</v>
+        <v>499400</v>
       </c>
       <c r="R102" t="n">
-        <v>6580907</v>
+        <v>6580831</v>
       </c>
       <c r="S102" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T102" t="inlineStr">
         <is>
@@ -11859,7 +11853,7 @@
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
@@ -11869,7 +11863,7 @@
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -11889,19 +11883,19 @@
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Anders Carlberg, Toni Berglund</t>
+          <t>Toni Berglund, Anders Carlberg</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
       <c r="AZ102" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128078988</t>
+          <t>https://artportalen.se/Sighting/128078655</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>128198622</v>
+        <v>128078988</v>
       </c>
       <c r="B103" t="n">
         <v>93233</v>
@@ -11930,19 +11924,16 @@
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
-      <c r="J103" t="inlineStr"/>
-      <c r="K103" t="inlineStr"/>
-      <c r="N103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
           <t>Alvars väg, Nrk</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>499524</v>
+        <v>499401</v>
       </c>
       <c r="R103" t="n">
-        <v>6580851</v>
+        <v>6580907</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11969,12 +11960,22 @@
       </c>
       <c r="Y103" t="inlineStr">
         <is>
-          <t>2025-09-01</t>
+          <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="Z103" t="inlineStr">
+        <is>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
         <is>
-          <t>2025-09-01</t>
+          <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AB103" t="inlineStr">
+        <is>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -11983,31 +11984,30 @@
       <c r="AE103" t="b">
         <v>0</v>
       </c>
-      <c r="AF103" t="inlineStr"/>
       <c r="AG103" t="b">
         <v>0</v>
       </c>
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>Toni Berglund</t>
+          <t>Anders Carlberg</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Toni Berglund</t>
+          <t>Anders Carlberg, Toni Berglund</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
       <c r="AZ103" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128198622</t>
+          <t>https://artportalen.se/Sighting/128078988</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>128198682</v>
+        <v>128198622</v>
       </c>
       <c r="B104" t="n">
         <v>93233</v>
@@ -12045,10 +12045,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>499461</v>
+        <v>499524</v>
       </c>
       <c r="R104" t="n">
-        <v>6580859</v>
+        <v>6580851</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -12107,16 +12107,16 @@
       <c r="AY104" t="inlineStr"/>
       <c r="AZ104" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128198682</t>
+          <t>https://artportalen.se/Sighting/128198622</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>128391581</v>
+        <v>128198682</v>
       </c>
       <c r="B105" t="n">
-        <v>93307</v>
+        <v>93233</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -12141,28 +12141,20 @@
           <t>(L.) P.Karst.</t>
         </is>
       </c>
-      <c r="I105" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J105" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+      <c r="I105" t="inlineStr"/>
+      <c r="J105" t="inlineStr"/>
       <c r="K105" t="inlineStr"/>
       <c r="N105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
-          <t>Blackstahyttan Alvars väg, Nrk</t>
+          <t>Alvars väg, Nrk</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>499378</v>
+        <v>499461</v>
       </c>
       <c r="R105" t="n">
-        <v>6580902</v>
+        <v>6580859</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -12189,12 +12181,12 @@
       </c>
       <c r="Y105" t="inlineStr">
         <is>
-          <t>2025-09-12</t>
+          <t>2025-09-01</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
         <is>
-          <t>2025-09-12</t>
+          <t>2025-09-01</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -12210,27 +12202,27 @@
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>Lotta Sörman</t>
+          <t>Toni Berglund</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Lotta Sörman</t>
+          <t>Toni Berglund</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
       <c r="AZ105" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128391581</t>
+          <t>https://artportalen.se/Sighting/128198682</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>136103331</v>
+        <v>128391581</v>
       </c>
       <c r="B106" t="n">
-        <v>93436</v>
+        <v>93307</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12257,26 +12249,26 @@
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="K106" t="inlineStr"/>
       <c r="N106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
-          <t>Blackstahyttan, Nrk</t>
+          <t>Blackstahyttan Alvars väg, Nrk</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>499508</v>
+        <v>499378</v>
       </c>
       <c r="R106" t="n">
-        <v>6580852</v>
+        <v>6580902</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -12303,12 +12295,12 @@
       </c>
       <c r="Y106" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -12321,37 +12313,27 @@
       <c r="AG106" t="b">
         <v>0</v>
       </c>
-      <c r="AH106" t="inlineStr">
-        <is>
-          <t>Blåbärsbarrskog</t>
-        </is>
-      </c>
-      <c r="AI106" t="inlineStr">
-        <is>
-          <t>på stig</t>
-        </is>
-      </c>
       <c r="AT106" t="inlineStr"/>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>Michael Andersson</t>
+          <t>Lotta Sörman</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>Michael Andersson, Toni Berglund</t>
+          <t>Lotta Sörman</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
       <c r="AZ106" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136103331</t>
+          <t>https://artportalen.se/Sighting/128391581</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>136597853</v>
+        <v>136103331</v>
       </c>
       <c r="B107" t="n">
         <v>93436</v>
@@ -12379,20 +12361,28 @@
           <t>(L.) P.Karst.</t>
         </is>
       </c>
-      <c r="I107" t="inlineStr"/>
-      <c r="J107" t="inlineStr"/>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K107" t="inlineStr"/>
       <c r="N107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
-          <t>Västantorp, Västantorp, Nrk</t>
+          <t>Blackstahyttan, Nrk</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>499477</v>
+        <v>499508</v>
       </c>
       <c r="R107" t="n">
-        <v>6580844</v>
+        <v>6580852</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -12419,12 +12409,12 @@
       </c>
       <c r="Y107" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -12437,52 +12427,62 @@
       <c r="AG107" t="b">
         <v>0</v>
       </c>
+      <c r="AH107" t="inlineStr">
+        <is>
+          <t>Blåbärsbarrskog</t>
+        </is>
+      </c>
+      <c r="AI107" t="inlineStr">
+        <is>
+          <t>på stig</t>
+        </is>
+      </c>
       <c r="AT107" t="inlineStr"/>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>Erik Göthlin</t>
+          <t>Michael Andersson</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>Erik Göthlin</t>
+          <t>Michael Andersson, Toni Berglund</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
       <c r="AZ107" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136597853</t>
+          <t>https://artportalen.se/Sighting/136103331</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>111858070</v>
+        <v>136597853</v>
       </c>
       <c r="B108" t="n">
-        <v>90681</v>
+        <v>93436</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>6268</v>
+        <v>5964</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Rökmusseron</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Tricholoma fucatum</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Kumm.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -12491,14 +12491,14 @@
       <c r="N108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
-          <t>Blackstahyttan, Nrk</t>
+          <t>Västantorp, Västantorp, Nrk</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>499456</v>
+        <v>499477</v>
       </c>
       <c r="R108" t="n">
-        <v>6580855</v>
+        <v>6580844</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -12525,12 +12525,12 @@
       </c>
       <c r="Y108" t="inlineStr">
         <is>
-          <t>2023-09-02</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
         <is>
-          <t>2023-09-02</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -12546,24 +12546,24 @@
       <c r="AT108" t="inlineStr"/>
       <c r="AW108" t="inlineStr">
         <is>
-          <t>Toni Berglund</t>
+          <t>Erik Göthlin</t>
         </is>
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>Toni Berglund</t>
+          <t>Erik Göthlin</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
       <c r="AZ108" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/111858070</t>
+          <t>https://artportalen.se/Sighting/136597853</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>128198683</v>
+        <v>111858070</v>
       </c>
       <c r="B109" t="n">
         <v>90681</v>
@@ -12597,14 +12597,14 @@
       <c r="N109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
-          <t>Alvars väg, Nrk</t>
+          <t>Blackstahyttan, Nrk</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>499461</v>
+        <v>499456</v>
       </c>
       <c r="R109" t="n">
-        <v>6580859</v>
+        <v>6580855</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -12631,12 +12631,12 @@
       </c>
       <c r="Y109" t="inlineStr">
         <is>
-          <t>2025-09-01</t>
+          <t>2023-09-02</t>
         </is>
       </c>
       <c r="AA109" t="inlineStr">
         <is>
-          <t>2025-09-01</t>
+          <t>2023-09-02</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -12663,16 +12663,16 @@
       <c r="AY109" t="inlineStr"/>
       <c r="AZ109" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128198683</t>
+          <t>https://artportalen.se/Sighting/111858070</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>136106499</v>
+        <v>128198683</v>
       </c>
       <c r="B110" t="n">
-        <v>75447</v>
+        <v>90681</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12680,41 +12680,37 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>6427</v>
+        <v>6268</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Glansfläck</t>
+          <t>Rökmusseron</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Diarthonis spadicea</t>
+          <t>Tricholoma fucatum</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Leight.) Frisch &amp; al.</t>
+          <t>(Fr.:Fr.) P. Kumm.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
       <c r="J110" t="inlineStr"/>
-      <c r="K110" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K110" t="inlineStr"/>
       <c r="N110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
-          <t>Blackstahyttan, Nrk</t>
+          <t>Alvars väg, Nrk</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>499436</v>
+        <v>499461</v>
       </c>
       <c r="R110" t="n">
-        <v>6580862</v>
+        <v>6580859</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -12741,12 +12737,12 @@
       </c>
       <c r="Y110" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2025-09-01</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2025-09-01</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -12759,55 +12755,27 @@
       <c r="AG110" t="b">
         <v>0</v>
       </c>
-      <c r="AH110" t="inlineStr">
-        <is>
-          <t>Barrsumpskog</t>
-        </is>
-      </c>
-      <c r="AJ110" t="inlineStr">
-        <is>
-          <t>klibbal</t>
-        </is>
-      </c>
-      <c r="AK110" t="inlineStr">
-        <is>
-          <t>Alnus glutinosa</t>
-        </is>
-      </c>
-      <c r="AM110" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AN110" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO110" t="inlineStr">
-        <is>
-          <t>1 substratenheter # Bark on living woody plant # Alnus glutinosa</t>
-        </is>
-      </c>
       <c r="AT110" t="inlineStr"/>
       <c r="AW110" t="inlineStr">
         <is>
-          <t>Michael Andersson</t>
+          <t>Toni Berglund</t>
         </is>
       </c>
       <c r="AX110" t="inlineStr">
         <is>
-          <t>Michael Andersson, Toni Berglund</t>
+          <t>Toni Berglund</t>
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
       <c r="AZ110" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136106499</t>
+          <t>https://artportalen.se/Sighting/128198683</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>136107535</v>
+        <v>136106499</v>
       </c>
       <c r="B111" t="n">
         <v>75447</v>
@@ -12849,10 +12817,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>499462</v>
+        <v>499436</v>
       </c>
       <c r="R111" t="n">
-        <v>6580861</v>
+        <v>6580862</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -12902,11 +12870,6 @@
           <t>Barrsumpskog</t>
         </is>
       </c>
-      <c r="AI111" t="inlineStr">
-        <is>
-          <t>bäckstrand</t>
-        </is>
-      </c>
       <c r="AJ111" t="inlineStr">
         <is>
           <t>klibbal</t>
@@ -12944,13 +12907,13 @@
       <c r="AY111" t="inlineStr"/>
       <c r="AZ111" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136107535</t>
+          <t>https://artportalen.se/Sighting/136106499</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>136107679</v>
+        <v>136107535</v>
       </c>
       <c r="B112" t="n">
         <v>75447</v>
@@ -12980,7 +12943,11 @@
       </c>
       <c r="I112" t="inlineStr"/>
       <c r="J112" t="inlineStr"/>
-      <c r="K112" t="inlineStr"/>
+      <c r="K112" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N112" t="inlineStr"/>
       <c r="P112" t="inlineStr">
         <is>
@@ -12988,10 +12955,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>499449</v>
+        <v>499462</v>
       </c>
       <c r="R112" t="n">
-        <v>6580856</v>
+        <v>6580861</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -13032,12 +12999,18 @@
       <c r="AE112" t="b">
         <v>0</v>
       </c>
+      <c r="AF112" t="inlineStr"/>
       <c r="AG112" t="b">
         <v>0</v>
       </c>
       <c r="AH112" t="inlineStr">
         <is>
           <t>Barrsumpskog</t>
+        </is>
+      </c>
+      <c r="AI112" t="inlineStr">
+        <is>
+          <t>bäckstrand</t>
         </is>
       </c>
       <c r="AJ112" t="inlineStr">
@@ -13071,22 +13044,22 @@
       </c>
       <c r="AX112" t="inlineStr">
         <is>
-          <t>Michael Andersson</t>
+          <t>Michael Andersson, Toni Berglund</t>
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
       <c r="AZ112" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136107679</t>
+          <t>https://artportalen.se/Sighting/136107535</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>12692</v>
+        <v>136107679</v>
       </c>
       <c r="B113" t="n">
-        <v>56614</v>
+        <v>75447</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -13094,48 +13067,37 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>100084</v>
+        <v>6427</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Hasselmus</t>
+          <t>Glansfläck</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Muscardinus avellanarius</t>
+          <t>Diarthonis spadicea</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I113" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K113" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L113" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+          <t>(Leight.) Frisch &amp; al.</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr"/>
+      <c r="J113" t="inlineStr"/>
+      <c r="K113" t="inlineStr"/>
+      <c r="N113" t="inlineStr"/>
       <c r="P113" t="inlineStr">
         <is>
-          <t>Skansberget, Kilsbergen, Nrk</t>
+          <t>Blackstahyttan, Nrk</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>499263</v>
+        <v>499449</v>
       </c>
       <c r="R113" t="n">
-        <v>6580923</v>
+        <v>6580856</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -13162,17 +13124,12 @@
       </c>
       <c r="Y113" t="inlineStr">
         <is>
-          <t>2007-10-07</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="AA113" t="inlineStr">
         <is>
-          <t>2007-10-07</t>
-        </is>
-      </c>
-      <c r="AC113" t="inlineStr">
-        <is>
-          <t>Lövrik sydostsluttning av Skansberget på blockrik mark, som här och var skapar naturliga gläntor. Vid fyndplatsen dominerar björk och rönn. Ett hanbo i liten enbuske, som står i skydd av högvuxen Calamagrostis.</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -13183,31 +13140,59 @@
       </c>
       <c r="AG113" t="b">
         <v>0</v>
+      </c>
+      <c r="AH113" t="inlineStr">
+        <is>
+          <t>Barrsumpskog</t>
+        </is>
+      </c>
+      <c r="AJ113" t="inlineStr">
+        <is>
+          <t>klibbal</t>
+        </is>
+      </c>
+      <c r="AK113" t="inlineStr">
+        <is>
+          <t>Alnus glutinosa</t>
+        </is>
+      </c>
+      <c r="AM113" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AN113" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO113" t="inlineStr">
+        <is>
+          <t>1 substratenheter # Bark on living woody plant # Alnus glutinosa</t>
+        </is>
       </c>
       <c r="AT113" t="inlineStr"/>
       <c r="AW113" t="inlineStr">
         <is>
-          <t>Boris Berglund</t>
+          <t>Michael Andersson</t>
         </is>
       </c>
       <c r="AX113" t="inlineStr">
         <is>
-          <t>Boris Berglund</t>
+          <t>Michael Andersson</t>
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
       <c r="AZ113" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/12692</t>
+          <t>https://artportalen.se/Sighting/136107679</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>96601406</v>
+        <v>12692</v>
       </c>
       <c r="B114" t="n">
-        <v>57141</v>
+        <v>56614</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -13215,21 +13200,21 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>100138</v>
+        <v>100084</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Hasselmus</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Muscardinus avellanarius</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
@@ -13237,27 +13222,29 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K114" t="inlineStr"/>
+      <c r="K114" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="L114" t="inlineStr">
         <is>
           <t>hane</t>
         </is>
       </c>
-      <c r="M114" t="inlineStr"/>
-      <c r="N114" t="inlineStr"/>
       <c r="P114" t="inlineStr">
         <is>
-          <t>Blackstahyttan, Nrk</t>
+          <t>Skansberget, Kilsbergen, Nrk</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>499424</v>
+        <v>499263</v>
       </c>
       <c r="R114" t="n">
-        <v>6580779</v>
+        <v>6580923</v>
       </c>
       <c r="S114" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T114" t="inlineStr">
         <is>
@@ -13281,12 +13268,17 @@
       </c>
       <c r="Y114" t="inlineStr">
         <is>
-          <t>2021-10-09</t>
+          <t>2007-10-07</t>
         </is>
       </c>
       <c r="AA114" t="inlineStr">
         <is>
-          <t>2021-10-09</t>
+          <t>2007-10-07</t>
+        </is>
+      </c>
+      <c r="AC114" t="inlineStr">
+        <is>
+          <t>Lövrik sydostsluttning av Skansberget på blockrik mark, som här och var skapar naturliga gläntor. Vid fyndplatsen dominerar björk och rönn. Ett hanbo i liten enbuske, som står i skydd av högvuxen Calamagrostis.</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -13301,27 +13293,27 @@
       <c r="AT114" t="inlineStr"/>
       <c r="AW114" t="inlineStr">
         <is>
-          <t>Toni Berglund</t>
+          <t>Boris Berglund</t>
         </is>
       </c>
       <c r="AX114" t="inlineStr">
         <is>
-          <t>Toni Berglund</t>
+          <t>Boris Berglund</t>
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
       <c r="AZ114" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/96601406</t>
+          <t>https://artportalen.se/Sighting/12692</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>136107711</v>
+        <v>96601406</v>
       </c>
       <c r="B115" t="n">
-        <v>5182</v>
+        <v>57141</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -13329,54 +13321,49 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>100526</v>
+        <v>100138</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I115" t="inlineStr"/>
-      <c r="J115" t="inlineStr"/>
-      <c r="K115" t="inlineStr">
-        <is>
-          <t>larv/nymf</t>
-        </is>
-      </c>
-      <c r="L115" t="inlineStr"/>
-      <c r="M115" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N115" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K115" t="inlineStr"/>
+      <c r="L115" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M115" t="inlineStr"/>
+      <c r="N115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
         <is>
           <t>Blackstahyttan, Nrk</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>499449</v>
+        <v>499424</v>
       </c>
       <c r="R115" t="n">
-        <v>6580856</v>
+        <v>6580779</v>
       </c>
       <c r="S115" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T115" t="inlineStr">
         <is>
@@ -13400,12 +13387,12 @@
       </c>
       <c r="Y115" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2021-10-09</t>
         </is>
       </c>
       <c r="AA115" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2021-10-09</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -13414,59 +13401,33 @@
       <c r="AE115" t="b">
         <v>0</v>
       </c>
-      <c r="AF115" t="inlineStr"/>
       <c r="AG115" t="b">
         <v>0</v>
-      </c>
-      <c r="AH115" t="inlineStr">
-        <is>
-          <t>Barrsumpskog</t>
-        </is>
-      </c>
-      <c r="AJ115" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK115" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM115" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, utan markontakt</t>
-        </is>
-      </c>
-      <c r="AO115" t="inlineStr">
-        <is>
-          <t>Horizontal, dead without ground contact # grov granlåga med kvarsittande bark # Picea abies</t>
-        </is>
       </c>
       <c r="AT115" t="inlineStr"/>
       <c r="AW115" t="inlineStr">
         <is>
-          <t>Michael Andersson</t>
+          <t>Toni Berglund</t>
         </is>
       </c>
       <c r="AX115" t="inlineStr">
         <is>
-          <t>Michael Andersson</t>
+          <t>Toni Berglund</t>
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
       <c r="AZ115" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136107711</t>
+          <t>https://artportalen.se/Sighting/96601406</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>128090297</v>
+        <v>136107711</v>
       </c>
       <c r="B116" t="n">
-        <v>58327</v>
+        <v>5182</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -13474,49 +13435,54 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>103015</v>
+        <v>100526</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I116" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K116" t="inlineStr"/>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr"/>
+      <c r="J116" t="inlineStr"/>
+      <c r="K116" t="inlineStr">
+        <is>
+          <t>larv/nymf</t>
+        </is>
+      </c>
       <c r="L116" t="inlineStr"/>
       <c r="M116" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N116" t="inlineStr"/>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N116" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P116" t="inlineStr">
         <is>
-          <t>Alvars väg, Nrk</t>
+          <t>Blackstahyttan, Nrk</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>499400</v>
+        <v>499449</v>
       </c>
       <c r="R116" t="n">
-        <v>6580831</v>
+        <v>6580856</v>
       </c>
       <c r="S116" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T116" t="inlineStr">
         <is>
@@ -13540,22 +13506,12 @@
       </c>
       <c r="Y116" t="inlineStr">
         <is>
-          <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="Z116" t="inlineStr">
-        <is>
-          <t>16:30</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="AA116" t="inlineStr">
         <is>
-          <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="AB116" t="inlineStr">
-        <is>
-          <t>16:30</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -13564,33 +13520,59 @@
       <c r="AE116" t="b">
         <v>0</v>
       </c>
+      <c r="AF116" t="inlineStr"/>
       <c r="AG116" t="b">
         <v>0</v>
+      </c>
+      <c r="AH116" t="inlineStr">
+        <is>
+          <t>Barrsumpskog</t>
+        </is>
+      </c>
+      <c r="AJ116" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK116" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM116" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, utan markontakt</t>
+        </is>
+      </c>
+      <c r="AO116" t="inlineStr">
+        <is>
+          <t>Horizontal, dead without ground contact # grov granlåga med kvarsittande bark # Picea abies</t>
+        </is>
       </c>
       <c r="AT116" t="inlineStr"/>
       <c r="AW116" t="inlineStr">
         <is>
-          <t>Anders Carlberg</t>
+          <t>Michael Andersson</t>
         </is>
       </c>
       <c r="AX116" t="inlineStr">
         <is>
-          <t>Anders Carlberg, Toni Berglund</t>
+          <t>Michael Andersson</t>
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
       <c r="AZ116" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128090297</t>
+          <t>https://artportalen.se/Sighting/136107711</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>136106670</v>
+        <v>128090297</v>
       </c>
       <c r="B117" t="n">
-        <v>98363</v>
+        <v>58327</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -13598,41 +13580,49 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>219815</v>
+        <v>103015</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Ekbräken</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Gymnocarpium dryopteris</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(L.) Newman</t>
-        </is>
-      </c>
-      <c r="I117" t="inlineStr"/>
-      <c r="J117" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K117" t="inlineStr"/>
       <c r="L117" t="inlineStr"/>
+      <c r="M117" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
-          <t>Blackstahyttan, Nrk</t>
+          <t>Alvars väg, Nrk</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>499401</v>
+        <v>499400</v>
       </c>
       <c r="R117" t="n">
-        <v>6580883</v>
+        <v>6580831</v>
       </c>
       <c r="S117" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T117" t="inlineStr">
         <is>
@@ -13656,12 +13646,22 @@
       </c>
       <c r="Y117" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="Z117" t="inlineStr">
+        <is>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AA117" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AB117" t="inlineStr">
+        <is>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -13670,39 +13670,33 @@
       <c r="AE117" t="b">
         <v>0</v>
       </c>
-      <c r="AF117" t="inlineStr"/>
       <c r="AG117" t="b">
         <v>0</v>
-      </c>
-      <c r="AH117" t="inlineStr">
-        <is>
-          <t>Barrsumpskog</t>
-        </is>
       </c>
       <c r="AT117" t="inlineStr"/>
       <c r="AW117" t="inlineStr">
         <is>
-          <t>Michael Andersson</t>
+          <t>Anders Carlberg</t>
         </is>
       </c>
       <c r="AX117" t="inlineStr">
         <is>
-          <t>Michael Andersson, Toni Berglund</t>
+          <t>Anders Carlberg, Toni Berglund</t>
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
       <c r="AZ117" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136106670</t>
+          <t>https://artportalen.se/Sighting/128090297</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>136106545</v>
+        <v>136106670</v>
       </c>
       <c r="B118" t="n">
-        <v>108437</v>
+        <v>98363</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -13710,30 +13704,26 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>220102</v>
+        <v>219815</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Kärrfibbla</t>
+          <t>Ekbräken</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Crepis paludosa</t>
+          <t>Gymnocarpium dryopteris</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(L.) Moench</t>
+          <t>(L.) Newman</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
       <c r="J118" t="inlineStr"/>
-      <c r="K118" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+      <c r="K118" t="inlineStr"/>
       <c r="L118" t="inlineStr"/>
       <c r="N118" t="inlineStr"/>
       <c r="P118" t="inlineStr">
@@ -13742,10 +13732,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>499412</v>
+        <v>499401</v>
       </c>
       <c r="R118" t="n">
-        <v>6580878</v>
+        <v>6580883</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -13809,13 +13799,13 @@
       <c r="AY118" t="inlineStr"/>
       <c r="AZ118" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136106545</t>
+          <t>https://artportalen.se/Sighting/136106670</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>136106660</v>
+        <v>136106545</v>
       </c>
       <c r="B119" t="n">
         <v>108437</v>
@@ -13847,7 +13837,7 @@
       <c r="J119" t="inlineStr"/>
       <c r="K119" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="L119" t="inlineStr"/>
@@ -13858,10 +13848,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>499401</v>
+        <v>499412</v>
       </c>
       <c r="R119" t="n">
-        <v>6580883</v>
+        <v>6580878</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -13925,54 +13915,62 @@
       <c r="AY119" t="inlineStr"/>
       <c r="AZ119" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136106660</t>
+          <t>https://artportalen.se/Sighting/136106545</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>87880231</v>
+        <v>136106660</v>
       </c>
       <c r="B120" t="n">
-        <v>109815</v>
+        <v>108437</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>220204</v>
+        <v>220102</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Slåtterfibbla</t>
+          <t>Kärrfibbla</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Hypochaeris maculata</t>
+          <t>Crepis paludosa</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Moench</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
+      <c r="J120" t="inlineStr"/>
+      <c r="K120" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L120" t="inlineStr"/>
+      <c r="N120" t="inlineStr"/>
       <c r="P120" t="inlineStr">
         <is>
-          <t>Blackstahyttan, skog V om, Nrk</t>
+          <t>Blackstahyttan, Nrk</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>499536</v>
+        <v>499401</v>
       </c>
       <c r="R120" t="n">
-        <v>6580741</v>
+        <v>6580883</v>
       </c>
       <c r="S120" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T120" t="inlineStr">
         <is>
@@ -13996,12 +13994,12 @@
       </c>
       <c r="Y120" t="inlineStr">
         <is>
-          <t>2020-09-07</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="AA120" t="inlineStr">
         <is>
-          <t>2020-09-07</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -14010,59 +14008,56 @@
       <c r="AE120" t="b">
         <v>0</v>
       </c>
+      <c r="AF120" t="inlineStr"/>
       <c r="AG120" t="b">
         <v>0</v>
       </c>
-      <c r="AI120" t="inlineStr">
-        <is>
-          <t>kalkrik barrskog</t>
+      <c r="AH120" t="inlineStr">
+        <is>
+          <t>Barrsumpskog</t>
         </is>
       </c>
       <c r="AT120" t="inlineStr"/>
       <c r="AW120" t="inlineStr">
         <is>
-          <t>Hans Rydberg</t>
+          <t>Michael Andersson</t>
         </is>
       </c>
       <c r="AX120" t="inlineStr">
         <is>
-          <t>Hans Rydberg</t>
-        </is>
-      </c>
-      <c r="AY120" t="inlineStr">
-        <is>
-          <t>Länsstyrelsen i Örebro län, inventering</t>
-        </is>
-      </c>
+          <t>Michael Andersson, Toni Berglund</t>
+        </is>
+      </c>
+      <c r="AY120" t="inlineStr"/>
       <c r="AZ120" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/87880231</t>
+          <t>https://artportalen.se/Sighting/136106660</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>136103300</v>
+        <v>87880231</v>
       </c>
       <c r="B121" t="n">
-        <v>107053</v>
+        <v>109815</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>220785</v>
+        <v>220204</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Slåtterfibbla</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Hypochaeris maculata</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
@@ -14071,23 +14066,19 @@
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
-      <c r="J121" t="inlineStr"/>
-      <c r="K121" t="inlineStr"/>
-      <c r="L121" t="inlineStr"/>
-      <c r="N121" t="inlineStr"/>
       <c r="P121" t="inlineStr">
         <is>
-          <t>Gretefallet, Blackstahyttan, Nrk</t>
+          <t>Blackstahyttan, skog V om, Nrk</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>499594</v>
+        <v>499536</v>
       </c>
       <c r="R121" t="n">
-        <v>6580771</v>
+        <v>6580741</v>
       </c>
       <c r="S121" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T121" t="inlineStr">
         <is>
@@ -14111,12 +14102,12 @@
       </c>
       <c r="Y121" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2020-09-07</t>
         </is>
       </c>
       <c r="AA121" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2020-09-07</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -14125,61 +14116,64 @@
       <c r="AE121" t="b">
         <v>0</v>
       </c>
-      <c r="AF121" t="inlineStr"/>
       <c r="AG121" t="b">
         <v>0</v>
       </c>
-      <c r="AH121" t="inlineStr">
-        <is>
-          <t>Blandskog</t>
+      <c r="AI121" t="inlineStr">
+        <is>
+          <t>kalkrik barrskog</t>
         </is>
       </c>
       <c r="AT121" t="inlineStr"/>
       <c r="AW121" t="inlineStr">
         <is>
-          <t>Michael Andersson</t>
+          <t>Hans Rydberg</t>
         </is>
       </c>
       <c r="AX121" t="inlineStr">
         <is>
-          <t>Michael Andersson, Toni Berglund</t>
-        </is>
-      </c>
-      <c r="AY121" t="inlineStr"/>
+          <t>Hans Rydberg</t>
+        </is>
+      </c>
+      <c r="AY121" t="inlineStr">
+        <is>
+          <t>Länsstyrelsen i Örebro län, inventering</t>
+        </is>
+      </c>
       <c r="AZ121" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136103300</t>
+          <t>https://artportalen.se/Sighting/87880231</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>136106552</v>
+        <v>136103300</v>
       </c>
       <c r="B122" t="n">
-        <v>106358</v>
+        <v>107053</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>221154</v>
+        <v>220785</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Skogsstjärna</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Lysimachia europaea</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(L.) U. Manns &amp; Anderb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -14189,14 +14183,14 @@
       <c r="N122" t="inlineStr"/>
       <c r="P122" t="inlineStr">
         <is>
-          <t>Blackstahyttan, Nrk</t>
+          <t>Gretefallet, Blackstahyttan, Nrk</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>499412</v>
+        <v>499594</v>
       </c>
       <c r="R122" t="n">
-        <v>6580878</v>
+        <v>6580771</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -14243,7 +14237,7 @@
       </c>
       <c r="AH122" t="inlineStr">
         <is>
-          <t>Barrsumpskog</t>
+          <t>Blandskog</t>
         </is>
       </c>
       <c r="AT122" t="inlineStr"/>
@@ -14260,13 +14254,13 @@
       <c r="AY122" t="inlineStr"/>
       <c r="AZ122" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136106552</t>
+          <t>https://artportalen.se/Sighting/136103300</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>136106673</v>
+        <v>136106552</v>
       </c>
       <c r="B123" t="n">
         <v>106358</v>
@@ -14305,10 +14299,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>499401</v>
+        <v>499412</v>
       </c>
       <c r="R123" t="n">
-        <v>6580883</v>
+        <v>6580878</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -14372,13 +14366,13 @@
       <c r="AY123" t="inlineStr"/>
       <c r="AZ123" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136106673</t>
+          <t>https://artportalen.se/Sighting/136106552</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>136107698</v>
+        <v>136106673</v>
       </c>
       <c r="B124" t="n">
         <v>106358</v>
@@ -14417,10 +14411,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>499449</v>
+        <v>499401</v>
       </c>
       <c r="R124" t="n">
-        <v>6580856</v>
+        <v>6580883</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -14484,13 +14478,13 @@
       <c r="AY124" t="inlineStr"/>
       <c r="AZ124" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136107698</t>
+          <t>https://artportalen.se/Sighting/136106673</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>131900407</v>
+        <v>136107698</v>
       </c>
       <c r="B125" t="n">
         <v>106358</v>
@@ -14501,30 +14495,26 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>221157</v>
+        <v>221154</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Blåbär</t>
+          <t>Skogsstjärna</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Vaccinium myrtillus</t>
+          <t>Lysimachia europaea</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) U. Manns &amp; Anderb.</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
       <c r="J125" t="inlineStr"/>
-      <c r="K125" t="inlineStr">
-        <is>
-          <t>vilstadium</t>
-        </is>
-      </c>
+      <c r="K125" t="inlineStr"/>
       <c r="L125" t="inlineStr"/>
       <c r="N125" t="inlineStr"/>
       <c r="P125" t="inlineStr">
@@ -14533,10 +14523,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>499349</v>
+        <v>499449</v>
       </c>
       <c r="R125" t="n">
-        <v>6580769</v>
+        <v>6580856</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -14563,12 +14553,12 @@
       </c>
       <c r="Y125" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="AA125" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -14583,7 +14573,7 @@
       </c>
       <c r="AH125" t="inlineStr">
         <is>
-          <t>Blåbärsbarrskog</t>
+          <t>Barrsumpskog</t>
         </is>
       </c>
       <c r="AT125" t="inlineStr"/>
@@ -14594,22 +14584,22 @@
       </c>
       <c r="AX125" t="inlineStr">
         <is>
-          <t>Michael Andersson</t>
+          <t>Michael Andersson, Toni Berglund</t>
         </is>
       </c>
       <c r="AY125" t="inlineStr"/>
       <c r="AZ125" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131900407</t>
+          <t>https://artportalen.se/Sighting/136107698</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>136103391</v>
+        <v>131900407</v>
       </c>
       <c r="B126" t="n">
-        <v>106517</v>
+        <v>106358</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -14638,7 +14628,7 @@
       <c r="J126" t="inlineStr"/>
       <c r="K126" t="inlineStr">
         <is>
-          <t>i frukt</t>
+          <t>vilstadium</t>
         </is>
       </c>
       <c r="L126" t="inlineStr"/>
@@ -14649,10 +14639,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>499508</v>
+        <v>499349</v>
       </c>
       <c r="R126" t="n">
-        <v>6580852</v>
+        <v>6580769</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -14679,12 +14669,12 @@
       </c>
       <c r="Y126" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="AA126" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="AD126" t="b">
@@ -14710,19 +14700,19 @@
       </c>
       <c r="AX126" t="inlineStr">
         <is>
-          <t>Michael Andersson, Toni Berglund</t>
+          <t>Michael Andersson</t>
         </is>
       </c>
       <c r="AY126" t="inlineStr"/>
       <c r="AZ126" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136103391</t>
+          <t>https://artportalen.se/Sighting/131900407</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>136107643</v>
+        <v>136103391</v>
       </c>
       <c r="B127" t="n">
         <v>106517</v>
@@ -14752,7 +14742,11 @@
       </c>
       <c r="I127" t="inlineStr"/>
       <c r="J127" t="inlineStr"/>
-      <c r="K127" t="inlineStr"/>
+      <c r="K127" t="inlineStr">
+        <is>
+          <t>i frukt</t>
+        </is>
+      </c>
       <c r="L127" t="inlineStr"/>
       <c r="N127" t="inlineStr"/>
       <c r="P127" t="inlineStr">
@@ -14761,10 +14755,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>499449</v>
+        <v>499508</v>
       </c>
       <c r="R127" t="n">
-        <v>6580856</v>
+        <v>6580852</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -14811,7 +14805,7 @@
       </c>
       <c r="AH127" t="inlineStr">
         <is>
-          <t>Barrsumpskog</t>
+          <t>Blåbärsbarrskog</t>
         </is>
       </c>
       <c r="AT127" t="inlineStr"/>
@@ -14828,33 +14822,33 @@
       <c r="AY127" t="inlineStr"/>
       <c r="AZ127" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136107643</t>
+          <t>https://artportalen.se/Sighting/136103391</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>136103972</v>
+        <v>136107643</v>
       </c>
       <c r="B128" t="n">
-        <v>100104</v>
+        <v>106517</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>222361</v>
+        <v>221157</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Loppstarr</t>
+          <t>Blåbär</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Carex pulicaris</t>
+          <t>Vaccinium myrtillus</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
@@ -14864,11 +14858,7 @@
       </c>
       <c r="I128" t="inlineStr"/>
       <c r="J128" t="inlineStr"/>
-      <c r="K128" t="inlineStr">
-        <is>
-          <t>i frukt</t>
-        </is>
-      </c>
+      <c r="K128" t="inlineStr"/>
       <c r="L128" t="inlineStr"/>
       <c r="N128" t="inlineStr"/>
       <c r="P128" t="inlineStr">
@@ -14877,10 +14867,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>499433</v>
+        <v>499449</v>
       </c>
       <c r="R128" t="n">
-        <v>6580754</v>
+        <v>6580856</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -14927,12 +14917,7 @@
       </c>
       <c r="AH128" t="inlineStr">
         <is>
-          <t>Blåbärsbarrskog</t>
-        </is>
-      </c>
-      <c r="AI128" t="inlineStr">
-        <is>
-          <t>på traktorspår i fuktig terrängsvacka</t>
+          <t>Barrsumpskog</t>
         </is>
       </c>
       <c r="AT128" t="inlineStr"/>
@@ -14949,13 +14934,13 @@
       <c r="AY128" t="inlineStr"/>
       <c r="AZ128" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136103972</t>
+          <t>https://artportalen.se/Sighting/136107643</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>136106473</v>
+        <v>136103972</v>
       </c>
       <c r="B129" t="n">
         <v>100104</v>
@@ -14983,37 +14968,25 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I129" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J129" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+      <c r="I129" t="inlineStr"/>
+      <c r="J129" t="inlineStr"/>
       <c r="K129" t="inlineStr">
         <is>
           <t>i frukt</t>
         </is>
       </c>
       <c r="L129" t="inlineStr"/>
-      <c r="N129" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N129" t="inlineStr"/>
       <c r="P129" t="inlineStr">
         <is>
           <t>Blackstahyttan, Nrk</t>
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>499436</v>
+        <v>499433</v>
       </c>
       <c r="R129" t="n">
-        <v>6580862</v>
+        <v>6580754</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -15060,7 +15033,12 @@
       </c>
       <c r="AH129" t="inlineStr">
         <is>
-          <t>Barrsumpskog</t>
+          <t>Blåbärsbarrskog</t>
+        </is>
+      </c>
+      <c r="AI129" t="inlineStr">
+        <is>
+          <t>på traktorspår i fuktig terrängsvacka</t>
         </is>
       </c>
       <c r="AT129" t="inlineStr"/>
@@ -15077,13 +15055,13 @@
       <c r="AY129" t="inlineStr"/>
       <c r="AZ129" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136106473</t>
+          <t>https://artportalen.se/Sighting/136103972</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>136107586</v>
+        <v>136106473</v>
       </c>
       <c r="B130" t="n">
         <v>100104</v>
@@ -15113,7 +15091,7 @@
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J130" t="inlineStr">
@@ -15127,17 +15105,21 @@
         </is>
       </c>
       <c r="L130" t="inlineStr"/>
-      <c r="N130" t="inlineStr"/>
+      <c r="N130" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P130" t="inlineStr">
         <is>
           <t>Blackstahyttan, Nrk</t>
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>499449</v>
+        <v>499436</v>
       </c>
       <c r="R130" t="n">
-        <v>6580856</v>
+        <v>6580862</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -15201,54 +15183,70 @@
       <c r="AY130" t="inlineStr"/>
       <c r="AZ130" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136107586</t>
+          <t>https://artportalen.se/Sighting/136106473</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>88151816</v>
+        <v>136107586</v>
       </c>
       <c r="B131" t="n">
-        <v>101326</v>
+        <v>100104</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>222498</v>
+        <v>222361</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Loppstarr</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Carex pulicaris</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I131" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J131" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K131" t="inlineStr">
+        <is>
+          <t>i frukt</t>
+        </is>
+      </c>
+      <c r="L131" t="inlineStr"/>
+      <c r="N131" t="inlineStr"/>
       <c r="P131" t="inlineStr">
         <is>
           <t>Blackstahyttan, Nrk</t>
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>499398</v>
+        <v>499449</v>
       </c>
       <c r="R131" t="n">
-        <v>6580897</v>
+        <v>6580856</v>
       </c>
       <c r="S131" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T131" t="inlineStr">
         <is>
@@ -15272,12 +15270,12 @@
       </c>
       <c r="Y131" t="inlineStr">
         <is>
-          <t>2020-09-23</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="AA131" t="inlineStr">
         <is>
-          <t>2020-09-23</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="AD131" t="b">
@@ -15286,39 +15284,36 @@
       <c r="AE131" t="b">
         <v>0</v>
       </c>
+      <c r="AF131" t="inlineStr"/>
       <c r="AG131" t="b">
         <v>0</v>
       </c>
-      <c r="AI131" t="inlineStr">
-        <is>
-          <t>gammal barrskog</t>
+      <c r="AH131" t="inlineStr">
+        <is>
+          <t>Barrsumpskog</t>
         </is>
       </c>
       <c r="AT131" t="inlineStr"/>
       <c r="AW131" t="inlineStr">
         <is>
-          <t>Hans Rydberg</t>
+          <t>Michael Andersson</t>
         </is>
       </c>
       <c r="AX131" t="inlineStr">
         <is>
-          <t>Hans Rydberg</t>
-        </is>
-      </c>
-      <c r="AY131" t="inlineStr">
-        <is>
-          <t>Länsstyrelsen i Örebro län, inventering</t>
-        </is>
-      </c>
+          <t>Michael Andersson, Toni Berglund</t>
+        </is>
+      </c>
+      <c r="AY131" t="inlineStr"/>
       <c r="AZ131" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/88151816</t>
+          <t>https://artportalen.se/Sighting/136107586</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>96195962</v>
+        <v>88151816</v>
       </c>
       <c r="B132" t="n">
         <v>101326</v>
@@ -15347,23 +15342,19 @@
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
-      <c r="J132" t="inlineStr"/>
-      <c r="K132" t="inlineStr"/>
-      <c r="L132" t="inlineStr"/>
-      <c r="N132" t="inlineStr"/>
       <c r="P132" t="inlineStr">
         <is>
-          <t>Alvars väg, Blackstahyttan, Nrk</t>
+          <t>Blackstahyttan, Nrk</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>499353</v>
+        <v>499398</v>
       </c>
       <c r="R132" t="n">
-        <v>6580961</v>
+        <v>6580897</v>
       </c>
       <c r="S132" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T132" t="inlineStr">
         <is>
@@ -15387,12 +15378,12 @@
       </c>
       <c r="Y132" t="inlineStr">
         <is>
-          <t>2021-09-19</t>
+          <t>2020-09-23</t>
         </is>
       </c>
       <c r="AA132" t="inlineStr">
         <is>
-          <t>2021-09-19</t>
+          <t>2020-09-23</t>
         </is>
       </c>
       <c r="AD132" t="b">
@@ -15401,36 +15392,39 @@
       <c r="AE132" t="b">
         <v>0</v>
       </c>
-      <c r="AF132" t="inlineStr"/>
       <c r="AG132" t="b">
         <v>0</v>
       </c>
       <c r="AI132" t="inlineStr">
         <is>
-          <t>gammal kalkbarrskog</t>
+          <t>gammal barrskog</t>
         </is>
       </c>
       <c r="AT132" t="inlineStr"/>
       <c r="AW132" t="inlineStr">
         <is>
-          <t>Michael Andersson</t>
+          <t>Hans Rydberg</t>
         </is>
       </c>
       <c r="AX132" t="inlineStr">
         <is>
-          <t>Michael Andersson, Toni Berglund</t>
-        </is>
-      </c>
-      <c r="AY132" t="inlineStr"/>
+          <t>Hans Rydberg</t>
+        </is>
+      </c>
+      <c r="AY132" t="inlineStr">
+        <is>
+          <t>Länsstyrelsen i Örebro län, inventering</t>
+        </is>
+      </c>
       <c r="AZ132" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/96195962</t>
+          <t>https://artportalen.se/Sighting/88151816</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>111858066</v>
+        <v>96195962</v>
       </c>
       <c r="B133" t="n">
         <v>101326</v>
@@ -15465,14 +15459,14 @@
       <c r="N133" t="inlineStr"/>
       <c r="P133" t="inlineStr">
         <is>
-          <t>Blackstahyttan, Nrk</t>
+          <t>Alvars väg, Blackstahyttan, Nrk</t>
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>499456</v>
+        <v>499353</v>
       </c>
       <c r="R133" t="n">
-        <v>6580855</v>
+        <v>6580961</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -15499,12 +15493,12 @@
       </c>
       <c r="Y133" t="inlineStr">
         <is>
-          <t>2023-09-02</t>
+          <t>2021-09-19</t>
         </is>
       </c>
       <c r="AA133" t="inlineStr">
         <is>
-          <t>2023-09-02</t>
+          <t>2021-09-19</t>
         </is>
       </c>
       <c r="AD133" t="b">
@@ -15517,30 +15511,35 @@
       <c r="AG133" t="b">
         <v>0</v>
       </c>
+      <c r="AI133" t="inlineStr">
+        <is>
+          <t>gammal kalkbarrskog</t>
+        </is>
+      </c>
       <c r="AT133" t="inlineStr"/>
       <c r="AW133" t="inlineStr">
         <is>
-          <t>Toni Berglund</t>
+          <t>Michael Andersson</t>
         </is>
       </c>
       <c r="AX133" t="inlineStr">
         <is>
-          <t>Toni Berglund</t>
+          <t>Michael Andersson, Toni Berglund</t>
         </is>
       </c>
       <c r="AY133" t="inlineStr"/>
       <c r="AZ133" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/111858066</t>
+          <t>https://artportalen.se/Sighting/96195962</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>131900406</v>
+        <v>111858066</v>
       </c>
       <c r="B134" t="n">
-        <v>101403</v>
+        <v>101326</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -15567,11 +15566,7 @@
       </c>
       <c r="I134" t="inlineStr"/>
       <c r="J134" t="inlineStr"/>
-      <c r="K134" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="K134" t="inlineStr"/>
       <c r="L134" t="inlineStr"/>
       <c r="N134" t="inlineStr"/>
       <c r="P134" t="inlineStr">
@@ -15580,10 +15575,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>499349</v>
+        <v>499456</v>
       </c>
       <c r="R134" t="n">
-        <v>6580769</v>
+        <v>6580855</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -15610,12 +15605,12 @@
       </c>
       <c r="Y134" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2023-09-02</t>
         </is>
       </c>
       <c r="AA134" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2023-09-02</t>
         </is>
       </c>
       <c r="AD134" t="b">
@@ -15628,35 +15623,30 @@
       <c r="AG134" t="b">
         <v>0</v>
       </c>
-      <c r="AH134" t="inlineStr">
-        <is>
-          <t>Blåbärsbarrskog</t>
-        </is>
-      </c>
       <c r="AT134" t="inlineStr"/>
       <c r="AW134" t="inlineStr">
         <is>
-          <t>Michael Andersson</t>
+          <t>Toni Berglund</t>
         </is>
       </c>
       <c r="AX134" t="inlineStr">
         <is>
-          <t>Michael Andersson</t>
+          <t>Toni Berglund</t>
         </is>
       </c>
       <c r="AY134" t="inlineStr"/>
       <c r="AZ134" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131900406</t>
+          <t>https://artportalen.se/Sighting/111858066</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>136103341</v>
+        <v>131900406</v>
       </c>
       <c r="B135" t="n">
-        <v>101552</v>
+        <v>101403</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -15696,10 +15686,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>499508</v>
+        <v>499349</v>
       </c>
       <c r="R135" t="n">
-        <v>6580852</v>
+        <v>6580769</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -15726,12 +15716,12 @@
       </c>
       <c r="Y135" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="AA135" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="AD135" t="b">
@@ -15757,19 +15747,19 @@
       </c>
       <c r="AX135" t="inlineStr">
         <is>
-          <t>Michael Andersson, Toni Berglund</t>
+          <t>Michael Andersson</t>
         </is>
       </c>
       <c r="AY135" t="inlineStr"/>
       <c r="AZ135" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136103341</t>
+          <t>https://artportalen.se/Sighting/131900406</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>136104024</v>
+        <v>136103341</v>
       </c>
       <c r="B136" t="n">
         <v>101552</v>
@@ -15812,10 +15802,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>499395</v>
+        <v>499508</v>
       </c>
       <c r="R136" t="n">
-        <v>6580882</v>
+        <v>6580852</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -15865,11 +15855,6 @@
           <t>Blåbärsbarrskog</t>
         </is>
       </c>
-      <c r="AI136" t="inlineStr">
-        <is>
-          <t>stigkant</t>
-        </is>
-      </c>
       <c r="AT136" t="inlineStr"/>
       <c r="AW136" t="inlineStr">
         <is>
@@ -15884,13 +15869,13 @@
       <c r="AY136" t="inlineStr"/>
       <c r="AZ136" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136104024</t>
+          <t>https://artportalen.se/Sighting/136103341</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>136106482</v>
+        <v>136104024</v>
       </c>
       <c r="B137" t="n">
         <v>101552</v>
@@ -15926,21 +15911,17 @@
         </is>
       </c>
       <c r="L137" t="inlineStr"/>
-      <c r="N137" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N137" t="inlineStr"/>
       <c r="P137" t="inlineStr">
         <is>
           <t>Blackstahyttan, Nrk</t>
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>499436</v>
+        <v>499395</v>
       </c>
       <c r="R137" t="n">
-        <v>6580862</v>
+        <v>6580882</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -15987,7 +15968,12 @@
       </c>
       <c r="AH137" t="inlineStr">
         <is>
-          <t>Barrsumpskog</t>
+          <t>Blåbärsbarrskog</t>
+        </is>
+      </c>
+      <c r="AI137" t="inlineStr">
+        <is>
+          <t>stigkant</t>
         </is>
       </c>
       <c r="AT137" t="inlineStr"/>
@@ -16004,13 +15990,13 @@
       <c r="AY137" t="inlineStr"/>
       <c r="AZ137" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136106482</t>
+          <t>https://artportalen.se/Sighting/136104024</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>136106695</v>
+        <v>136106482</v>
       </c>
       <c r="B138" t="n">
         <v>101552</v>
@@ -16046,17 +16032,21 @@
         </is>
       </c>
       <c r="L138" t="inlineStr"/>
-      <c r="N138" t="inlineStr"/>
+      <c r="N138" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P138" t="inlineStr">
         <is>
           <t>Blackstahyttan, Nrk</t>
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>499406</v>
+        <v>499436</v>
       </c>
       <c r="R138" t="n">
-        <v>6580906</v>
+        <v>6580862</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -16103,7 +16093,7 @@
       </c>
       <c r="AH138" t="inlineStr">
         <is>
-          <t>Blåbärsgranskog</t>
+          <t>Barrsumpskog</t>
         </is>
       </c>
       <c r="AT138" t="inlineStr"/>
@@ -16120,13 +16110,13 @@
       <c r="AY138" t="inlineStr"/>
       <c r="AZ138" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136106695</t>
+          <t>https://artportalen.se/Sighting/136106482</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>136107556</v>
+        <v>136106695</v>
       </c>
       <c r="B139" t="n">
         <v>101552</v>
@@ -16169,10 +16159,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>499462</v>
+        <v>499406</v>
       </c>
       <c r="R139" t="n">
-        <v>6580861</v>
+        <v>6580906</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -16219,7 +16209,7 @@
       </c>
       <c r="AH139" t="inlineStr">
         <is>
-          <t>Barrsumpskog</t>
+          <t>Blåbärsgranskog</t>
         </is>
       </c>
       <c r="AT139" t="inlineStr"/>
@@ -16236,16 +16226,16 @@
       <c r="AY139" t="inlineStr"/>
       <c r="AZ139" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136107556</t>
+          <t>https://artportalen.se/Sighting/136106695</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>80046503</v>
+        <v>136107556</v>
       </c>
       <c r="B140" t="n">
-        <v>101228</v>
+        <v>101552</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -16253,37 +16243,45 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>222771</v>
+        <v>222498</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
+      <c r="J140" t="inlineStr"/>
+      <c r="K140" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L140" t="inlineStr"/>
+      <c r="N140" t="inlineStr"/>
       <c r="P140" t="inlineStr">
         <is>
           <t>Blackstahyttan, Nrk</t>
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>499235</v>
+        <v>499462</v>
       </c>
       <c r="R140" t="n">
-        <v>6580819</v>
+        <v>6580861</v>
       </c>
       <c r="S140" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T140" t="inlineStr">
         <is>
@@ -16307,17 +16305,12 @@
       </c>
       <c r="Y140" t="inlineStr">
         <is>
-          <t>2019-09-21</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="AA140" t="inlineStr">
         <is>
-          <t>2019-09-21</t>
-        </is>
-      </c>
-      <c r="AC140" t="inlineStr">
-        <is>
-          <t>NA</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="AD140" t="b">
@@ -16326,33 +16319,39 @@
       <c r="AE140" t="b">
         <v>0</v>
       </c>
+      <c r="AF140" t="inlineStr"/>
       <c r="AG140" t="b">
         <v>0</v>
+      </c>
+      <c r="AH140" t="inlineStr">
+        <is>
+          <t>Barrsumpskog</t>
+        </is>
       </c>
       <c r="AT140" t="inlineStr"/>
       <c r="AW140" t="inlineStr">
         <is>
-          <t>Barbara Kühn</t>
+          <t>Michael Andersson</t>
         </is>
       </c>
       <c r="AX140" t="inlineStr">
         <is>
-          <t>Barbara Kühn, David Tverling, Helena Björnström, Josefina Jansson, Anna Hammar, Anders Carlberg</t>
+          <t>Michael Andersson, Toni Berglund</t>
         </is>
       </c>
       <c r="AY140" t="inlineStr"/>
       <c r="AZ140" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/80046503</t>
+          <t>https://artportalen.se/Sighting/136107556</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>136106667</v>
+        <v>80046503</v>
       </c>
       <c r="B141" t="n">
-        <v>101473</v>
+        <v>101228</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -16360,16 +16359,16 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>222782</v>
+        <v>222771</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Vitsippa</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Anemone nemorosa</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
@@ -16378,27 +16377,19 @@
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
-      <c r="J141" t="inlineStr"/>
-      <c r="K141" t="inlineStr">
-        <is>
-          <t>gulnande löv/blad</t>
-        </is>
-      </c>
-      <c r="L141" t="inlineStr"/>
-      <c r="N141" t="inlineStr"/>
       <c r="P141" t="inlineStr">
         <is>
           <t>Blackstahyttan, Nrk</t>
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>499401</v>
+        <v>499235</v>
       </c>
       <c r="R141" t="n">
-        <v>6580883</v>
+        <v>6580819</v>
       </c>
       <c r="S141" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T141" t="inlineStr">
         <is>
@@ -16422,12 +16413,17 @@
       </c>
       <c r="Y141" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2019-09-21</t>
         </is>
       </c>
       <c r="AA141" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2019-09-21</t>
+        </is>
+      </c>
+      <c r="AC141" t="inlineStr">
+        <is>
+          <t>NA</t>
         </is>
       </c>
       <c r="AD141" t="b">
@@ -16436,39 +16432,33 @@
       <c r="AE141" t="b">
         <v>0</v>
       </c>
-      <c r="AF141" t="inlineStr"/>
       <c r="AG141" t="b">
         <v>0</v>
-      </c>
-      <c r="AH141" t="inlineStr">
-        <is>
-          <t>Barrsumpskog</t>
-        </is>
       </c>
       <c r="AT141" t="inlineStr"/>
       <c r="AW141" t="inlineStr">
         <is>
-          <t>Michael Andersson</t>
+          <t>Barbara Kühn</t>
         </is>
       </c>
       <c r="AX141" t="inlineStr">
         <is>
-          <t>Michael Andersson, Toni Berglund</t>
+          <t>Barbara Kühn, David Tverling, Helena Björnström, Josefina Jansson, Anna Hammar, Anders Carlberg</t>
         </is>
       </c>
       <c r="AY141" t="inlineStr"/>
       <c r="AZ141" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136106667</t>
+          <t>https://artportalen.se/Sighting/80046503</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>136107703</v>
+        <v>136106667</v>
       </c>
       <c r="B142" t="n">
-        <v>99619</v>
+        <v>101473</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -16476,16 +16466,16 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>222812</v>
+        <v>222782</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Liljekonvalj</t>
+          <t>Vitsippa</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Convallaria majalis</t>
+          <t>Anemone nemorosa</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
@@ -16497,7 +16487,7 @@
       <c r="J142" t="inlineStr"/>
       <c r="K142" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>gulnande löv/blad</t>
         </is>
       </c>
       <c r="L142" t="inlineStr"/>
@@ -16508,10 +16498,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>499449</v>
+        <v>499401</v>
       </c>
       <c r="R142" t="n">
-        <v>6580856</v>
+        <v>6580883</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -16575,16 +16565,16 @@
       <c r="AY142" t="inlineStr"/>
       <c r="AZ142" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136107703</t>
+          <t>https://artportalen.se/Sighting/136106667</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>136107647</v>
+        <v>136107703</v>
       </c>
       <c r="B143" t="n">
-        <v>99651</v>
+        <v>99619</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -16592,21 +16582,21 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>222857</v>
+        <v>222812</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Ekorrbär</t>
+          <t>Liljekonvalj</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Maianthemum bifolium</t>
+          <t>Convallaria majalis</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(L.) F. W. Schmidt</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
@@ -16691,16 +16681,16 @@
       <c r="AY143" t="inlineStr"/>
       <c r="AZ143" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136107647</t>
+          <t>https://artportalen.se/Sighting/136107703</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>136103347</v>
+        <v>136107647</v>
       </c>
       <c r="B144" t="n">
-        <v>98393</v>
+        <v>99651</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -16708,26 +16698,30 @@
         </is>
       </c>
       <c r="E144" t="n">
-        <v>223358</v>
+        <v>222857</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Hultbräken</t>
+          <t>Ekorrbär</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Phegopteris connectilis</t>
+          <t>Maianthemum bifolium</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(Michx.) Watt</t>
+          <t>(L.) F. W. Schmidt</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
       <c r="J144" t="inlineStr"/>
-      <c r="K144" t="inlineStr"/>
+      <c r="K144" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L144" t="inlineStr"/>
       <c r="N144" t="inlineStr"/>
       <c r="P144" t="inlineStr">
@@ -16736,10 +16730,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>499508</v>
+        <v>499449</v>
       </c>
       <c r="R144" t="n">
-        <v>6580852</v>
+        <v>6580856</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -16786,7 +16780,7 @@
       </c>
       <c r="AH144" t="inlineStr">
         <is>
-          <t>Blåbärsbarrskog</t>
+          <t>Barrsumpskog</t>
         </is>
       </c>
       <c r="AT144" t="inlineStr"/>
@@ -16803,13 +16797,13 @@
       <c r="AY144" t="inlineStr"/>
       <c r="AZ144" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136103347</t>
+          <t>https://artportalen.se/Sighting/136107647</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>136107617</v>
+        <v>136103347</v>
       </c>
       <c r="B145" t="n">
         <v>98393</v>
@@ -16848,10 +16842,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>499449</v>
+        <v>499508</v>
       </c>
       <c r="R145" t="n">
-        <v>6580856</v>
+        <v>6580852</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -16898,7 +16892,7 @@
       </c>
       <c r="AH145" t="inlineStr">
         <is>
-          <t>Barrsumpskog</t>
+          <t>Blåbärsbarrskog</t>
         </is>
       </c>
       <c r="AT145" t="inlineStr"/>
@@ -16915,16 +16909,16 @@
       <c r="AY145" t="inlineStr"/>
       <c r="AZ145" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136107617</t>
+          <t>https://artportalen.se/Sighting/136103347</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>96368447</v>
+        <v>136107617</v>
       </c>
       <c r="B146" t="n">
-        <v>89079</v>
+        <v>98393</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -16932,24 +16926,28 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>239209</v>
+        <v>223358</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Kantarellvaxing</t>
+          <t>Hultbräken</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Hygrocybe cantharellus</t>
+          <t>Phegopteris connectilis</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Michx.) Watt</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
+      <c r="J146" t="inlineStr"/>
+      <c r="K146" t="inlineStr"/>
+      <c r="L146" t="inlineStr"/>
+      <c r="N146" t="inlineStr"/>
       <c r="P146" t="inlineStr">
         <is>
           <t>Blackstahyttan, Nrk</t>
@@ -16959,7 +16957,7 @@
         <v>499449</v>
       </c>
       <c r="R146" t="n">
-        <v>6580861</v>
+        <v>6580856</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -16986,12 +16984,12 @@
       </c>
       <c r="Y146" t="inlineStr">
         <is>
-          <t>2021-09-27</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="AA146" t="inlineStr">
         <is>
-          <t>2021-09-27</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="AD146" t="b">
@@ -17000,64 +16998,61 @@
       <c r="AE146" t="b">
         <v>0</v>
       </c>
+      <c r="AF146" t="inlineStr"/>
       <c r="AG146" t="b">
         <v>0</v>
       </c>
-      <c r="AI146" t="inlineStr">
-        <is>
-          <t>barrskog</t>
+      <c r="AH146" t="inlineStr">
+        <is>
+          <t>Barrsumpskog</t>
         </is>
       </c>
       <c r="AT146" t="inlineStr"/>
       <c r="AW146" t="inlineStr">
         <is>
-          <t>Hans Rydberg</t>
+          <t>Michael Andersson</t>
         </is>
       </c>
       <c r="AX146" t="inlineStr">
         <is>
-          <t>Hans Rydberg</t>
-        </is>
-      </c>
-      <c r="AY146" t="inlineStr">
-        <is>
-          <t>Länsstyrelsen i Örebro län, inventering</t>
-        </is>
-      </c>
+          <t>Michael Andersson, Toni Berglund</t>
+        </is>
+      </c>
+      <c r="AY146" t="inlineStr"/>
       <c r="AZ146" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/96368447</t>
+          <t>https://artportalen.se/Sighting/136107617</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>75733782</v>
+        <v>96368447</v>
       </c>
       <c r="B147" t="n">
-        <v>91428</v>
+        <v>89079</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E147" t="n">
-        <v>256756</v>
+        <v>239209</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Blek fingersvamp</t>
+          <t>Kantarellvaxing</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Ramaria pallida</t>
+          <t>Hygrocybe cantharellus</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(Schaeff.) Ricken</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
@@ -17067,10 +17062,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>499237</v>
+        <v>499449</v>
       </c>
       <c r="R147" t="n">
-        <v>6580806</v>
+        <v>6580861</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -17097,12 +17092,12 @@
       </c>
       <c r="Y147" t="inlineStr">
         <is>
-          <t>2018-10-13</t>
+          <t>2021-09-27</t>
         </is>
       </c>
       <c r="AA147" t="inlineStr">
         <is>
-          <t>2018-10-13</t>
+          <t>2021-09-27</t>
         </is>
       </c>
       <c r="AD147" t="b">
@@ -17113,16 +17108,21 @@
       </c>
       <c r="AG147" t="b">
         <v>0</v>
+      </c>
+      <c r="AI147" t="inlineStr">
+        <is>
+          <t>barrskog</t>
+        </is>
       </c>
       <c r="AT147" t="inlineStr"/>
       <c r="AW147" t="inlineStr">
         <is>
-          <t>Helena Björnström</t>
+          <t>Hans Rydberg</t>
         </is>
       </c>
       <c r="AX147" t="inlineStr">
         <is>
-          <t>Helena Björnström</t>
+          <t>Hans Rydberg</t>
         </is>
       </c>
       <c r="AY147" t="inlineStr">
@@ -17132,13 +17132,13 @@
       </c>
       <c r="AZ147" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/75733782</t>
+          <t>https://artportalen.se/Sighting/96368447</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>96195231</v>
+        <v>75733782</v>
       </c>
       <c r="B148" t="n">
         <v>91428</v>
@@ -17166,28 +17166,17 @@
           <t>(Schaeff.) Ricken</t>
         </is>
       </c>
-      <c r="I148" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J148" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
-      <c r="K148" t="inlineStr"/>
-      <c r="N148" t="inlineStr"/>
+      <c r="I148" t="inlineStr"/>
       <c r="P148" t="inlineStr">
         <is>
-          <t>Alvars väg, Blackstahyttan, Nrk</t>
+          <t>Blackstahyttan, Nrk</t>
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>499328</v>
+        <v>499237</v>
       </c>
       <c r="R148" t="n">
-        <v>6580771</v>
+        <v>6580806</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -17214,12 +17203,12 @@
       </c>
       <c r="Y148" t="inlineStr">
         <is>
-          <t>2021-09-19</t>
+          <t>2018-10-13</t>
         </is>
       </c>
       <c r="AA148" t="inlineStr">
         <is>
-          <t>2021-09-19</t>
+          <t>2018-10-13</t>
         </is>
       </c>
       <c r="AD148" t="b">
@@ -17228,36 +17217,34 @@
       <c r="AE148" t="b">
         <v>0</v>
       </c>
-      <c r="AF148" t="inlineStr"/>
       <c r="AG148" t="b">
         <v>0</v>
-      </c>
-      <c r="AI148" t="inlineStr">
-        <is>
-          <t>gammal kalkbarrskog</t>
-        </is>
       </c>
       <c r="AT148" t="inlineStr"/>
       <c r="AW148" t="inlineStr">
         <is>
-          <t>Michael Andersson</t>
+          <t>Helena Björnström</t>
         </is>
       </c>
       <c r="AX148" t="inlineStr">
         <is>
-          <t>Michael Andersson, Toni Berglund</t>
-        </is>
-      </c>
-      <c r="AY148" t="inlineStr"/>
+          <t>Helena Björnström</t>
+        </is>
+      </c>
+      <c r="AY148" t="inlineStr">
+        <is>
+          <t>Länsstyrelsen i Örebro län, inventering</t>
+        </is>
+      </c>
       <c r="AZ148" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/96195231</t>
+          <t>https://artportalen.se/Sighting/75733782</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>128198743</v>
+        <v>96195231</v>
       </c>
       <c r="B149" t="n">
         <v>91428</v>
@@ -17285,20 +17272,28 @@
           <t>(Schaeff.) Ricken</t>
         </is>
       </c>
-      <c r="I149" t="inlineStr"/>
-      <c r="J149" t="inlineStr"/>
+      <c r="I149" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J149" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="K149" t="inlineStr"/>
       <c r="N149" t="inlineStr"/>
       <c r="P149" t="inlineStr">
         <is>
-          <t>Alvars väg, Nrk</t>
+          <t>Alvars väg, Blackstahyttan, Nrk</t>
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>499358</v>
+        <v>499328</v>
       </c>
       <c r="R149" t="n">
-        <v>6580971</v>
+        <v>6580771</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -17325,12 +17320,12 @@
       </c>
       <c r="Y149" t="inlineStr">
         <is>
-          <t>2025-09-01</t>
+          <t>2021-09-19</t>
         </is>
       </c>
       <c r="AA149" t="inlineStr">
         <is>
-          <t>2025-09-01</t>
+          <t>2021-09-19</t>
         </is>
       </c>
       <c r="AD149" t="b">
@@ -17343,27 +17338,32 @@
       <c r="AG149" t="b">
         <v>0</v>
       </c>
+      <c r="AI149" t="inlineStr">
+        <is>
+          <t>gammal kalkbarrskog</t>
+        </is>
+      </c>
       <c r="AT149" t="inlineStr"/>
       <c r="AW149" t="inlineStr">
         <is>
-          <t>Toni Berglund</t>
+          <t>Michael Andersson</t>
         </is>
       </c>
       <c r="AX149" t="inlineStr">
         <is>
-          <t>Toni Berglund</t>
+          <t>Michael Andersson, Toni Berglund</t>
         </is>
       </c>
       <c r="AY149" t="inlineStr"/>
       <c r="AZ149" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128198743</t>
+          <t>https://artportalen.se/Sighting/96195231</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>128198755</v>
+        <v>128198743</v>
       </c>
       <c r="B150" t="n">
         <v>91428</v>
@@ -17397,14 +17397,14 @@
       <c r="N150" t="inlineStr"/>
       <c r="P150" t="inlineStr">
         <is>
-          <t>Blackstahyttan, Nrk</t>
+          <t>Alvars väg, Nrk</t>
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>499290</v>
+        <v>499358</v>
       </c>
       <c r="R150" t="n">
-        <v>6580799</v>
+        <v>6580971</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -17463,38 +17463,38 @@
       <c r="AY150" t="inlineStr"/>
       <c r="AZ150" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128198755</t>
+          <t>https://artportalen.se/Sighting/128198743</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>111857904</v>
+        <v>128198755</v>
       </c>
       <c r="B151" t="n">
-        <v>87297</v>
+        <v>91428</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E151" t="n">
-        <v>6003296</v>
+        <v>256756</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Stor odörspindling</t>
+          <t>Blek fingersvamp</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Cortinarius mussivus</t>
+          <t>Ramaria pallida</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(Fr.) Melot</t>
+          <t>(Schaeff.) Ricken</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
@@ -17507,10 +17507,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>499392</v>
+        <v>499290</v>
       </c>
       <c r="R151" t="n">
-        <v>6580908</v>
+        <v>6580799</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -17537,17 +17537,12 @@
       </c>
       <c r="Y151" t="inlineStr">
         <is>
-          <t>2023-09-02</t>
+          <t>2025-09-01</t>
         </is>
       </c>
       <c r="AA151" t="inlineStr">
         <is>
-          <t>2023-09-02</t>
-        </is>
-      </c>
-      <c r="AC151" t="inlineStr">
-        <is>
-          <t>16 fruktkroppar.</t>
+          <t>2025-09-01</t>
         </is>
       </c>
       <c r="AD151" t="b">
@@ -17568,19 +17563,19 @@
       </c>
       <c r="AX151" t="inlineStr">
         <is>
-          <t>Toni Berglund, Lotta Sörman, Anneli Sjöstrand</t>
+          <t>Toni Berglund</t>
         </is>
       </c>
       <c r="AY151" t="inlineStr"/>
       <c r="AZ151" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/111857904</t>
+          <t>https://artportalen.se/Sighting/128198755</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>128078934</v>
+        <v>111857904</v>
       </c>
       <c r="B152" t="n">
         <v>87297</v>
@@ -17609,16 +17604,19 @@
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
+      <c r="J152" t="inlineStr"/>
+      <c r="K152" t="inlineStr"/>
+      <c r="N152" t="inlineStr"/>
       <c r="P152" t="inlineStr">
         <is>
-          <t>Alvars väg, Nrk</t>
+          <t>Blackstahyttan, Nrk</t>
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>499401</v>
+        <v>499392</v>
       </c>
       <c r="R152" t="n">
-        <v>6580907</v>
+        <v>6580908</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -17645,22 +17643,17 @@
       </c>
       <c r="Y152" t="inlineStr">
         <is>
-          <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="Z152" t="inlineStr">
-        <is>
-          <t>15:28</t>
+          <t>2023-09-02</t>
         </is>
       </c>
       <c r="AA152" t="inlineStr">
         <is>
-          <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="AB152" t="inlineStr">
-        <is>
-          <t>15:28</t>
+          <t>2023-09-02</t>
+        </is>
+      </c>
+      <c r="AC152" t="inlineStr">
+        <is>
+          <t>16 fruktkroppar.</t>
         </is>
       </c>
       <c r="AD152" t="b">
@@ -17669,76 +17662,66 @@
       <c r="AE152" t="b">
         <v>0</v>
       </c>
+      <c r="AF152" t="inlineStr"/>
       <c r="AG152" t="b">
         <v>0</v>
       </c>
       <c r="AT152" t="inlineStr"/>
       <c r="AW152" t="inlineStr">
         <is>
-          <t>Anders Carlberg</t>
+          <t>Toni Berglund</t>
         </is>
       </c>
       <c r="AX152" t="inlineStr">
         <is>
-          <t>Anders Carlberg, Toni Berglund</t>
+          <t>Toni Berglund, Lotta Sörman, Anneli Sjöstrand</t>
         </is>
       </c>
       <c r="AY152" t="inlineStr"/>
       <c r="AZ152" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128078934</t>
+          <t>https://artportalen.se/Sighting/111857904</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>96359797</v>
+        <v>128078934</v>
       </c>
       <c r="B153" t="n">
-        <v>93200</v>
+        <v>87297</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E153" t="n">
-        <v>6003297</v>
+        <v>6003296</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Spricktaggsvamp</t>
+          <t>Stor odörspindling</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Hydnellum glaucopus</t>
+          <t>Cortinarius mussivus</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(Maas Geest. &amp; Nannf.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
-        </is>
-      </c>
-      <c r="I153" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J153" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K153" t="inlineStr"/>
-      <c r="N153" t="inlineStr"/>
+          <t>(Fr.) Melot</t>
+        </is>
+      </c>
+      <c r="I153" t="inlineStr"/>
       <c r="P153" t="inlineStr">
         <is>
-          <t>Alvars väg, Blackstahyttan, Nrk</t>
+          <t>Alvars väg, Nrk</t>
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>499400</v>
+        <v>499401</v>
       </c>
       <c r="R153" t="n">
         <v>6580907</v>
@@ -17768,12 +17751,22 @@
       </c>
       <c r="Y153" t="inlineStr">
         <is>
-          <t>2021-09-19</t>
+          <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="Z153" t="inlineStr">
+        <is>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AA153" t="inlineStr">
         <is>
-          <t>2021-09-19</t>
+          <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AB153" t="inlineStr">
+        <is>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AD153" t="b">
@@ -17782,36 +17775,30 @@
       <c r="AE153" t="b">
         <v>0</v>
       </c>
-      <c r="AF153" t="inlineStr"/>
       <c r="AG153" t="b">
         <v>0</v>
-      </c>
-      <c r="AI153" t="inlineStr">
-        <is>
-          <t>under gran i gammal kalkbarrskog</t>
-        </is>
       </c>
       <c r="AT153" t="inlineStr"/>
       <c r="AW153" t="inlineStr">
         <is>
-          <t>Michael Andersson</t>
+          <t>Anders Carlberg</t>
         </is>
       </c>
       <c r="AX153" t="inlineStr">
         <is>
-          <t>Michael Andersson, Toni Berglund</t>
+          <t>Anders Carlberg, Toni Berglund</t>
         </is>
       </c>
       <c r="AY153" t="inlineStr"/>
       <c r="AZ153" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/96359797</t>
+          <t>https://artportalen.se/Sighting/128078934</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>128079275</v>
+        <v>96359797</v>
       </c>
       <c r="B154" t="n">
         <v>93200</v>
@@ -17839,17 +17826,25 @@
           <t>(Maas Geest. &amp; Nannf.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
-      <c r="I154" t="inlineStr"/>
-      <c r="J154" t="inlineStr"/>
+      <c r="I154" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J154" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K154" t="inlineStr"/>
       <c r="N154" t="inlineStr"/>
       <c r="P154" t="inlineStr">
         <is>
-          <t>Alvars väg, Nrk</t>
+          <t>Alvars väg, Blackstahyttan, Nrk</t>
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>499401</v>
+        <v>499400</v>
       </c>
       <c r="R154" t="n">
         <v>6580907</v>
@@ -17879,58 +17874,53 @@
       </c>
       <c r="Y154" t="inlineStr">
         <is>
-          <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="Z154" t="inlineStr">
-        <is>
-          <t>15:28</t>
+          <t>2021-09-19</t>
         </is>
       </c>
       <c r="AA154" t="inlineStr">
         <is>
-          <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="AB154" t="inlineStr">
-        <is>
-          <t>15:28</t>
+          <t>2021-09-19</t>
         </is>
       </c>
       <c r="AD154" t="b">
         <v>0</v>
       </c>
       <c r="AE154" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF154" t="inlineStr"/>
       <c r="AG154" t="b">
         <v>0</v>
       </c>
+      <c r="AI154" t="inlineStr">
+        <is>
+          <t>under gran i gammal kalkbarrskog</t>
+        </is>
+      </c>
       <c r="AT154" t="inlineStr"/>
       <c r="AW154" t="inlineStr">
         <is>
-          <t>Anders Carlberg</t>
+          <t>Michael Andersson</t>
         </is>
       </c>
       <c r="AX154" t="inlineStr">
         <is>
-          <t>Anders Carlberg, Toni Berglund</t>
+          <t>Michael Andersson, Toni Berglund</t>
         </is>
       </c>
       <c r="AY154" t="inlineStr"/>
       <c r="AZ154" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128079275</t>
+          <t>https://artportalen.se/Sighting/96359797</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>136104021</v>
+        <v>128079275</v>
       </c>
       <c r="B155" t="n">
-        <v>93403</v>
+        <v>93200</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -17955,28 +17945,20 @@
           <t>(Maas Geest. &amp; Nannf.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
-      <c r="I155" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J155" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="I155" t="inlineStr"/>
+      <c r="J155" t="inlineStr"/>
       <c r="K155" t="inlineStr"/>
       <c r="N155" t="inlineStr"/>
       <c r="P155" t="inlineStr">
         <is>
-          <t>Blackstahyttan, Nrk</t>
+          <t>Alvars väg, Nrk</t>
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>499395</v>
+        <v>499401</v>
       </c>
       <c r="R155" t="n">
-        <v>6580882</v>
+        <v>6580907</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -18003,55 +17985,55 @@
       </c>
       <c r="Y155" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="Z155" t="inlineStr">
+        <is>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AA155" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AB155" t="inlineStr">
+        <is>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AD155" t="b">
         <v>0</v>
       </c>
       <c r="AE155" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF155" t="inlineStr"/>
       <c r="AG155" t="b">
         <v>0</v>
       </c>
-      <c r="AH155" t="inlineStr">
-        <is>
-          <t>Blåbärsbarrskog</t>
-        </is>
-      </c>
-      <c r="AI155" t="inlineStr">
-        <is>
-          <t>stigkant</t>
-        </is>
-      </c>
       <c r="AT155" t="inlineStr"/>
       <c r="AW155" t="inlineStr">
         <is>
-          <t>Michael Andersson</t>
+          <t>Anders Carlberg</t>
         </is>
       </c>
       <c r="AX155" t="inlineStr">
         <is>
-          <t>Michael Andersson, Toni Berglund</t>
+          <t>Anders Carlberg, Toni Berglund</t>
         </is>
       </c>
       <c r="AY155" t="inlineStr"/>
       <c r="AZ155" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136104021</t>
+          <t>https://artportalen.se/Sighting/128079275</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>136107324</v>
+        <v>136104021</v>
       </c>
       <c r="B156" t="n">
         <v>93403</v>
@@ -18097,10 +18079,10 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>499495</v>
+        <v>499395</v>
       </c>
       <c r="R156" t="n">
-        <v>6580853</v>
+        <v>6580882</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -18152,7 +18134,7 @@
       </c>
       <c r="AI156" t="inlineStr">
         <is>
-          <t>kalkbarrskog invid bäck</t>
+          <t>stigkant</t>
         </is>
       </c>
       <c r="AT156" t="inlineStr"/>
@@ -18169,50 +18151,62 @@
       <c r="AY156" t="inlineStr"/>
       <c r="AZ156" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136107324</t>
+          <t>https://artportalen.se/Sighting/136104021</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>136599222</v>
+        <v>136107324</v>
       </c>
       <c r="B157" t="n">
-        <v>93414</v>
+        <v>93403</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E157" t="n">
-        <v>6047725</v>
+        <v>6003297</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Rödfläckig zontaggsvamp</t>
+          <t>Spricktaggsvamp</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Hydnellum rufoconcrescens nom.prov.</t>
-        </is>
-      </c>
-      <c r="H157" t="inlineStr"/>
-      <c r="I157" t="inlineStr"/>
-      <c r="J157" t="inlineStr"/>
+          <t>Hydnellum glaucopus</t>
+        </is>
+      </c>
+      <c r="H157" t="inlineStr">
+        <is>
+          <t>(Maas Geest. &amp; Nannf.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+        </is>
+      </c>
+      <c r="I157" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J157" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K157" t="inlineStr"/>
       <c r="N157" t="inlineStr"/>
       <c r="P157" t="inlineStr">
         <is>
-          <t>Västantorp, Västantorp, Nrk</t>
+          <t>Blackstahyttan, Nrk</t>
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>499491</v>
+        <v>499495</v>
       </c>
       <c r="R157" t="n">
-        <v>6580841</v>
+        <v>6580853</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -18239,17 +18233,12 @@
       </c>
       <c r="Y157" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="AA157" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
-        </is>
-      </c>
-      <c r="AC157" t="inlineStr">
-        <is>
-          <t>Vid stigen kors Bäck. Med svartvit tagg, P niger och bockspindling.</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="AD157" t="b">
@@ -18262,30 +18251,40 @@
       <c r="AG157" t="b">
         <v>0</v>
       </c>
+      <c r="AH157" t="inlineStr">
+        <is>
+          <t>Blåbärsbarrskog</t>
+        </is>
+      </c>
+      <c r="AI157" t="inlineStr">
+        <is>
+          <t>kalkbarrskog invid bäck</t>
+        </is>
+      </c>
       <c r="AT157" t="inlineStr"/>
       <c r="AW157" t="inlineStr">
         <is>
-          <t>Erik Göthlin</t>
+          <t>Michael Andersson</t>
         </is>
       </c>
       <c r="AX157" t="inlineStr">
         <is>
-          <t>Erik Göthlin</t>
+          <t>Michael Andersson, Toni Berglund</t>
         </is>
       </c>
       <c r="AY157" t="inlineStr"/>
       <c r="AZ157" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136599222</t>
+          <t>https://artportalen.se/Sighting/136107324</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>136597788</v>
+        <v>136599222</v>
       </c>
       <c r="B158" t="n">
-        <v>93428</v>
+        <v>93414</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -18293,34 +18292,33 @@
         </is>
       </c>
       <c r="E158" t="n">
-        <v>6332770</v>
+        <v>6047725</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Rödfläckig zontaggsvamp</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
-        </is>
-      </c>
-      <c r="H158" t="inlineStr">
-        <is>
-          <t>(Fr.) P.Karst.</t>
-        </is>
-      </c>
+          <t>Hydnellum rufoconcrescens nom.prov.</t>
+        </is>
+      </c>
+      <c r="H158" t="inlineStr"/>
       <c r="I158" t="inlineStr"/>
+      <c r="J158" t="inlineStr"/>
+      <c r="K158" t="inlineStr"/>
+      <c r="N158" t="inlineStr"/>
       <c r="P158" t="inlineStr">
         <is>
-          <t>Gretefallet, Gretefallet, Nrk</t>
+          <t>Västantorp, Västantorp, Nrk</t>
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>499525</v>
+        <v>499491</v>
       </c>
       <c r="R158" t="n">
-        <v>6580853</v>
+        <v>6580841</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -18355,12 +18353,18 @@
           <t>2026-09-13</t>
         </is>
       </c>
+      <c r="AC158" t="inlineStr">
+        <is>
+          <t>Vid stigen kors Bäck. Med svartvit tagg, P niger och bockspindling.</t>
+        </is>
+      </c>
       <c r="AD158" t="b">
         <v>0</v>
       </c>
       <c r="AE158" t="b">
         <v>0</v>
       </c>
+      <c r="AF158" t="inlineStr"/>
       <c r="AG158" t="b">
         <v>0</v>
       </c>
@@ -18378,7 +18382,215 @@
       <c r="AY158" t="inlineStr"/>
       <c r="AZ158" t="inlineStr">
         <is>
+          <t>https://artportalen.se/Sighting/136599222</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="n">
+        <v>136597788</v>
+      </c>
+      <c r="B159" t="n">
+        <v>93428</v>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E159" t="n">
+        <v>6332770</v>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>Svart taggsvamp</t>
+        </is>
+      </c>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>Phellodon niger</t>
+        </is>
+      </c>
+      <c r="H159" t="inlineStr">
+        <is>
+          <t>(Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I159" t="inlineStr"/>
+      <c r="P159" t="inlineStr">
+        <is>
+          <t>Gretefallet, Gretefallet, Nrk</t>
+        </is>
+      </c>
+      <c r="Q159" t="n">
+        <v>499525</v>
+      </c>
+      <c r="R159" t="n">
+        <v>6580853</v>
+      </c>
+      <c r="S159" t="n">
+        <v>10</v>
+      </c>
+      <c r="T159" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U159" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="V159" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W159" t="inlineStr">
+        <is>
+          <t>Kil</t>
+        </is>
+      </c>
+      <c r="Y159" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="AA159" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="AD159" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE159" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG159" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT159" t="inlineStr"/>
+      <c r="AW159" t="inlineStr">
+        <is>
+          <t>Erik Göthlin</t>
+        </is>
+      </c>
+      <c r="AX159" t="inlineStr">
+        <is>
+          <t>Erik Göthlin</t>
+        </is>
+      </c>
+      <c r="AY159" t="inlineStr"/>
+      <c r="AZ159" t="inlineStr">
+        <is>
           <t>https://artportalen.se/Sighting/136597788</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="n">
+        <v>136609580</v>
+      </c>
+      <c r="B160" t="n">
+        <v>93428</v>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E160" t="n">
+        <v>6332770</v>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>Svart taggsvamp</t>
+        </is>
+      </c>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>Phellodon niger</t>
+        </is>
+      </c>
+      <c r="H160" t="inlineStr">
+        <is>
+          <t>(Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I160" t="inlineStr"/>
+      <c r="J160" t="inlineStr"/>
+      <c r="K160" t="inlineStr"/>
+      <c r="N160" t="inlineStr"/>
+      <c r="P160" t="inlineStr">
+        <is>
+          <t>NV Blackstahyttan, Nrk</t>
+        </is>
+      </c>
+      <c r="Q160" t="n">
+        <v>499533</v>
+      </c>
+      <c r="R160" t="n">
+        <v>6580838</v>
+      </c>
+      <c r="S160" t="n">
+        <v>10</v>
+      </c>
+      <c r="T160" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U160" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="V160" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W160" t="inlineStr">
+        <is>
+          <t>Kil</t>
+        </is>
+      </c>
+      <c r="Y160" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="AA160" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="AD160" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE160" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF160" t="inlineStr"/>
+      <c r="AG160" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT160" t="inlineStr"/>
+      <c r="AW160" t="inlineStr">
+        <is>
+          <t>Erik Göthlin</t>
+        </is>
+      </c>
+      <c r="AX160" t="inlineStr">
+        <is>
+          <t>Erik Göthlin</t>
+        </is>
+      </c>
+      <c r="AY160" t="inlineStr"/>
+      <c r="AZ160" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136609580</t>
         </is>
       </c>
     </row>
@@ -18541,6 +18753,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ156" r:id="rId155"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ157" r:id="rId156"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ158" r:id="rId157"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ159" r:id="rId158"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ160" r:id="rId159"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/S 3548-2025 artfynd.xlsx
+++ b/artfynd/S 3548-2025 artfynd.xlsx
@@ -3074,7 +3074,7 @@
         <v>136107340</v>
       </c>
       <c r="B24" t="n">
-        <v>93402</v>
+        <v>93405</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3979,7 +3979,7 @@
         <v>136106654</v>
       </c>
       <c r="B32" t="n">
-        <v>97997</v>
+        <v>98000</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -5428,7 +5428,7 @@
         <v>136107502</v>
       </c>
       <c r="B45" t="n">
-        <v>96927</v>
+        <v>96930</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5557,7 +5557,7 @@
         <v>136107520</v>
       </c>
       <c r="B46" t="n">
-        <v>96927</v>
+        <v>96930</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5686,7 +5686,7 @@
         <v>136107706</v>
       </c>
       <c r="B47" t="n">
-        <v>96927</v>
+        <v>96930</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5810,7 +5810,7 @@
         <v>136107596</v>
       </c>
       <c r="B48" t="n">
-        <v>97954</v>
+        <v>97957</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5939,7 +5939,7 @@
         <v>136107444</v>
       </c>
       <c r="B49" t="n">
-        <v>98065</v>
+        <v>98068</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6069,7 +6069,7 @@
         <v>136107670</v>
       </c>
       <c r="B50" t="n">
-        <v>96554</v>
+        <v>96557</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6166,7 +6166,7 @@
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Michael Andersson, Toni Berglund</t>
+          <t>Toni Berglund, Michael Andersson</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
@@ -6729,7 +6729,7 @@
         <v>136106530</v>
       </c>
       <c r="B56" t="n">
-        <v>91872</v>
+        <v>91881</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -9035,7 +9035,7 @@
         <v>136597825</v>
       </c>
       <c r="B77" t="n">
-        <v>93412</v>
+        <v>93415</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -10450,7 +10450,7 @@
         <v>136597260</v>
       </c>
       <c r="B90" t="n">
-        <v>93426</v>
+        <v>93429</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10564,7 +10564,7 @@
         <v>136609571</v>
       </c>
       <c r="B91" t="n">
-        <v>93426</v>
+        <v>93429</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10670,7 +10670,7 @@
         <v>136103383</v>
       </c>
       <c r="B92" t="n">
-        <v>93429</v>
+        <v>93432</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10896,7 +10896,7 @@
         <v>136103380</v>
       </c>
       <c r="B94" t="n">
-        <v>91588</v>
+        <v>91590</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -12336,7 +12336,7 @@
         <v>136103331</v>
       </c>
       <c r="B107" t="n">
-        <v>93436</v>
+        <v>93439</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12460,7 +12460,7 @@
         <v>136597853</v>
       </c>
       <c r="B108" t="n">
-        <v>93436</v>
+        <v>93439</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -13696,7 +13696,7 @@
         <v>136106670</v>
       </c>
       <c r="B118" t="n">
-        <v>98363</v>
+        <v>98366</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -13808,7 +13808,7 @@
         <v>136106545</v>
       </c>
       <c r="B119" t="n">
-        <v>108437</v>
+        <v>108440</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -13924,7 +13924,7 @@
         <v>136106660</v>
       </c>
       <c r="B120" t="n">
-        <v>108437</v>
+        <v>108440</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -14151,7 +14151,7 @@
         <v>136103300</v>
       </c>
       <c r="B122" t="n">
-        <v>107053</v>
+        <v>107056</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -14263,7 +14263,7 @@
         <v>136106552</v>
       </c>
       <c r="B123" t="n">
-        <v>106358</v>
+        <v>106361</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -14375,7 +14375,7 @@
         <v>136106673</v>
       </c>
       <c r="B124" t="n">
-        <v>106358</v>
+        <v>106361</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -14487,7 +14487,7 @@
         <v>136107698</v>
       </c>
       <c r="B125" t="n">
-        <v>106358</v>
+        <v>106361</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -14715,7 +14715,7 @@
         <v>136103391</v>
       </c>
       <c r="B127" t="n">
-        <v>106517</v>
+        <v>106520</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -14831,7 +14831,7 @@
         <v>136107643</v>
       </c>
       <c r="B128" t="n">
-        <v>106517</v>
+        <v>106520</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -14928,7 +14928,7 @@
       </c>
       <c r="AX128" t="inlineStr">
         <is>
-          <t>Michael Andersson, Toni Berglund</t>
+          <t>Toni Berglund, Michael Andersson</t>
         </is>
       </c>
       <c r="AY128" t="inlineStr"/>
@@ -14943,7 +14943,7 @@
         <v>136103972</v>
       </c>
       <c r="B129" t="n">
-        <v>100104</v>
+        <v>100107</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -15064,7 +15064,7 @@
         <v>136106473</v>
       </c>
       <c r="B130" t="n">
-        <v>100104</v>
+        <v>100107</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -15192,7 +15192,7 @@
         <v>136107586</v>
       </c>
       <c r="B131" t="n">
-        <v>100104</v>
+        <v>100107</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -15762,7 +15762,7 @@
         <v>136103341</v>
       </c>
       <c r="B136" t="n">
-        <v>101552</v>
+        <v>101555</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -15878,7 +15878,7 @@
         <v>136104024</v>
       </c>
       <c r="B137" t="n">
-        <v>101552</v>
+        <v>101555</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -15999,7 +15999,7 @@
         <v>136106482</v>
       </c>
       <c r="B138" t="n">
-        <v>101552</v>
+        <v>101555</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -16119,7 +16119,7 @@
         <v>136106695</v>
       </c>
       <c r="B139" t="n">
-        <v>101552</v>
+        <v>101555</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -16235,7 +16235,7 @@
         <v>136107556</v>
       </c>
       <c r="B140" t="n">
-        <v>101552</v>
+        <v>101555</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -16458,7 +16458,7 @@
         <v>136106667</v>
       </c>
       <c r="B142" t="n">
-        <v>101473</v>
+        <v>101476</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -16574,7 +16574,7 @@
         <v>136107703</v>
       </c>
       <c r="B143" t="n">
-        <v>99619</v>
+        <v>99622</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -16690,7 +16690,7 @@
         <v>136107647</v>
       </c>
       <c r="B144" t="n">
-        <v>99651</v>
+        <v>99654</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -16791,7 +16791,7 @@
       </c>
       <c r="AX144" t="inlineStr">
         <is>
-          <t>Michael Andersson, Toni Berglund</t>
+          <t>Toni Berglund, Michael Andersson</t>
         </is>
       </c>
       <c r="AY144" t="inlineStr"/>
@@ -16806,7 +16806,7 @@
         <v>136103347</v>
       </c>
       <c r="B145" t="n">
-        <v>98393</v>
+        <v>98396</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -16918,7 +16918,7 @@
         <v>136107617</v>
       </c>
       <c r="B146" t="n">
-        <v>98393</v>
+        <v>98396</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -17015,7 +17015,7 @@
       </c>
       <c r="AX146" t="inlineStr">
         <is>
-          <t>Michael Andersson, Toni Berglund</t>
+          <t>Toni Berglund, Michael Andersson</t>
         </is>
       </c>
       <c r="AY146" t="inlineStr"/>
@@ -18036,7 +18036,7 @@
         <v>136104021</v>
       </c>
       <c r="B156" t="n">
-        <v>93403</v>
+        <v>93406</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -18160,7 +18160,7 @@
         <v>136107324</v>
       </c>
       <c r="B157" t="n">
-        <v>93403</v>
+        <v>93406</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -18284,7 +18284,7 @@
         <v>136599222</v>
       </c>
       <c r="B158" t="n">
-        <v>93414</v>
+        <v>93417</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -18391,7 +18391,7 @@
         <v>136597788</v>
       </c>
       <c r="B159" t="n">
-        <v>93428</v>
+        <v>93431</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -18493,7 +18493,7 @@
         <v>136609580</v>
       </c>
       <c r="B160" t="n">
-        <v>93428</v>
+        <v>93431</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>

--- a/artfynd/S 3548-2025 artfynd.xlsx
+++ b/artfynd/S 3548-2025 artfynd.xlsx
@@ -3074,7 +3074,7 @@
         <v>136107340</v>
       </c>
       <c r="B24" t="n">
-        <v>93405</v>
+        <v>93406</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3979,7 +3979,7 @@
         <v>136106654</v>
       </c>
       <c r="B32" t="n">
-        <v>98000</v>
+        <v>98001</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -5428,7 +5428,7 @@
         <v>136107502</v>
       </c>
       <c r="B45" t="n">
-        <v>96930</v>
+        <v>96931</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5557,7 +5557,7 @@
         <v>136107520</v>
       </c>
       <c r="B46" t="n">
-        <v>96930</v>
+        <v>96931</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5686,7 +5686,7 @@
         <v>136107706</v>
       </c>
       <c r="B47" t="n">
-        <v>96930</v>
+        <v>96931</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5810,7 +5810,7 @@
         <v>136107596</v>
       </c>
       <c r="B48" t="n">
-        <v>97957</v>
+        <v>97958</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5939,7 +5939,7 @@
         <v>136107444</v>
       </c>
       <c r="B49" t="n">
-        <v>98068</v>
+        <v>98069</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6069,7 +6069,7 @@
         <v>136107670</v>
       </c>
       <c r="B50" t="n">
-        <v>96557</v>
+        <v>96558</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6166,7 +6166,7 @@
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Toni Berglund, Michael Andersson</t>
+          <t>Michael Andersson, Toni Berglund</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
@@ -6729,7 +6729,7 @@
         <v>136106530</v>
       </c>
       <c r="B56" t="n">
-        <v>91881</v>
+        <v>91882</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -9035,7 +9035,7 @@
         <v>136597825</v>
       </c>
       <c r="B77" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -10450,7 +10450,7 @@
         <v>136597260</v>
       </c>
       <c r="B90" t="n">
-        <v>93429</v>
+        <v>93430</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10564,7 +10564,7 @@
         <v>136609571</v>
       </c>
       <c r="B91" t="n">
-        <v>93429</v>
+        <v>93430</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10670,7 +10670,7 @@
         <v>136103383</v>
       </c>
       <c r="B92" t="n">
-        <v>93432</v>
+        <v>93433</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -12336,7 +12336,7 @@
         <v>136103331</v>
       </c>
       <c r="B107" t="n">
-        <v>93439</v>
+        <v>93440</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12460,7 +12460,7 @@
         <v>136597853</v>
       </c>
       <c r="B108" t="n">
-        <v>93439</v>
+        <v>93440</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -13696,7 +13696,7 @@
         <v>136106670</v>
       </c>
       <c r="B118" t="n">
-        <v>98366</v>
+        <v>98367</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -13808,7 +13808,7 @@
         <v>136106545</v>
       </c>
       <c r="B119" t="n">
-        <v>108440</v>
+        <v>108441</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -13924,7 +13924,7 @@
         <v>136106660</v>
       </c>
       <c r="B120" t="n">
-        <v>108440</v>
+        <v>108441</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -14151,7 +14151,7 @@
         <v>136103300</v>
       </c>
       <c r="B122" t="n">
-        <v>107056</v>
+        <v>107057</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -14263,7 +14263,7 @@
         <v>136106552</v>
       </c>
       <c r="B123" t="n">
-        <v>106361</v>
+        <v>106362</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -14375,7 +14375,7 @@
         <v>136106673</v>
       </c>
       <c r="B124" t="n">
-        <v>106361</v>
+        <v>106362</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -14487,7 +14487,7 @@
         <v>136107698</v>
       </c>
       <c r="B125" t="n">
-        <v>106361</v>
+        <v>106362</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -14715,7 +14715,7 @@
         <v>136103391</v>
       </c>
       <c r="B127" t="n">
-        <v>106520</v>
+        <v>106521</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -14831,7 +14831,7 @@
         <v>136107643</v>
       </c>
       <c r="B128" t="n">
-        <v>106520</v>
+        <v>106521</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -14928,7 +14928,7 @@
       </c>
       <c r="AX128" t="inlineStr">
         <is>
-          <t>Toni Berglund, Michael Andersson</t>
+          <t>Michael Andersson, Toni Berglund</t>
         </is>
       </c>
       <c r="AY128" t="inlineStr"/>
@@ -14943,7 +14943,7 @@
         <v>136103972</v>
       </c>
       <c r="B129" t="n">
-        <v>100107</v>
+        <v>100108</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -15064,7 +15064,7 @@
         <v>136106473</v>
       </c>
       <c r="B130" t="n">
-        <v>100107</v>
+        <v>100108</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -15192,7 +15192,7 @@
         <v>136107586</v>
       </c>
       <c r="B131" t="n">
-        <v>100107</v>
+        <v>100108</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -15762,7 +15762,7 @@
         <v>136103341</v>
       </c>
       <c r="B136" t="n">
-        <v>101555</v>
+        <v>101556</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -15878,7 +15878,7 @@
         <v>136104024</v>
       </c>
       <c r="B137" t="n">
-        <v>101555</v>
+        <v>101556</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -15999,7 +15999,7 @@
         <v>136106482</v>
       </c>
       <c r="B138" t="n">
-        <v>101555</v>
+        <v>101556</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -16119,7 +16119,7 @@
         <v>136106695</v>
       </c>
       <c r="B139" t="n">
-        <v>101555</v>
+        <v>101556</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -16235,7 +16235,7 @@
         <v>136107556</v>
       </c>
       <c r="B140" t="n">
-        <v>101555</v>
+        <v>101556</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -16458,7 +16458,7 @@
         <v>136106667</v>
       </c>
       <c r="B142" t="n">
-        <v>101476</v>
+        <v>101477</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -16574,7 +16574,7 @@
         <v>136107703</v>
       </c>
       <c r="B143" t="n">
-        <v>99622</v>
+        <v>99623</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -16690,7 +16690,7 @@
         <v>136107647</v>
       </c>
       <c r="B144" t="n">
-        <v>99654</v>
+        <v>99655</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -16791,7 +16791,7 @@
       </c>
       <c r="AX144" t="inlineStr">
         <is>
-          <t>Toni Berglund, Michael Andersson</t>
+          <t>Michael Andersson, Toni Berglund</t>
         </is>
       </c>
       <c r="AY144" t="inlineStr"/>
@@ -16806,7 +16806,7 @@
         <v>136103347</v>
       </c>
       <c r="B145" t="n">
-        <v>98396</v>
+        <v>98397</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -16918,7 +16918,7 @@
         <v>136107617</v>
       </c>
       <c r="B146" t="n">
-        <v>98396</v>
+        <v>98397</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -17015,7 +17015,7 @@
       </c>
       <c r="AX146" t="inlineStr">
         <is>
-          <t>Toni Berglund, Michael Andersson</t>
+          <t>Michael Andersson, Toni Berglund</t>
         </is>
       </c>
       <c r="AY146" t="inlineStr"/>
@@ -18036,7 +18036,7 @@
         <v>136104021</v>
       </c>
       <c r="B156" t="n">
-        <v>93406</v>
+        <v>93407</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -18160,7 +18160,7 @@
         <v>136107324</v>
       </c>
       <c r="B157" t="n">
-        <v>93406</v>
+        <v>93407</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -18284,7 +18284,7 @@
         <v>136599222</v>
       </c>
       <c r="B158" t="n">
-        <v>93417</v>
+        <v>93418</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -18391,7 +18391,7 @@
         <v>136597788</v>
       </c>
       <c r="B159" t="n">
-        <v>93431</v>
+        <v>93432</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -18493,7 +18493,7 @@
         <v>136609580</v>
       </c>
       <c r="B160" t="n">
-        <v>93431</v>
+        <v>93432</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>

--- a/artfynd/S 3548-2025 artfynd.xlsx
+++ b/artfynd/S 3548-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ160"/>
+  <dimension ref="A1:AZ161"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17575,36 +17575,44 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>111857904</v>
+        <v>136738638</v>
       </c>
       <c r="B152" t="n">
-        <v>87297</v>
+        <v>91609</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E152" t="n">
-        <v>6003296</v>
+        <v>256756</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Stor odörspindling</t>
+          <t>Blek fingersvamp</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Cortinarius mussivus</t>
+          <t>Ramaria pallida</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(Fr.) Melot</t>
-        </is>
-      </c>
-      <c r="I152" t="inlineStr"/>
-      <c r="J152" t="inlineStr"/>
+          <t>(Schaeff.) Ricken</t>
+        </is>
+      </c>
+      <c r="I152" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J152" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K152" t="inlineStr"/>
       <c r="N152" t="inlineStr"/>
       <c r="P152" t="inlineStr">
@@ -17613,10 +17621,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>499392</v>
+        <v>499290</v>
       </c>
       <c r="R152" t="n">
-        <v>6580908</v>
+        <v>6580794</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -17643,17 +17651,12 @@
       </c>
       <c r="Y152" t="inlineStr">
         <is>
-          <t>2023-09-02</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="AA152" t="inlineStr">
         <is>
-          <t>2023-09-02</t>
-        </is>
-      </c>
-      <c r="AC152" t="inlineStr">
-        <is>
-          <t>16 fruktkroppar.</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="AD152" t="b">
@@ -17662,7 +17665,6 @@
       <c r="AE152" t="b">
         <v>0</v>
       </c>
-      <c r="AF152" t="inlineStr"/>
       <c r="AG152" t="b">
         <v>0</v>
       </c>
@@ -17674,19 +17676,19 @@
       </c>
       <c r="AX152" t="inlineStr">
         <is>
-          <t>Toni Berglund, Lotta Sörman, Anneli Sjöstrand</t>
+          <t>Toni Berglund</t>
         </is>
       </c>
       <c r="AY152" t="inlineStr"/>
       <c r="AZ152" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/111857904</t>
+          <t>https://artportalen.se/Sighting/136738638</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>128078934</v>
+        <v>111857904</v>
       </c>
       <c r="B153" t="n">
         <v>87297</v>
@@ -17715,16 +17717,19 @@
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
+      <c r="J153" t="inlineStr"/>
+      <c r="K153" t="inlineStr"/>
+      <c r="N153" t="inlineStr"/>
       <c r="P153" t="inlineStr">
         <is>
-          <t>Alvars väg, Nrk</t>
+          <t>Blackstahyttan, Nrk</t>
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>499401</v>
+        <v>499392</v>
       </c>
       <c r="R153" t="n">
-        <v>6580907</v>
+        <v>6580908</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -17751,22 +17756,17 @@
       </c>
       <c r="Y153" t="inlineStr">
         <is>
-          <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="Z153" t="inlineStr">
-        <is>
-          <t>15:28</t>
+          <t>2023-09-02</t>
         </is>
       </c>
       <c r="AA153" t="inlineStr">
         <is>
-          <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="AB153" t="inlineStr">
-        <is>
-          <t>15:28</t>
+          <t>2023-09-02</t>
+        </is>
+      </c>
+      <c r="AC153" t="inlineStr">
+        <is>
+          <t>16 fruktkroppar.</t>
         </is>
       </c>
       <c r="AD153" t="b">
@@ -17775,76 +17775,66 @@
       <c r="AE153" t="b">
         <v>0</v>
       </c>
+      <c r="AF153" t="inlineStr"/>
       <c r="AG153" t="b">
         <v>0</v>
       </c>
       <c r="AT153" t="inlineStr"/>
       <c r="AW153" t="inlineStr">
         <is>
-          <t>Anders Carlberg</t>
+          <t>Toni Berglund</t>
         </is>
       </c>
       <c r="AX153" t="inlineStr">
         <is>
-          <t>Anders Carlberg, Toni Berglund</t>
+          <t>Toni Berglund, Lotta Sörman, Anneli Sjöstrand</t>
         </is>
       </c>
       <c r="AY153" t="inlineStr"/>
       <c r="AZ153" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128078934</t>
+          <t>https://artportalen.se/Sighting/111857904</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>96359797</v>
+        <v>128078934</v>
       </c>
       <c r="B154" t="n">
-        <v>93200</v>
+        <v>87297</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E154" t="n">
-        <v>6003297</v>
+        <v>6003296</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Spricktaggsvamp</t>
+          <t>Stor odörspindling</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Hydnellum glaucopus</t>
+          <t>Cortinarius mussivus</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(Maas Geest. &amp; Nannf.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
-        </is>
-      </c>
-      <c r="I154" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J154" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K154" t="inlineStr"/>
-      <c r="N154" t="inlineStr"/>
+          <t>(Fr.) Melot</t>
+        </is>
+      </c>
+      <c r="I154" t="inlineStr"/>
       <c r="P154" t="inlineStr">
         <is>
-          <t>Alvars väg, Blackstahyttan, Nrk</t>
+          <t>Alvars väg, Nrk</t>
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>499400</v>
+        <v>499401</v>
       </c>
       <c r="R154" t="n">
         <v>6580907</v>
@@ -17874,12 +17864,22 @@
       </c>
       <c r="Y154" t="inlineStr">
         <is>
-          <t>2021-09-19</t>
+          <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="Z154" t="inlineStr">
+        <is>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AA154" t="inlineStr">
         <is>
-          <t>2021-09-19</t>
+          <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AB154" t="inlineStr">
+        <is>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AD154" t="b">
@@ -17888,36 +17888,30 @@
       <c r="AE154" t="b">
         <v>0</v>
       </c>
-      <c r="AF154" t="inlineStr"/>
       <c r="AG154" t="b">
         <v>0</v>
-      </c>
-      <c r="AI154" t="inlineStr">
-        <is>
-          <t>under gran i gammal kalkbarrskog</t>
-        </is>
       </c>
       <c r="AT154" t="inlineStr"/>
       <c r="AW154" t="inlineStr">
         <is>
-          <t>Michael Andersson</t>
+          <t>Anders Carlberg</t>
         </is>
       </c>
       <c r="AX154" t="inlineStr">
         <is>
-          <t>Michael Andersson, Toni Berglund</t>
+          <t>Anders Carlberg, Toni Berglund</t>
         </is>
       </c>
       <c r="AY154" t="inlineStr"/>
       <c r="AZ154" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/96359797</t>
+          <t>https://artportalen.se/Sighting/128078934</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>128079275</v>
+        <v>96359797</v>
       </c>
       <c r="B155" t="n">
         <v>93200</v>
@@ -17945,17 +17939,25 @@
           <t>(Maas Geest. &amp; Nannf.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
-      <c r="I155" t="inlineStr"/>
-      <c r="J155" t="inlineStr"/>
+      <c r="I155" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J155" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K155" t="inlineStr"/>
       <c r="N155" t="inlineStr"/>
       <c r="P155" t="inlineStr">
         <is>
-          <t>Alvars väg, Nrk</t>
+          <t>Alvars väg, Blackstahyttan, Nrk</t>
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>499401</v>
+        <v>499400</v>
       </c>
       <c r="R155" t="n">
         <v>6580907</v>
@@ -17985,58 +17987,53 @@
       </c>
       <c r="Y155" t="inlineStr">
         <is>
-          <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="Z155" t="inlineStr">
-        <is>
-          <t>15:28</t>
+          <t>2021-09-19</t>
         </is>
       </c>
       <c r="AA155" t="inlineStr">
         <is>
-          <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="AB155" t="inlineStr">
-        <is>
-          <t>15:28</t>
+          <t>2021-09-19</t>
         </is>
       </c>
       <c r="AD155" t="b">
         <v>0</v>
       </c>
       <c r="AE155" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF155" t="inlineStr"/>
       <c r="AG155" t="b">
         <v>0</v>
       </c>
+      <c r="AI155" t="inlineStr">
+        <is>
+          <t>under gran i gammal kalkbarrskog</t>
+        </is>
+      </c>
       <c r="AT155" t="inlineStr"/>
       <c r="AW155" t="inlineStr">
         <is>
-          <t>Anders Carlberg</t>
+          <t>Michael Andersson</t>
         </is>
       </c>
       <c r="AX155" t="inlineStr">
         <is>
-          <t>Anders Carlberg, Toni Berglund</t>
+          <t>Michael Andersson, Toni Berglund</t>
         </is>
       </c>
       <c r="AY155" t="inlineStr"/>
       <c r="AZ155" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128079275</t>
+          <t>https://artportalen.se/Sighting/96359797</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>136104021</v>
+        <v>128079275</v>
       </c>
       <c r="B156" t="n">
-        <v>93407</v>
+        <v>93200</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -18061,28 +18058,20 @@
           <t>(Maas Geest. &amp; Nannf.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
-      <c r="I156" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J156" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="I156" t="inlineStr"/>
+      <c r="J156" t="inlineStr"/>
       <c r="K156" t="inlineStr"/>
       <c r="N156" t="inlineStr"/>
       <c r="P156" t="inlineStr">
         <is>
-          <t>Blackstahyttan, Nrk</t>
+          <t>Alvars väg, Nrk</t>
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>499395</v>
+        <v>499401</v>
       </c>
       <c r="R156" t="n">
-        <v>6580882</v>
+        <v>6580907</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -18109,55 +18098,55 @@
       </c>
       <c r="Y156" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="Z156" t="inlineStr">
+        <is>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AA156" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AB156" t="inlineStr">
+        <is>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AD156" t="b">
         <v>0</v>
       </c>
       <c r="AE156" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF156" t="inlineStr"/>
       <c r="AG156" t="b">
         <v>0</v>
       </c>
-      <c r="AH156" t="inlineStr">
-        <is>
-          <t>Blåbärsbarrskog</t>
-        </is>
-      </c>
-      <c r="AI156" t="inlineStr">
-        <is>
-          <t>stigkant</t>
-        </is>
-      </c>
       <c r="AT156" t="inlineStr"/>
       <c r="AW156" t="inlineStr">
         <is>
-          <t>Michael Andersson</t>
+          <t>Anders Carlberg</t>
         </is>
       </c>
       <c r="AX156" t="inlineStr">
         <is>
-          <t>Michael Andersson, Toni Berglund</t>
+          <t>Anders Carlberg, Toni Berglund</t>
         </is>
       </c>
       <c r="AY156" t="inlineStr"/>
       <c r="AZ156" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136104021</t>
+          <t>https://artportalen.se/Sighting/128079275</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>136107324</v>
+        <v>136104021</v>
       </c>
       <c r="B157" t="n">
         <v>93407</v>
@@ -18203,10 +18192,10 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>499495</v>
+        <v>499395</v>
       </c>
       <c r="R157" t="n">
-        <v>6580853</v>
+        <v>6580882</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -18258,7 +18247,7 @@
       </c>
       <c r="AI157" t="inlineStr">
         <is>
-          <t>kalkbarrskog invid bäck</t>
+          <t>stigkant</t>
         </is>
       </c>
       <c r="AT157" t="inlineStr"/>
@@ -18275,50 +18264,62 @@
       <c r="AY157" t="inlineStr"/>
       <c r="AZ157" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136107324</t>
+          <t>https://artportalen.se/Sighting/136104021</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>136599222</v>
+        <v>136107324</v>
       </c>
       <c r="B158" t="n">
-        <v>93418</v>
+        <v>93407</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E158" t="n">
-        <v>6047725</v>
+        <v>6003297</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Rödfläckig zontaggsvamp</t>
+          <t>Spricktaggsvamp</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Hydnellum rufoconcrescens nom.prov.</t>
-        </is>
-      </c>
-      <c r="H158" t="inlineStr"/>
-      <c r="I158" t="inlineStr"/>
-      <c r="J158" t="inlineStr"/>
+          <t>Hydnellum glaucopus</t>
+        </is>
+      </c>
+      <c r="H158" t="inlineStr">
+        <is>
+          <t>(Maas Geest. &amp; Nannf.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+        </is>
+      </c>
+      <c r="I158" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J158" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K158" t="inlineStr"/>
       <c r="N158" t="inlineStr"/>
       <c r="P158" t="inlineStr">
         <is>
-          <t>Västantorp, Västantorp, Nrk</t>
+          <t>Blackstahyttan, Nrk</t>
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>499491</v>
+        <v>499495</v>
       </c>
       <c r="R158" t="n">
-        <v>6580841</v>
+        <v>6580853</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -18345,17 +18346,12 @@
       </c>
       <c r="Y158" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="AA158" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
-        </is>
-      </c>
-      <c r="AC158" t="inlineStr">
-        <is>
-          <t>Vid stigen kors Bäck. Med svartvit tagg, P niger och bockspindling.</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="AD158" t="b">
@@ -18368,30 +18364,40 @@
       <c r="AG158" t="b">
         <v>0</v>
       </c>
+      <c r="AH158" t="inlineStr">
+        <is>
+          <t>Blåbärsbarrskog</t>
+        </is>
+      </c>
+      <c r="AI158" t="inlineStr">
+        <is>
+          <t>kalkbarrskog invid bäck</t>
+        </is>
+      </c>
       <c r="AT158" t="inlineStr"/>
       <c r="AW158" t="inlineStr">
         <is>
-          <t>Erik Göthlin</t>
+          <t>Michael Andersson</t>
         </is>
       </c>
       <c r="AX158" t="inlineStr">
         <is>
-          <t>Erik Göthlin</t>
+          <t>Michael Andersson, Toni Berglund</t>
         </is>
       </c>
       <c r="AY158" t="inlineStr"/>
       <c r="AZ158" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136599222</t>
+          <t>https://artportalen.se/Sighting/136107324</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>136597788</v>
+        <v>136599222</v>
       </c>
       <c r="B159" t="n">
-        <v>93432</v>
+        <v>93418</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -18399,34 +18405,33 @@
         </is>
       </c>
       <c r="E159" t="n">
-        <v>6332770</v>
+        <v>6047725</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Rödfläckig zontaggsvamp</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
-        </is>
-      </c>
-      <c r="H159" t="inlineStr">
-        <is>
-          <t>(Fr.) P.Karst.</t>
-        </is>
-      </c>
+          <t>Hydnellum rufoconcrescens nom.prov.</t>
+        </is>
+      </c>
+      <c r="H159" t="inlineStr"/>
       <c r="I159" t="inlineStr"/>
+      <c r="J159" t="inlineStr"/>
+      <c r="K159" t="inlineStr"/>
+      <c r="N159" t="inlineStr"/>
       <c r="P159" t="inlineStr">
         <is>
-          <t>Gretefallet, Gretefallet, Nrk</t>
+          <t>Västantorp, Västantorp, Nrk</t>
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>499525</v>
+        <v>499491</v>
       </c>
       <c r="R159" t="n">
-        <v>6580853</v>
+        <v>6580841</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -18461,12 +18466,18 @@
           <t>2026-09-13</t>
         </is>
       </c>
+      <c r="AC159" t="inlineStr">
+        <is>
+          <t>Vid stigen kors Bäck. Med svartvit tagg, P niger och bockspindling.</t>
+        </is>
+      </c>
       <c r="AD159" t="b">
         <v>0</v>
       </c>
       <c r="AE159" t="b">
         <v>0</v>
       </c>
+      <c r="AF159" t="inlineStr"/>
       <c r="AG159" t="b">
         <v>0</v>
       </c>
@@ -18484,13 +18495,13 @@
       <c r="AY159" t="inlineStr"/>
       <c r="AZ159" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136597788</t>
+          <t>https://artportalen.se/Sighting/136599222</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>136609580</v>
+        <v>136597788</v>
       </c>
       <c r="B160" t="n">
         <v>93432</v>
@@ -18519,19 +18530,16 @@
         </is>
       </c>
       <c r="I160" t="inlineStr"/>
-      <c r="J160" t="inlineStr"/>
-      <c r="K160" t="inlineStr"/>
-      <c r="N160" t="inlineStr"/>
       <c r="P160" t="inlineStr">
         <is>
-          <t>NV Blackstahyttan, Nrk</t>
+          <t>Gretefallet, Gretefallet, Nrk</t>
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>499533</v>
+        <v>499525</v>
       </c>
       <c r="R160" t="n">
-        <v>6580838</v>
+        <v>6580853</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -18572,7 +18580,6 @@
       <c r="AE160" t="b">
         <v>0</v>
       </c>
-      <c r="AF160" t="inlineStr"/>
       <c r="AG160" t="b">
         <v>0</v>
       </c>
@@ -18589,6 +18596,112 @@
       </c>
       <c r="AY160" t="inlineStr"/>
       <c r="AZ160" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136597788</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="n">
+        <v>136609580</v>
+      </c>
+      <c r="B161" t="n">
+        <v>93432</v>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E161" t="n">
+        <v>6332770</v>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>Svart taggsvamp</t>
+        </is>
+      </c>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>Phellodon niger</t>
+        </is>
+      </c>
+      <c r="H161" t="inlineStr">
+        <is>
+          <t>(Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I161" t="inlineStr"/>
+      <c r="J161" t="inlineStr"/>
+      <c r="K161" t="inlineStr"/>
+      <c r="N161" t="inlineStr"/>
+      <c r="P161" t="inlineStr">
+        <is>
+          <t>NV Blackstahyttan, Nrk</t>
+        </is>
+      </c>
+      <c r="Q161" t="n">
+        <v>499533</v>
+      </c>
+      <c r="R161" t="n">
+        <v>6580838</v>
+      </c>
+      <c r="S161" t="n">
+        <v>10</v>
+      </c>
+      <c r="T161" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U161" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="V161" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W161" t="inlineStr">
+        <is>
+          <t>Kil</t>
+        </is>
+      </c>
+      <c r="Y161" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="AA161" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="AD161" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE161" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF161" t="inlineStr"/>
+      <c r="AG161" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT161" t="inlineStr"/>
+      <c r="AW161" t="inlineStr">
+        <is>
+          <t>Erik Göthlin</t>
+        </is>
+      </c>
+      <c r="AX161" t="inlineStr">
+        <is>
+          <t>Erik Göthlin</t>
+        </is>
+      </c>
+      <c r="AY161" t="inlineStr"/>
+      <c r="AZ161" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/136609580</t>
         </is>
@@ -18755,6 +18868,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ158" r:id="rId157"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ159" r:id="rId158"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ160" r:id="rId159"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ161" r:id="rId160"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/S 3548-2025 artfynd.xlsx
+++ b/artfynd/S 3548-2025 artfynd.xlsx
@@ -3074,7 +3074,7 @@
         <v>136107340</v>
       </c>
       <c r="B24" t="n">
-        <v>93406</v>
+        <v>93411</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3979,7 +3979,7 @@
         <v>136106654</v>
       </c>
       <c r="B32" t="n">
-        <v>98001</v>
+        <v>98006</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -5428,7 +5428,7 @@
         <v>136107502</v>
       </c>
       <c r="B45" t="n">
-        <v>96931</v>
+        <v>96936</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5557,7 +5557,7 @@
         <v>136107520</v>
       </c>
       <c r="B46" t="n">
-        <v>96931</v>
+        <v>96936</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5686,7 +5686,7 @@
         <v>136107706</v>
       </c>
       <c r="B47" t="n">
-        <v>96931</v>
+        <v>96936</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5810,7 +5810,7 @@
         <v>136107596</v>
       </c>
       <c r="B48" t="n">
-        <v>97958</v>
+        <v>97963</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5939,7 +5939,7 @@
         <v>136107444</v>
       </c>
       <c r="B49" t="n">
-        <v>98069</v>
+        <v>98074</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6069,7 +6069,7 @@
         <v>136107670</v>
       </c>
       <c r="B50" t="n">
-        <v>96558</v>
+        <v>96563</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6729,7 +6729,7 @@
         <v>136106530</v>
       </c>
       <c r="B56" t="n">
-        <v>91882</v>
+        <v>91887</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -9035,7 +9035,7 @@
         <v>136597825</v>
       </c>
       <c r="B77" t="n">
-        <v>93416</v>
+        <v>93421</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -10450,7 +10450,7 @@
         <v>136597260</v>
       </c>
       <c r="B90" t="n">
-        <v>93430</v>
+        <v>93435</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10564,7 +10564,7 @@
         <v>136609571</v>
       </c>
       <c r="B91" t="n">
-        <v>93430</v>
+        <v>93435</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10670,7 +10670,7 @@
         <v>136103383</v>
       </c>
       <c r="B92" t="n">
-        <v>93433</v>
+        <v>93438</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10896,7 +10896,7 @@
         <v>136103380</v>
       </c>
       <c r="B94" t="n">
-        <v>91590</v>
+        <v>91592</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -12336,7 +12336,7 @@
         <v>136103331</v>
       </c>
       <c r="B107" t="n">
-        <v>93440</v>
+        <v>93445</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12460,7 +12460,7 @@
         <v>136597853</v>
       </c>
       <c r="B108" t="n">
-        <v>93440</v>
+        <v>93445</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12778,7 +12778,7 @@
         <v>136106499</v>
       </c>
       <c r="B111" t="n">
-        <v>75447</v>
+        <v>75449</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -12916,7 +12916,7 @@
         <v>136107535</v>
       </c>
       <c r="B112" t="n">
-        <v>75447</v>
+        <v>75449</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -13059,7 +13059,7 @@
         <v>136107679</v>
       </c>
       <c r="B113" t="n">
-        <v>75447</v>
+        <v>75449</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -13696,7 +13696,7 @@
         <v>136106670</v>
       </c>
       <c r="B118" t="n">
-        <v>98367</v>
+        <v>98372</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -13808,7 +13808,7 @@
         <v>136106545</v>
       </c>
       <c r="B119" t="n">
-        <v>108441</v>
+        <v>108446</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -13924,7 +13924,7 @@
         <v>136106660</v>
       </c>
       <c r="B120" t="n">
-        <v>108441</v>
+        <v>108446</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -14151,7 +14151,7 @@
         <v>136103300</v>
       </c>
       <c r="B122" t="n">
-        <v>107057</v>
+        <v>107062</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -14263,7 +14263,7 @@
         <v>136106552</v>
       </c>
       <c r="B123" t="n">
-        <v>106362</v>
+        <v>106367</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -14375,7 +14375,7 @@
         <v>136106673</v>
       </c>
       <c r="B124" t="n">
-        <v>106362</v>
+        <v>106367</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -14487,7 +14487,7 @@
         <v>136107698</v>
       </c>
       <c r="B125" t="n">
-        <v>106362</v>
+        <v>106367</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -14715,7 +14715,7 @@
         <v>136103391</v>
       </c>
       <c r="B127" t="n">
-        <v>106521</v>
+        <v>106526</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -14831,7 +14831,7 @@
         <v>136107643</v>
       </c>
       <c r="B128" t="n">
-        <v>106521</v>
+        <v>106526</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -14943,7 +14943,7 @@
         <v>136103972</v>
       </c>
       <c r="B129" t="n">
-        <v>100108</v>
+        <v>100113</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -15064,7 +15064,7 @@
         <v>136106473</v>
       </c>
       <c r="B130" t="n">
-        <v>100108</v>
+        <v>100113</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -15192,7 +15192,7 @@
         <v>136107586</v>
       </c>
       <c r="B131" t="n">
-        <v>100108</v>
+        <v>100113</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -15762,7 +15762,7 @@
         <v>136103341</v>
       </c>
       <c r="B136" t="n">
-        <v>101556</v>
+        <v>101561</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -15878,7 +15878,7 @@
         <v>136104024</v>
       </c>
       <c r="B137" t="n">
-        <v>101556</v>
+        <v>101561</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -15999,7 +15999,7 @@
         <v>136106482</v>
       </c>
       <c r="B138" t="n">
-        <v>101556</v>
+        <v>101561</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -16119,7 +16119,7 @@
         <v>136106695</v>
       </c>
       <c r="B139" t="n">
-        <v>101556</v>
+        <v>101561</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -16235,7 +16235,7 @@
         <v>136107556</v>
       </c>
       <c r="B140" t="n">
-        <v>101556</v>
+        <v>101561</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -16458,7 +16458,7 @@
         <v>136106667</v>
       </c>
       <c r="B142" t="n">
-        <v>101477</v>
+        <v>101482</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -16574,7 +16574,7 @@
         <v>136107703</v>
       </c>
       <c r="B143" t="n">
-        <v>99623</v>
+        <v>99628</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -16690,7 +16690,7 @@
         <v>136107647</v>
       </c>
       <c r="B144" t="n">
-        <v>99655</v>
+        <v>99660</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -16806,7 +16806,7 @@
         <v>136103347</v>
       </c>
       <c r="B145" t="n">
-        <v>98397</v>
+        <v>98402</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -16918,7 +16918,7 @@
         <v>136107617</v>
       </c>
       <c r="B146" t="n">
-        <v>98397</v>
+        <v>98402</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -17578,7 +17578,7 @@
         <v>136738638</v>
       </c>
       <c r="B152" t="n">
-        <v>91609</v>
+        <v>91611</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -18149,7 +18149,7 @@
         <v>136104021</v>
       </c>
       <c r="B157" t="n">
-        <v>93407</v>
+        <v>93412</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -18273,7 +18273,7 @@
         <v>136107324</v>
       </c>
       <c r="B158" t="n">
-        <v>93407</v>
+        <v>93412</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -18397,7 +18397,7 @@
         <v>136599222</v>
       </c>
       <c r="B159" t="n">
-        <v>93418</v>
+        <v>93423</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -18504,7 +18504,7 @@
         <v>136597788</v>
       </c>
       <c r="B160" t="n">
-        <v>93432</v>
+        <v>93437</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -18606,7 +18606,7 @@
         <v>136609580</v>
       </c>
       <c r="B161" t="n">
-        <v>93432</v>
+        <v>93437</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>

--- a/artfynd/S 3548-2025 artfynd.xlsx
+++ b/artfynd/S 3548-2025 artfynd.xlsx
@@ -9035,7 +9035,7 @@
         <v>136597825</v>
       </c>
       <c r="B77" t="n">
-        <v>93421</v>
+        <v>93423</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -10450,7 +10450,7 @@
         <v>136597260</v>
       </c>
       <c r="B90" t="n">
-        <v>93435</v>
+        <v>93437</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10564,7 +10564,7 @@
         <v>136609571</v>
       </c>
       <c r="B91" t="n">
-        <v>93435</v>
+        <v>93437</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -12460,7 +12460,7 @@
         <v>136597853</v>
       </c>
       <c r="B108" t="n">
-        <v>93445</v>
+        <v>93447</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -17578,7 +17578,7 @@
         <v>136738638</v>
       </c>
       <c r="B152" t="n">
-        <v>91611</v>
+        <v>91613</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -18397,7 +18397,7 @@
         <v>136599222</v>
       </c>
       <c r="B159" t="n">
-        <v>93423</v>
+        <v>93425</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -18504,7 +18504,7 @@
         <v>136597788</v>
       </c>
       <c r="B160" t="n">
-        <v>93437</v>
+        <v>93439</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -18606,7 +18606,7 @@
         <v>136609580</v>
       </c>
       <c r="B161" t="n">
-        <v>93437</v>
+        <v>93439</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>

--- a/artfynd/S 3548-2025 artfynd.xlsx
+++ b/artfynd/S 3548-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ161"/>
+  <dimension ref="A1:AZ162"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8271,10 +8271,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>73691143</v>
+        <v>137007784</v>
       </c>
       <c r="B70" t="n">
-        <v>93209</v>
+        <v>93411</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8282,37 +8282,41 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>4366</v>
+        <v>4364</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Banker</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Blackstahyttan V, Nrk</t>
+          <t>Klockhammar, Nrk</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>499350</v>
+        <v>499486</v>
       </c>
       <c r="R70" t="n">
-        <v>6580778</v>
+        <v>6580846</v>
       </c>
       <c r="S70" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -8336,12 +8340,27 @@
       </c>
       <c r="Y70" t="inlineStr">
         <is>
-          <t>2018-10-14</t>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="Z70" t="inlineStr">
+        <is>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>2018-10-14</t>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="AB70" t="inlineStr">
+        <is>
+          <t>10:44</t>
+        </is>
+      </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8356,24 +8375,24 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>David Tverling</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>David Tverling, Anna Hammar, Lotta Sörman, Therese Steiner</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
       <c r="AZ70" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/73691143</t>
+          <t>https://artportalen.se/Sighting/137007784</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>75733752</v>
+        <v>73691143</v>
       </c>
       <c r="B71" t="n">
         <v>93209</v>
@@ -8404,14 +8423,14 @@
       <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Blackstahyttan, Nrk</t>
+          <t>Blackstahyttan V, Nrk</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>499351</v>
+        <v>499350</v>
       </c>
       <c r="R71" t="n">
-        <v>6580978</v>
+        <v>6580778</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8438,12 +8457,12 @@
       </c>
       <c r="Y71" t="inlineStr">
         <is>
-          <t>2018-10-13</t>
+          <t>2018-10-14</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>2018-10-13</t>
+          <t>2018-10-14</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8458,28 +8477,24 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Helena Björnström</t>
+          <t>David Tverling</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Helena Björnström</t>
-        </is>
-      </c>
-      <c r="AY71" t="inlineStr">
-        <is>
-          <t>Länsstyrelsen i Örebro län, inventering</t>
-        </is>
-      </c>
+          <t>David Tverling, Anna Hammar, Lotta Sörman, Therese Steiner</t>
+        </is>
+      </c>
+      <c r="AY71" t="inlineStr"/>
       <c r="AZ71" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/75733752</t>
+          <t>https://artportalen.se/Sighting/73691143</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>88151679</v>
+        <v>75733752</v>
       </c>
       <c r="B72" t="n">
         <v>93209</v>
@@ -8514,13 +8529,13 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>499398</v>
+        <v>499351</v>
       </c>
       <c r="R72" t="n">
-        <v>6580897</v>
+        <v>6580978</v>
       </c>
       <c r="S72" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -8544,12 +8559,12 @@
       </c>
       <c r="Y72" t="inlineStr">
         <is>
-          <t>2020-09-23</t>
+          <t>2018-10-13</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
         <is>
-          <t>2020-09-23</t>
+          <t>2018-10-13</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8560,21 +8575,16 @@
       </c>
       <c r="AG72" t="b">
         <v>0</v>
-      </c>
-      <c r="AI72" t="inlineStr">
-        <is>
-          <t>gammal barrskog</t>
-        </is>
       </c>
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Hans Rydberg</t>
+          <t>Helena Björnström</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Hans Rydberg</t>
+          <t>Helena Björnström</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr">
@@ -8584,13 +8594,13 @@
       </c>
       <c r="AZ72" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/88151679</t>
+          <t>https://artportalen.se/Sighting/75733752</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>96334081</v>
+        <v>88151679</v>
       </c>
       <c r="B73" t="n">
         <v>93209</v>
@@ -8618,31 +8628,20 @@
           <t>Banker</t>
         </is>
       </c>
-      <c r="I73" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J73" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K73" t="inlineStr"/>
-      <c r="N73" t="inlineStr"/>
+      <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Alvars väg, Blackstahyttan, Nrk</t>
+          <t>Blackstahyttan, Nrk</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>499393</v>
+        <v>499398</v>
       </c>
       <c r="R73" t="n">
-        <v>6580905</v>
+        <v>6580897</v>
       </c>
       <c r="S73" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -8666,12 +8665,12 @@
       </c>
       <c r="Y73" t="inlineStr">
         <is>
-          <t>2021-09-19</t>
+          <t>2020-09-23</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>2021-09-19</t>
+          <t>2020-09-23</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8680,36 +8679,39 @@
       <c r="AE73" t="b">
         <v>0</v>
       </c>
-      <c r="AF73" t="inlineStr"/>
       <c r="AG73" t="b">
         <v>0</v>
       </c>
       <c r="AI73" t="inlineStr">
         <is>
-          <t>gammal kalkbarrskog</t>
+          <t>gammal barrskog</t>
         </is>
       </c>
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Michael Andersson</t>
+          <t>Hans Rydberg</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Michael Andersson, Toni Berglund</t>
-        </is>
-      </c>
-      <c r="AY73" t="inlineStr"/>
+          <t>Hans Rydberg</t>
+        </is>
+      </c>
+      <c r="AY73" t="inlineStr">
+        <is>
+          <t>Länsstyrelsen i Örebro län, inventering</t>
+        </is>
+      </c>
       <c r="AZ73" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/96334081</t>
+          <t>https://artportalen.se/Sighting/88151679</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>96359789</v>
+        <v>96334081</v>
       </c>
       <c r="B74" t="n">
         <v>93209</v>
@@ -8737,8 +8739,16 @@
           <t>Banker</t>
         </is>
       </c>
-      <c r="I74" t="inlineStr"/>
-      <c r="J74" t="inlineStr"/>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K74" t="inlineStr"/>
       <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
@@ -8747,13 +8757,13 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>499400</v>
+        <v>499393</v>
       </c>
       <c r="R74" t="n">
-        <v>6580907</v>
+        <v>6580905</v>
       </c>
       <c r="S74" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -8797,7 +8807,7 @@
       </c>
       <c r="AI74" t="inlineStr">
         <is>
-          <t>under gran i gammal kalkbarrskog</t>
+          <t>gammal kalkbarrskog</t>
         </is>
       </c>
       <c r="AT74" t="inlineStr"/>
@@ -8814,13 +8824,13 @@
       <c r="AY74" t="inlineStr"/>
       <c r="AZ74" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/96359789</t>
+          <t>https://artportalen.se/Sighting/96334081</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>111858054</v>
+        <v>96359789</v>
       </c>
       <c r="B75" t="n">
         <v>93209</v>
@@ -8854,14 +8864,14 @@
       <c r="N75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Blackstahyttan, Nrk</t>
+          <t>Alvars väg, Blackstahyttan, Nrk</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>499481</v>
+        <v>499400</v>
       </c>
       <c r="R75" t="n">
-        <v>6580859</v>
+        <v>6580907</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8888,12 +8898,12 @@
       </c>
       <c r="Y75" t="inlineStr">
         <is>
-          <t>2023-09-02</t>
+          <t>2021-09-19</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>2023-09-02</t>
+          <t>2021-09-19</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8906,27 +8916,32 @@
       <c r="AG75" t="b">
         <v>0</v>
       </c>
+      <c r="AI75" t="inlineStr">
+        <is>
+          <t>under gran i gammal kalkbarrskog</t>
+        </is>
+      </c>
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Toni Berglund</t>
+          <t>Michael Andersson</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Toni Berglund</t>
+          <t>Michael Andersson, Toni Berglund</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
       <c r="AZ75" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/111858054</t>
+          <t>https://artportalen.se/Sighting/96359789</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>128198646</v>
+        <v>111858054</v>
       </c>
       <c r="B76" t="n">
         <v>93209</v>
@@ -8960,14 +8975,14 @@
       <c r="N76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Alvars väg, Nrk</t>
+          <t>Blackstahyttan, Nrk</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>499496</v>
+        <v>499481</v>
       </c>
       <c r="R76" t="n">
-        <v>6580849</v>
+        <v>6580859</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8994,12 +9009,12 @@
       </c>
       <c r="Y76" t="inlineStr">
         <is>
-          <t>2025-09-01</t>
+          <t>2023-09-02</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
         <is>
-          <t>2025-09-01</t>
+          <t>2023-09-02</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9026,16 +9041,16 @@
       <c r="AY76" t="inlineStr"/>
       <c r="AZ76" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128198646</t>
+          <t>https://artportalen.se/Sighting/111858054</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>136597825</v>
+        <v>128198646</v>
       </c>
       <c r="B77" t="n">
-        <v>93423</v>
+        <v>93209</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9061,16 +9076,19 @@
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
+      <c r="J77" t="inlineStr"/>
+      <c r="K77" t="inlineStr"/>
+      <c r="N77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Västantorp, Västantorp, Nrk</t>
+          <t>Alvars väg, Nrk</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>499477</v>
+        <v>499496</v>
       </c>
       <c r="R77" t="n">
-        <v>6580844</v>
+        <v>6580849</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -9097,12 +9115,12 @@
       </c>
       <c r="Y77" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2025-09-01</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2025-09-01</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9111,33 +9129,34 @@
       <c r="AE77" t="b">
         <v>0</v>
       </c>
+      <c r="AF77" t="inlineStr"/>
       <c r="AG77" t="b">
         <v>0</v>
       </c>
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Erik Göthlin</t>
+          <t>Toni Berglund</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Erik Göthlin</t>
+          <t>Toni Berglund</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
       <c r="AZ77" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136597825</t>
+          <t>https://artportalen.se/Sighting/128198646</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>111857920</v>
+        <v>136597825</v>
       </c>
       <c r="B78" t="n">
-        <v>93215</v>
+        <v>93423</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9145,37 +9164,34 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>4368</v>
+        <v>4366</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Dofttaggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Hydnellum suaveolens</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) P. Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
-      <c r="J78" t="inlineStr"/>
-      <c r="K78" t="inlineStr"/>
-      <c r="N78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Blackstahyttan, Nrk</t>
+          <t>Västantorp, Västantorp, Nrk</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>499522</v>
+        <v>499477</v>
       </c>
       <c r="R78" t="n">
-        <v>6580856</v>
+        <v>6580844</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -9202,17 +9218,12 @@
       </c>
       <c r="Y78" t="inlineStr">
         <is>
-          <t>2023-09-02</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
         <is>
-          <t>2023-09-02</t>
-        </is>
-      </c>
-      <c r="AC78" t="inlineStr">
-        <is>
-          <t>Mycket rikligt med fruktkroppar.</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9221,31 +9232,30 @@
       <c r="AE78" t="b">
         <v>0</v>
       </c>
-      <c r="AF78" t="inlineStr"/>
       <c r="AG78" t="b">
         <v>0</v>
       </c>
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Toni Berglund</t>
+          <t>Erik Göthlin</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Toni Berglund</t>
+          <t>Erik Göthlin</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
       <c r="AZ78" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/111857920</t>
+          <t>https://artportalen.se/Sighting/136597825</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>111858048</v>
+        <v>111857920</v>
       </c>
       <c r="B79" t="n">
         <v>93215</v>
@@ -9283,10 +9293,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>499481</v>
+        <v>499522</v>
       </c>
       <c r="R79" t="n">
-        <v>6580859</v>
+        <v>6580856</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9323,7 +9333,7 @@
       </c>
       <c r="AC79" t="inlineStr">
         <is>
-          <t>Rikligt med fruktkroppar.</t>
+          <t>Mycket rikligt med fruktkroppar.</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9350,13 +9360,13 @@
       <c r="AY79" t="inlineStr"/>
       <c r="AZ79" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/111858048</t>
+          <t>https://artportalen.se/Sighting/111857920</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>128198645</v>
+        <v>111858048</v>
       </c>
       <c r="B80" t="n">
         <v>93215</v>
@@ -9390,14 +9400,14 @@
       <c r="N80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Alvars väg, Nrk</t>
+          <t>Blackstahyttan, Nrk</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>499496</v>
+        <v>499481</v>
       </c>
       <c r="R80" t="n">
-        <v>6580849</v>
+        <v>6580859</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9424,12 +9434,17 @@
       </c>
       <c r="Y80" t="inlineStr">
         <is>
-          <t>2025-09-01</t>
+          <t>2023-09-02</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
         <is>
-          <t>2025-09-01</t>
+          <t>2023-09-02</t>
+        </is>
+      </c>
+      <c r="AC80" t="inlineStr">
+        <is>
+          <t>Rikligt med fruktkroppar.</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9456,54 +9471,57 @@
       <c r="AY80" t="inlineStr"/>
       <c r="AZ80" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128198645</t>
+          <t>https://artportalen.se/Sighting/111858048</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>80046502</v>
+        <v>128198645</v>
       </c>
       <c r="B81" t="n">
-        <v>92869</v>
+        <v>93215</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>4769</v>
+        <v>4368</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Dofttaggsvamp</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Hydnellum suaveolens</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(Scop.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
+      <c r="J81" t="inlineStr"/>
+      <c r="K81" t="inlineStr"/>
+      <c r="N81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Blackstahyttan, Nrk</t>
+          <t>Alvars väg, Nrk</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>499235</v>
+        <v>499496</v>
       </c>
       <c r="R81" t="n">
-        <v>6580819</v>
+        <v>6580849</v>
       </c>
       <c r="S81" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -9527,17 +9545,12 @@
       </c>
       <c r="Y81" t="inlineStr">
         <is>
-          <t>2019-09-21</t>
+          <t>2025-09-01</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
         <is>
-          <t>2019-09-21</t>
-        </is>
-      </c>
-      <c r="AC81" t="inlineStr">
-        <is>
-          <t>NA</t>
+          <t>2025-09-01</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9546,30 +9559,31 @@
       <c r="AE81" t="b">
         <v>0</v>
       </c>
+      <c r="AF81" t="inlineStr"/>
       <c r="AG81" t="b">
         <v>0</v>
       </c>
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Barbara Kühn</t>
+          <t>Toni Berglund</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Barbara Kühn, David Tverling, Helena Björnström, Josefina Jansson, Anna Hammar, Anders Carlberg</t>
+          <t>Toni Berglund</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
       <c r="AZ81" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/80046502</t>
+          <t>https://artportalen.se/Sighting/128198645</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>96368201</v>
+        <v>80046502</v>
       </c>
       <c r="B82" t="n">
         <v>92869</v>
@@ -9604,13 +9618,13 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>499417</v>
+        <v>499235</v>
       </c>
       <c r="R82" t="n">
-        <v>6580838</v>
+        <v>6580819</v>
       </c>
       <c r="S82" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -9634,12 +9648,17 @@
       </c>
       <c r="Y82" t="inlineStr">
         <is>
-          <t>2021-09-27</t>
+          <t>2019-09-21</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
         <is>
-          <t>2021-09-27</t>
+          <t>2019-09-21</t>
+        </is>
+      </c>
+      <c r="AC82" t="inlineStr">
+        <is>
+          <t>NA</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9650,37 +9669,28 @@
       </c>
       <c r="AG82" t="b">
         <v>0</v>
-      </c>
-      <c r="AI82" t="inlineStr">
-        <is>
-          <t>barrskog</t>
-        </is>
       </c>
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Hans Rydberg</t>
+          <t>Barbara Kühn</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Hans Rydberg</t>
-        </is>
-      </c>
-      <c r="AY82" t="inlineStr">
-        <is>
-          <t>Länsstyrelsen i Örebro län, inventering</t>
-        </is>
-      </c>
+          <t>Barbara Kühn, David Tverling, Helena Björnström, Josefina Jansson, Anna Hammar, Anders Carlberg</t>
+        </is>
+      </c>
+      <c r="AY82" t="inlineStr"/>
       <c r="AZ82" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/96368201</t>
+          <t>https://artportalen.se/Sighting/80046502</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>96368202</v>
+        <v>96368201</v>
       </c>
       <c r="B83" t="n">
         <v>92869</v>
@@ -9715,10 +9725,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>499465</v>
+        <v>499417</v>
       </c>
       <c r="R83" t="n">
-        <v>6580853</v>
+        <v>6580838</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9785,13 +9795,13 @@
       </c>
       <c r="AZ83" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/96368202</t>
+          <t>https://artportalen.se/Sighting/96368201</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>96368203</v>
+        <v>96368202</v>
       </c>
       <c r="B84" t="n">
         <v>92869</v>
@@ -9826,10 +9836,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>499432</v>
+        <v>499465</v>
       </c>
       <c r="R84" t="n">
-        <v>6580867</v>
+        <v>6580853</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9896,13 +9906,13 @@
       </c>
       <c r="AZ84" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/96368203</t>
+          <t>https://artportalen.se/Sighting/96368202</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>128198632</v>
+        <v>96368203</v>
       </c>
       <c r="B85" t="n">
         <v>92869</v>
@@ -9931,19 +9941,16 @@
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
-      <c r="J85" t="inlineStr"/>
-      <c r="K85" t="inlineStr"/>
-      <c r="N85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Alvars väg, Nrk</t>
+          <t>Blackstahyttan, Nrk</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>499538</v>
+        <v>499432</v>
       </c>
       <c r="R85" t="n">
-        <v>6580862</v>
+        <v>6580867</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9970,17 +9977,12 @@
       </c>
       <c r="Y85" t="inlineStr">
         <is>
-          <t>2025-09-01</t>
+          <t>2021-09-27</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
         <is>
-          <t>2025-09-01</t>
-        </is>
-      </c>
-      <c r="AC85" t="inlineStr">
-        <is>
-          <t>Allmän</t>
+          <t>2021-09-27</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9989,31 +9991,39 @@
       <c r="AE85" t="b">
         <v>0</v>
       </c>
-      <c r="AF85" t="inlineStr"/>
       <c r="AG85" t="b">
         <v>0</v>
+      </c>
+      <c r="AI85" t="inlineStr">
+        <is>
+          <t>barrskog</t>
+        </is>
       </c>
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Toni Berglund</t>
+          <t>Hans Rydberg</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Toni Berglund</t>
-        </is>
-      </c>
-      <c r="AY85" t="inlineStr"/>
+          <t>Hans Rydberg</t>
+        </is>
+      </c>
+      <c r="AY85" t="inlineStr">
+        <is>
+          <t>Länsstyrelsen i Örebro län, inventering</t>
+        </is>
+      </c>
       <c r="AZ85" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128198632</t>
+          <t>https://artportalen.se/Sighting/96368203</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>128198659</v>
+        <v>128198632</v>
       </c>
       <c r="B86" t="n">
         <v>92869</v>
@@ -10051,10 +10061,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>499464</v>
+        <v>499538</v>
       </c>
       <c r="R86" t="n">
-        <v>6580851</v>
+        <v>6580862</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -10089,6 +10099,11 @@
           <t>2025-09-01</t>
         </is>
       </c>
+      <c r="AC86" t="inlineStr">
+        <is>
+          <t>Allmän</t>
+        </is>
+      </c>
       <c r="AD86" t="b">
         <v>0</v>
       </c>
@@ -10113,13 +10128,13 @@
       <c r="AY86" t="inlineStr"/>
       <c r="AZ86" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128198659</t>
+          <t>https://artportalen.se/Sighting/128198632</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>128198667</v>
+        <v>128198659</v>
       </c>
       <c r="B87" t="n">
         <v>92869</v>
@@ -10157,10 +10172,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>499467</v>
+        <v>499464</v>
       </c>
       <c r="R87" t="n">
-        <v>6580849</v>
+        <v>6580851</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -10219,51 +10234,54 @@
       <c r="AY87" t="inlineStr"/>
       <c r="AZ87" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128198667</t>
+          <t>https://artportalen.se/Sighting/128198659</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>96368723</v>
+        <v>128198667</v>
       </c>
       <c r="B88" t="n">
-        <v>90522</v>
+        <v>92869</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>4962</v>
+        <v>4769</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Mjölsvärting</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Lyophyllum semitale</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Fr. : Fr.) Kühner</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
+      <c r="J88" t="inlineStr"/>
+      <c r="K88" t="inlineStr"/>
+      <c r="N88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Blackstahyttan, Nrk</t>
+          <t>Alvars väg, Nrk</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>499348</v>
+        <v>499467</v>
       </c>
       <c r="R88" t="n">
-        <v>6580781</v>
+        <v>6580849</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -10290,12 +10308,12 @@
       </c>
       <c r="Y88" t="inlineStr">
         <is>
-          <t>2021-09-27</t>
+          <t>2025-09-01</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
         <is>
-          <t>2021-09-27</t>
+          <t>2025-09-01</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10304,42 +10322,34 @@
       <c r="AE88" t="b">
         <v>0</v>
       </c>
+      <c r="AF88" t="inlineStr"/>
       <c r="AG88" t="b">
         <v>0</v>
-      </c>
-      <c r="AI88" t="inlineStr">
-        <is>
-          <t>barrskog</t>
-        </is>
       </c>
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Hans Rydberg</t>
+          <t>Toni Berglund</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Hans Rydberg</t>
-        </is>
-      </c>
-      <c r="AY88" t="inlineStr">
-        <is>
-          <t>Länsstyrelsen i Örebro län, inventering</t>
-        </is>
-      </c>
+          <t>Toni Berglund</t>
+        </is>
+      </c>
+      <c r="AY88" t="inlineStr"/>
       <c r="AZ88" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/96368723</t>
+          <t>https://artportalen.se/Sighting/128198667</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>111858018</v>
+        <v>96368723</v>
       </c>
       <c r="B89" t="n">
-        <v>93223</v>
+        <v>90522</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10347,37 +10357,34 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>5448</v>
+        <v>4962</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Mjölsvärting</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Phellodon melaleucus</t>
+          <t>Lyophyllum semitale</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Sw. ex Fr.) P.Karst.</t>
+          <t>(Fr. : Fr.) Kühner</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
-      <c r="J89" t="inlineStr"/>
-      <c r="K89" t="inlineStr"/>
-      <c r="N89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
           <t>Blackstahyttan, Nrk</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>499512</v>
+        <v>499348</v>
       </c>
       <c r="R89" t="n">
-        <v>6580862</v>
+        <v>6580781</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10404,17 +10411,12 @@
       </c>
       <c r="Y89" t="inlineStr">
         <is>
-          <t>2023-09-02</t>
+          <t>2021-09-27</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
         <is>
-          <t>2023-09-02</t>
-        </is>
-      </c>
-      <c r="AC89" t="inlineStr">
-        <is>
-          <t>1 mycel. Rikligt med fruktkroppar.</t>
+          <t>2021-09-27</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10423,34 +10425,42 @@
       <c r="AE89" t="b">
         <v>0</v>
       </c>
-      <c r="AF89" t="inlineStr"/>
       <c r="AG89" t="b">
         <v>0</v>
+      </c>
+      <c r="AI89" t="inlineStr">
+        <is>
+          <t>barrskog</t>
+        </is>
       </c>
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Toni Berglund</t>
+          <t>Hans Rydberg</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Toni Berglund</t>
-        </is>
-      </c>
-      <c r="AY89" t="inlineStr"/>
+          <t>Hans Rydberg</t>
+        </is>
+      </c>
+      <c r="AY89" t="inlineStr">
+        <is>
+          <t>Länsstyrelsen i Örebro län, inventering</t>
+        </is>
+      </c>
       <c r="AZ89" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/111858018</t>
+          <t>https://artportalen.se/Sighting/96368723</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>136597260</v>
+        <v>111858018</v>
       </c>
       <c r="B90" t="n">
-        <v>93437</v>
+        <v>93223</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10475,31 +10485,23 @@
           <t>(Sw. ex Fr.) P.Karst.</t>
         </is>
       </c>
-      <c r="I90" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J90" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+      <c r="I90" t="inlineStr"/>
+      <c r="J90" t="inlineStr"/>
       <c r="K90" t="inlineStr"/>
       <c r="N90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Gretefallet, Gretefallet, Nrk</t>
+          <t>Blackstahyttan, Nrk</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>499513</v>
+        <v>499512</v>
       </c>
       <c r="R90" t="n">
-        <v>6580848</v>
+        <v>6580862</v>
       </c>
       <c r="S90" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -10523,12 +10525,17 @@
       </c>
       <c r="Y90" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2023-09-02</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2023-09-02</t>
+        </is>
+      </c>
+      <c r="AC90" t="inlineStr">
+        <is>
+          <t>1 mycel. Rikligt med fruktkroppar.</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10544,24 +10551,24 @@
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Erik Göthlin</t>
+          <t>Toni Berglund</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Erik Göthlin</t>
+          <t>Toni Berglund</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
       <c r="AZ90" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136597260</t>
+          <t>https://artportalen.se/Sighting/111858018</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>136609571</v>
+        <v>136597260</v>
       </c>
       <c r="B91" t="n">
         <v>93437</v>
@@ -10589,23 +10596,31 @@
           <t>(Sw. ex Fr.) P.Karst.</t>
         </is>
       </c>
-      <c r="I91" t="inlineStr"/>
-      <c r="J91" t="inlineStr"/>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="K91" t="inlineStr"/>
       <c r="N91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
-          <t>NV Blackstahyttan, Nrk</t>
+          <t>Gretefallet, Gretefallet, Nrk</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>499533</v>
+        <v>499513</v>
       </c>
       <c r="R91" t="n">
-        <v>6580838</v>
+        <v>6580848</v>
       </c>
       <c r="S91" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T91" t="inlineStr">
         <is>
@@ -10661,58 +10676,54 @@
       <c r="AY91" t="inlineStr"/>
       <c r="AZ91" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136609571</t>
+          <t>https://artportalen.se/Sighting/136597260</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>136103383</v>
+        <v>136609571</v>
       </c>
       <c r="B92" t="n">
-        <v>93438</v>
+        <v>93437</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>5449</v>
+        <v>5448</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Svart taggsvamp agg.</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Phellodon niger s.lat.</t>
-        </is>
-      </c>
-      <c r="H92" t="inlineStr"/>
-      <c r="I92" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J92" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>Phellodon melaleucus</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>(Sw. ex Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr"/>
+      <c r="J92" t="inlineStr"/>
       <c r="K92" t="inlineStr"/>
       <c r="N92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
-          <t>Blackstahyttan, Nrk</t>
+          <t>NV Blackstahyttan, Nrk</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>499508</v>
+        <v>499533</v>
       </c>
       <c r="R92" t="n">
-        <v>6580852</v>
+        <v>6580838</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10739,12 +10750,12 @@
       </c>
       <c r="Y92" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10757,70 +10768,72 @@
       <c r="AG92" t="b">
         <v>0</v>
       </c>
-      <c r="AH92" t="inlineStr">
-        <is>
-          <t>Blåbärsbarrskog</t>
-        </is>
-      </c>
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Michael Andersson</t>
+          <t>Erik Göthlin</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Michael Andersson, Toni Berglund</t>
+          <t>Erik Göthlin</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
       <c r="AZ92" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136103383</t>
+          <t>https://artportalen.se/Sighting/136609571</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>96368341</v>
+        <v>136103383</v>
       </c>
       <c r="B93" t="n">
-        <v>91409</v>
+        <v>93438</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>5741</v>
+        <v>5449</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Tjockfotad fingersvamp</t>
+          <t>Svart taggsvamp agg.</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Ramaria flavescens</t>
-        </is>
-      </c>
-      <c r="H93" t="inlineStr">
-        <is>
-          <t>(Schaeff.) R. H. Petersen</t>
-        </is>
-      </c>
-      <c r="I93" t="inlineStr"/>
+          <t>Phellodon niger s.lat.</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr"/>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr"/>
+      <c r="N93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
           <t>Blackstahyttan, Nrk</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>499465</v>
+        <v>499508</v>
       </c>
       <c r="R93" t="n">
-        <v>6580853</v>
+        <v>6580852</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10847,12 +10860,12 @@
       </c>
       <c r="Y93" t="inlineStr">
         <is>
-          <t>2021-09-27</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
         <is>
-          <t>2021-09-27</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10861,42 +10874,39 @@
       <c r="AE93" t="b">
         <v>0</v>
       </c>
+      <c r="AF93" t="inlineStr"/>
       <c r="AG93" t="b">
         <v>0</v>
       </c>
-      <c r="AI93" t="inlineStr">
-        <is>
-          <t>barrskog</t>
+      <c r="AH93" t="inlineStr">
+        <is>
+          <t>Blåbärsbarrskog</t>
         </is>
       </c>
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Hans Rydberg</t>
+          <t>Michael Andersson</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Hans Rydberg</t>
-        </is>
-      </c>
-      <c r="AY93" t="inlineStr">
-        <is>
-          <t>Länsstyrelsen i Örebro län, inventering</t>
-        </is>
-      </c>
+          <t>Michael Andersson, Toni Berglund</t>
+        </is>
+      </c>
+      <c r="AY93" t="inlineStr"/>
       <c r="AZ93" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/96368341</t>
+          <t>https://artportalen.se/Sighting/136103383</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>136103380</v>
+        <v>96368341</v>
       </c>
       <c r="B94" t="n">
-        <v>91592</v>
+        <v>91409</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10921,28 +10931,17 @@
           <t>(Schaeff.) R. H. Petersen</t>
         </is>
       </c>
-      <c r="I94" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J94" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K94" t="inlineStr"/>
-      <c r="N94" t="inlineStr"/>
+      <c r="I94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
           <t>Blackstahyttan, Nrk</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>499508</v>
+        <v>499465</v>
       </c>
       <c r="R94" t="n">
-        <v>6580852</v>
+        <v>6580853</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10969,12 +10968,12 @@
       </c>
       <c r="Y94" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2021-09-27</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2021-09-27</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10983,39 +10982,42 @@
       <c r="AE94" t="b">
         <v>0</v>
       </c>
-      <c r="AF94" t="inlineStr"/>
       <c r="AG94" t="b">
         <v>0</v>
       </c>
-      <c r="AH94" t="inlineStr">
-        <is>
-          <t>Blåbärsbarrskog</t>
+      <c r="AI94" t="inlineStr">
+        <is>
+          <t>barrskog</t>
         </is>
       </c>
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Michael Andersson</t>
+          <t>Hans Rydberg</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Michael Andersson, Toni Berglund</t>
-        </is>
-      </c>
-      <c r="AY94" t="inlineStr"/>
+          <t>Hans Rydberg</t>
+        </is>
+      </c>
+      <c r="AY94" t="inlineStr">
+        <is>
+          <t>Länsstyrelsen i Örebro län, inventering</t>
+        </is>
+      </c>
       <c r="AZ94" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136103380</t>
+          <t>https://artportalen.se/Sighting/96368341</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>111858050</v>
+        <v>136103380</v>
       </c>
       <c r="B95" t="n">
-        <v>91443</v>
+        <v>91592</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11023,25 +11025,33 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>5754</v>
+        <v>5741</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Gultoppig fingersvamp</t>
+          <t>Tjockfotad fingersvamp</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Ramaria testaceoflava</t>
+          <t>Ramaria flavescens</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Bres.) Corner</t>
-        </is>
-      </c>
-      <c r="I95" t="inlineStr"/>
-      <c r="J95" t="inlineStr"/>
+          <t>(Schaeff.) R. H. Petersen</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K95" t="inlineStr"/>
       <c r="N95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
@@ -11050,10 +11060,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>499481</v>
+        <v>499508</v>
       </c>
       <c r="R95" t="n">
-        <v>6580859</v>
+        <v>6580852</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -11080,12 +11090,12 @@
       </c>
       <c r="Y95" t="inlineStr">
         <is>
-          <t>2023-09-02</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
         <is>
-          <t>2023-09-02</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -11098,30 +11108,35 @@
       <c r="AG95" t="b">
         <v>0</v>
       </c>
+      <c r="AH95" t="inlineStr">
+        <is>
+          <t>Blåbärsbarrskog</t>
+        </is>
+      </c>
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>Toni Berglund</t>
+          <t>Michael Andersson</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Toni Berglund</t>
+          <t>Michael Andersson, Toni Berglund</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
       <c r="AZ95" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/111858050</t>
+          <t>https://artportalen.se/Sighting/136103380</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>88151498</v>
+        <v>111858050</v>
       </c>
       <c r="B96" t="n">
-        <v>93233</v>
+        <v>91443</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11129,37 +11144,40 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>5964</v>
+        <v>5754</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Gultoppig fingersvamp</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Ramaria testaceoflava</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Bres.) Corner</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
+      <c r="J96" t="inlineStr"/>
+      <c r="K96" t="inlineStr"/>
+      <c r="N96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
           <t>Blackstahyttan, Nrk</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>499398</v>
+        <v>499481</v>
       </c>
       <c r="R96" t="n">
-        <v>6580897</v>
+        <v>6580859</v>
       </c>
       <c r="S96" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T96" t="inlineStr">
         <is>
@@ -11183,12 +11201,12 @@
       </c>
       <c r="Y96" t="inlineStr">
         <is>
-          <t>2020-09-23</t>
+          <t>2023-09-02</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
         <is>
-          <t>2020-09-23</t>
+          <t>2023-09-02</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -11201,36 +11219,27 @@
       <c r="AG96" t="b">
         <v>0</v>
       </c>
-      <c r="AI96" t="inlineStr">
-        <is>
-          <t>gammal barrskog</t>
-        </is>
-      </c>
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>Hans Rydberg</t>
+          <t>Toni Berglund</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Hans Rydberg</t>
-        </is>
-      </c>
-      <c r="AY96" t="inlineStr">
-        <is>
-          <t>Länsstyrelsen i Örebro län, inventering</t>
-        </is>
-      </c>
+          <t>Toni Berglund</t>
+        </is>
+      </c>
+      <c r="AY96" t="inlineStr"/>
       <c r="AZ96" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/88151498</t>
+          <t>https://artportalen.se/Sighting/111858050</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>96195240</v>
+        <v>88151498</v>
       </c>
       <c r="B97" t="n">
         <v>93233</v>
@@ -11259,22 +11268,19 @@
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
-      <c r="J97" t="inlineStr"/>
-      <c r="K97" t="inlineStr"/>
-      <c r="N97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
-          <t>Alvars väg, Blackstahyttan, Nrk</t>
+          <t>Blackstahyttan, Nrk</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>499328</v>
+        <v>499398</v>
       </c>
       <c r="R97" t="n">
-        <v>6580771</v>
+        <v>6580897</v>
       </c>
       <c r="S97" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T97" t="inlineStr">
         <is>
@@ -11298,12 +11304,12 @@
       </c>
       <c r="Y97" t="inlineStr">
         <is>
-          <t>2021-09-19</t>
+          <t>2020-09-23</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
         <is>
-          <t>2021-09-19</t>
+          <t>2020-09-23</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -11318,30 +11324,34 @@
       </c>
       <c r="AI97" t="inlineStr">
         <is>
-          <t>gammal kalkbarrskog</t>
+          <t>gammal barrskog</t>
         </is>
       </c>
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Michael Andersson</t>
+          <t>Hans Rydberg</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Michael Andersson, Toni Berglund</t>
-        </is>
-      </c>
-      <c r="AY97" t="inlineStr"/>
+          <t>Hans Rydberg</t>
+        </is>
+      </c>
+      <c r="AY97" t="inlineStr">
+        <is>
+          <t>Länsstyrelsen i Örebro län, inventering</t>
+        </is>
+      </c>
       <c r="AZ97" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/96195240</t>
+          <t>https://artportalen.se/Sighting/88151498</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>96195935</v>
+        <v>96195240</v>
       </c>
       <c r="B98" t="n">
         <v>93233</v>
@@ -11369,16 +11379,8 @@
           <t>(L.) P.Karst.</t>
         </is>
       </c>
-      <c r="I98" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J98" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+      <c r="I98" t="inlineStr"/>
+      <c r="J98" t="inlineStr"/>
       <c r="K98" t="inlineStr"/>
       <c r="N98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
@@ -11387,10 +11389,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>499353</v>
+        <v>499328</v>
       </c>
       <c r="R98" t="n">
-        <v>6580961</v>
+        <v>6580771</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -11454,13 +11456,13 @@
       <c r="AY98" t="inlineStr"/>
       <c r="AZ98" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/96195935</t>
+          <t>https://artportalen.se/Sighting/96195240</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>96359793</v>
+        <v>96195935</v>
       </c>
       <c r="B99" t="n">
         <v>93233</v>
@@ -11488,8 +11490,16 @@
           <t>(L.) P.Karst.</t>
         </is>
       </c>
-      <c r="I99" t="inlineStr"/>
-      <c r="J99" t="inlineStr"/>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="K99" t="inlineStr"/>
       <c r="N99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
@@ -11498,10 +11508,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>499400</v>
+        <v>499353</v>
       </c>
       <c r="R99" t="n">
-        <v>6580907</v>
+        <v>6580961</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -11548,7 +11558,7 @@
       </c>
       <c r="AI99" t="inlineStr">
         <is>
-          <t>under gran i gammal kalkbarrskog</t>
+          <t>gammal kalkbarrskog</t>
         </is>
       </c>
       <c r="AT99" t="inlineStr"/>
@@ -11565,13 +11575,13 @@
       <c r="AY99" t="inlineStr"/>
       <c r="AZ99" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/96359793</t>
+          <t>https://artportalen.se/Sighting/96195935</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>111858029</v>
+        <v>96359793</v>
       </c>
       <c r="B100" t="n">
         <v>93233</v>
@@ -11605,14 +11615,14 @@
       <c r="N100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
-          <t>Blackstahyttan, Nrk</t>
+          <t>Alvars väg, Blackstahyttan, Nrk</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>499495</v>
+        <v>499400</v>
       </c>
       <c r="R100" t="n">
-        <v>6580849</v>
+        <v>6580907</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11639,12 +11649,12 @@
       </c>
       <c r="Y100" t="inlineStr">
         <is>
-          <t>2023-09-02</t>
+          <t>2021-09-19</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
         <is>
-          <t>2023-09-02</t>
+          <t>2021-09-19</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -11657,27 +11667,32 @@
       <c r="AG100" t="b">
         <v>0</v>
       </c>
+      <c r="AI100" t="inlineStr">
+        <is>
+          <t>under gran i gammal kalkbarrskog</t>
+        </is>
+      </c>
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Toni Berglund</t>
+          <t>Michael Andersson</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Toni Berglund</t>
+          <t>Michael Andersson, Toni Berglund</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
       <c r="AZ100" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/111858029</t>
+          <t>https://artportalen.se/Sighting/96359793</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>111858049</v>
+        <v>111858029</v>
       </c>
       <c r="B101" t="n">
         <v>93233</v>
@@ -11715,10 +11730,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>499481</v>
+        <v>499495</v>
       </c>
       <c r="R101" t="n">
-        <v>6580859</v>
+        <v>6580849</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11777,13 +11792,13 @@
       <c r="AY101" t="inlineStr"/>
       <c r="AZ101" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/111858049</t>
+          <t>https://artportalen.se/Sighting/111858029</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>128078655</v>
+        <v>111858049</v>
       </c>
       <c r="B102" t="n">
         <v>93233</v>
@@ -11812,19 +11827,22 @@
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
+      <c r="J102" t="inlineStr"/>
+      <c r="K102" t="inlineStr"/>
+      <c r="N102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
-          <t>Alvars väg, Nrk</t>
+          <t>Blackstahyttan, Nrk</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>499400</v>
+        <v>499481</v>
       </c>
       <c r="R102" t="n">
-        <v>6580831</v>
+        <v>6580859</v>
       </c>
       <c r="S102" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T102" t="inlineStr">
         <is>
@@ -11848,22 +11866,12 @@
       </c>
       <c r="Y102" t="inlineStr">
         <is>
-          <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="Z102" t="inlineStr">
-        <is>
-          <t>15:05</t>
+          <t>2023-09-02</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
         <is>
-          <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="AB102" t="inlineStr">
-        <is>
-          <t>15:05</t>
+          <t>2023-09-02</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -11872,30 +11880,31 @@
       <c r="AE102" t="b">
         <v>0</v>
       </c>
+      <c r="AF102" t="inlineStr"/>
       <c r="AG102" t="b">
         <v>0</v>
       </c>
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Anders Carlberg</t>
+          <t>Toni Berglund</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Toni Berglund, Anders Carlberg</t>
+          <t>Toni Berglund</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
       <c r="AZ102" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128078655</t>
+          <t>https://artportalen.se/Sighting/111858049</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>128078988</v>
+        <v>128078655</v>
       </c>
       <c r="B103" t="n">
         <v>93233</v>
@@ -11930,13 +11939,13 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>499401</v>
+        <v>499400</v>
       </c>
       <c r="R103" t="n">
-        <v>6580907</v>
+        <v>6580831</v>
       </c>
       <c r="S103" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T103" t="inlineStr">
         <is>
@@ -11965,7 +11974,7 @@
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
@@ -11975,7 +11984,7 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -11995,19 +12004,19 @@
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Anders Carlberg, Toni Berglund</t>
+          <t>Toni Berglund, Anders Carlberg</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
       <c r="AZ103" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128078988</t>
+          <t>https://artportalen.se/Sighting/128078655</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>128198622</v>
+        <v>128078988</v>
       </c>
       <c r="B104" t="n">
         <v>93233</v>
@@ -12036,19 +12045,16 @@
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
-      <c r="J104" t="inlineStr"/>
-      <c r="K104" t="inlineStr"/>
-      <c r="N104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
           <t>Alvars väg, Nrk</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>499524</v>
+        <v>499401</v>
       </c>
       <c r="R104" t="n">
-        <v>6580851</v>
+        <v>6580907</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -12075,12 +12081,22 @@
       </c>
       <c r="Y104" t="inlineStr">
         <is>
-          <t>2025-09-01</t>
+          <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="Z104" t="inlineStr">
+        <is>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
         <is>
-          <t>2025-09-01</t>
+          <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AB104" t="inlineStr">
+        <is>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -12089,31 +12105,30 @@
       <c r="AE104" t="b">
         <v>0</v>
       </c>
-      <c r="AF104" t="inlineStr"/>
       <c r="AG104" t="b">
         <v>0</v>
       </c>
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>Toni Berglund</t>
+          <t>Anders Carlberg</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Toni Berglund</t>
+          <t>Anders Carlberg, Toni Berglund</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
       <c r="AZ104" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128198622</t>
+          <t>https://artportalen.se/Sighting/128078988</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>128198682</v>
+        <v>128198622</v>
       </c>
       <c r="B105" t="n">
         <v>93233</v>
@@ -12151,10 +12166,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>499461</v>
+        <v>499524</v>
       </c>
       <c r="R105" t="n">
-        <v>6580859</v>
+        <v>6580851</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -12213,16 +12228,16 @@
       <c r="AY105" t="inlineStr"/>
       <c r="AZ105" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128198682</t>
+          <t>https://artportalen.se/Sighting/128198622</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>128391581</v>
+        <v>128198682</v>
       </c>
       <c r="B106" t="n">
-        <v>93307</v>
+        <v>93233</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12247,28 +12262,20 @@
           <t>(L.) P.Karst.</t>
         </is>
       </c>
-      <c r="I106" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J106" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+      <c r="I106" t="inlineStr"/>
+      <c r="J106" t="inlineStr"/>
       <c r="K106" t="inlineStr"/>
       <c r="N106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
-          <t>Blackstahyttan Alvars väg, Nrk</t>
+          <t>Alvars väg, Nrk</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>499378</v>
+        <v>499461</v>
       </c>
       <c r="R106" t="n">
-        <v>6580902</v>
+        <v>6580859</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -12295,12 +12302,12 @@
       </c>
       <c r="Y106" t="inlineStr">
         <is>
-          <t>2025-09-12</t>
+          <t>2025-09-01</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
         <is>
-          <t>2025-09-12</t>
+          <t>2025-09-01</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -12316,27 +12323,27 @@
       <c r="AT106" t="inlineStr"/>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>Lotta Sörman</t>
+          <t>Toni Berglund</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>Lotta Sörman</t>
+          <t>Toni Berglund</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
       <c r="AZ106" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128391581</t>
+          <t>https://artportalen.se/Sighting/128198682</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>136103331</v>
+        <v>128391581</v>
       </c>
       <c r="B107" t="n">
-        <v>93445</v>
+        <v>93307</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12363,26 +12370,26 @@
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>mycel</t>
         </is>
       </c>
       <c r="K107" t="inlineStr"/>
       <c r="N107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
-          <t>Blackstahyttan, Nrk</t>
+          <t>Blackstahyttan Alvars väg, Nrk</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>499508</v>
+        <v>499378</v>
       </c>
       <c r="R107" t="n">
-        <v>6580852</v>
+        <v>6580902</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -12409,12 +12416,12 @@
       </c>
       <c r="Y107" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -12427,40 +12434,30 @@
       <c r="AG107" t="b">
         <v>0</v>
       </c>
-      <c r="AH107" t="inlineStr">
-        <is>
-          <t>Blåbärsbarrskog</t>
-        </is>
-      </c>
-      <c r="AI107" t="inlineStr">
-        <is>
-          <t>på stig</t>
-        </is>
-      </c>
       <c r="AT107" t="inlineStr"/>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>Michael Andersson</t>
+          <t>Lotta Sörman</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>Michael Andersson, Toni Berglund</t>
+          <t>Lotta Sörman</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
       <c r="AZ107" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136103331</t>
+          <t>https://artportalen.se/Sighting/128391581</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>136597853</v>
+        <v>136103331</v>
       </c>
       <c r="B108" t="n">
-        <v>93447</v>
+        <v>93445</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12485,20 +12482,28 @@
           <t>(L.) P.Karst.</t>
         </is>
       </c>
-      <c r="I108" t="inlineStr"/>
-      <c r="J108" t="inlineStr"/>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J108" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K108" t="inlineStr"/>
       <c r="N108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
-          <t>Västantorp, Västantorp, Nrk</t>
+          <t>Blackstahyttan, Nrk</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>499477</v>
+        <v>499508</v>
       </c>
       <c r="R108" t="n">
-        <v>6580844</v>
+        <v>6580852</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -12525,12 +12530,12 @@
       </c>
       <c r="Y108" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -12543,52 +12548,62 @@
       <c r="AG108" t="b">
         <v>0</v>
       </c>
+      <c r="AH108" t="inlineStr">
+        <is>
+          <t>Blåbärsbarrskog</t>
+        </is>
+      </c>
+      <c r="AI108" t="inlineStr">
+        <is>
+          <t>på stig</t>
+        </is>
+      </c>
       <c r="AT108" t="inlineStr"/>
       <c r="AW108" t="inlineStr">
         <is>
-          <t>Erik Göthlin</t>
+          <t>Michael Andersson</t>
         </is>
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>Erik Göthlin</t>
+          <t>Michael Andersson, Toni Berglund</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
       <c r="AZ108" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136597853</t>
+          <t>https://artportalen.se/Sighting/136103331</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>111858070</v>
+        <v>136597853</v>
       </c>
       <c r="B109" t="n">
-        <v>90681</v>
+        <v>93447</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>6268</v>
+        <v>5964</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Rökmusseron</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Tricholoma fucatum</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Kumm.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -12597,14 +12612,14 @@
       <c r="N109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
-          <t>Blackstahyttan, Nrk</t>
+          <t>Västantorp, Västantorp, Nrk</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>499456</v>
+        <v>499477</v>
       </c>
       <c r="R109" t="n">
-        <v>6580855</v>
+        <v>6580844</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -12631,12 +12646,12 @@
       </c>
       <c r="Y109" t="inlineStr">
         <is>
-          <t>2023-09-02</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="AA109" t="inlineStr">
         <is>
-          <t>2023-09-02</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -12652,24 +12667,24 @@
       <c r="AT109" t="inlineStr"/>
       <c r="AW109" t="inlineStr">
         <is>
-          <t>Toni Berglund</t>
+          <t>Erik Göthlin</t>
         </is>
       </c>
       <c r="AX109" t="inlineStr">
         <is>
-          <t>Toni Berglund</t>
+          <t>Erik Göthlin</t>
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
       <c r="AZ109" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/111858070</t>
+          <t>https://artportalen.se/Sighting/136597853</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>128198683</v>
+        <v>111858070</v>
       </c>
       <c r="B110" t="n">
         <v>90681</v>
@@ -12703,14 +12718,14 @@
       <c r="N110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
-          <t>Alvars väg, Nrk</t>
+          <t>Blackstahyttan, Nrk</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>499461</v>
+        <v>499456</v>
       </c>
       <c r="R110" t="n">
-        <v>6580859</v>
+        <v>6580855</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -12737,12 +12752,12 @@
       </c>
       <c r="Y110" t="inlineStr">
         <is>
-          <t>2025-09-01</t>
+          <t>2023-09-02</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
         <is>
-          <t>2025-09-01</t>
+          <t>2023-09-02</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -12769,16 +12784,16 @@
       <c r="AY110" t="inlineStr"/>
       <c r="AZ110" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128198683</t>
+          <t>https://artportalen.se/Sighting/111858070</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>136106499</v>
+        <v>128198683</v>
       </c>
       <c r="B111" t="n">
-        <v>75449</v>
+        <v>90681</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -12786,41 +12801,37 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>6427</v>
+        <v>6268</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Glansfläck</t>
+          <t>Rökmusseron</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Diarthonis spadicea</t>
+          <t>Tricholoma fucatum</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Leight.) Frisch &amp; al.</t>
+          <t>(Fr.:Fr.) P. Kumm.</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
       <c r="J111" t="inlineStr"/>
-      <c r="K111" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K111" t="inlineStr"/>
       <c r="N111" t="inlineStr"/>
       <c r="P111" t="inlineStr">
         <is>
-          <t>Blackstahyttan, Nrk</t>
+          <t>Alvars väg, Nrk</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>499436</v>
+        <v>499461</v>
       </c>
       <c r="R111" t="n">
-        <v>6580862</v>
+        <v>6580859</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -12847,12 +12858,12 @@
       </c>
       <c r="Y111" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2025-09-01</t>
         </is>
       </c>
       <c r="AA111" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2025-09-01</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -12865,55 +12876,27 @@
       <c r="AG111" t="b">
         <v>0</v>
       </c>
-      <c r="AH111" t="inlineStr">
-        <is>
-          <t>Barrsumpskog</t>
-        </is>
-      </c>
-      <c r="AJ111" t="inlineStr">
-        <is>
-          <t>klibbal</t>
-        </is>
-      </c>
-      <c r="AK111" t="inlineStr">
-        <is>
-          <t>Alnus glutinosa</t>
-        </is>
-      </c>
-      <c r="AM111" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AN111" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO111" t="inlineStr">
-        <is>
-          <t>1 substratenheter # Bark on living woody plant # Alnus glutinosa</t>
-        </is>
-      </c>
       <c r="AT111" t="inlineStr"/>
       <c r="AW111" t="inlineStr">
         <is>
-          <t>Michael Andersson</t>
+          <t>Toni Berglund</t>
         </is>
       </c>
       <c r="AX111" t="inlineStr">
         <is>
-          <t>Michael Andersson, Toni Berglund</t>
+          <t>Toni Berglund</t>
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
       <c r="AZ111" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136106499</t>
+          <t>https://artportalen.se/Sighting/128198683</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>136107535</v>
+        <v>136106499</v>
       </c>
       <c r="B112" t="n">
         <v>75449</v>
@@ -12955,10 +12938,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>499462</v>
+        <v>499436</v>
       </c>
       <c r="R112" t="n">
-        <v>6580861</v>
+        <v>6580862</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -13008,11 +12991,6 @@
           <t>Barrsumpskog</t>
         </is>
       </c>
-      <c r="AI112" t="inlineStr">
-        <is>
-          <t>bäckstrand</t>
-        </is>
-      </c>
       <c r="AJ112" t="inlineStr">
         <is>
           <t>klibbal</t>
@@ -13050,13 +13028,13 @@
       <c r="AY112" t="inlineStr"/>
       <c r="AZ112" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136107535</t>
+          <t>https://artportalen.se/Sighting/136106499</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>136107679</v>
+        <v>136107535</v>
       </c>
       <c r="B113" t="n">
         <v>75449</v>
@@ -13086,7 +13064,11 @@
       </c>
       <c r="I113" t="inlineStr"/>
       <c r="J113" t="inlineStr"/>
-      <c r="K113" t="inlineStr"/>
+      <c r="K113" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N113" t="inlineStr"/>
       <c r="P113" t="inlineStr">
         <is>
@@ -13094,10 +13076,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>499449</v>
+        <v>499462</v>
       </c>
       <c r="R113" t="n">
-        <v>6580856</v>
+        <v>6580861</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -13138,12 +13120,18 @@
       <c r="AE113" t="b">
         <v>0</v>
       </c>
+      <c r="AF113" t="inlineStr"/>
       <c r="AG113" t="b">
         <v>0</v>
       </c>
       <c r="AH113" t="inlineStr">
         <is>
           <t>Barrsumpskog</t>
+        </is>
+      </c>
+      <c r="AI113" t="inlineStr">
+        <is>
+          <t>bäckstrand</t>
         </is>
       </c>
       <c r="AJ113" t="inlineStr">
@@ -13177,22 +13165,22 @@
       </c>
       <c r="AX113" t="inlineStr">
         <is>
-          <t>Michael Andersson</t>
+          <t>Michael Andersson, Toni Berglund</t>
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
       <c r="AZ113" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136107679</t>
+          <t>https://artportalen.se/Sighting/136107535</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>12692</v>
+        <v>136107679</v>
       </c>
       <c r="B114" t="n">
-        <v>56614</v>
+        <v>75449</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -13200,48 +13188,37 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>100084</v>
+        <v>6427</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Hasselmus</t>
+          <t>Glansfläck</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Muscardinus avellanarius</t>
+          <t>Diarthonis spadicea</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I114" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K114" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L114" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+          <t>(Leight.) Frisch &amp; al.</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr"/>
+      <c r="J114" t="inlineStr"/>
+      <c r="K114" t="inlineStr"/>
+      <c r="N114" t="inlineStr"/>
       <c r="P114" t="inlineStr">
         <is>
-          <t>Skansberget, Kilsbergen, Nrk</t>
+          <t>Blackstahyttan, Nrk</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>499263</v>
+        <v>499449</v>
       </c>
       <c r="R114" t="n">
-        <v>6580923</v>
+        <v>6580856</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -13268,17 +13245,12 @@
       </c>
       <c r="Y114" t="inlineStr">
         <is>
-          <t>2007-10-07</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="AA114" t="inlineStr">
         <is>
-          <t>2007-10-07</t>
-        </is>
-      </c>
-      <c r="AC114" t="inlineStr">
-        <is>
-          <t>Lövrik sydostsluttning av Skansberget på blockrik mark, som här och var skapar naturliga gläntor. Vid fyndplatsen dominerar björk och rönn. Ett hanbo i liten enbuske, som står i skydd av högvuxen Calamagrostis.</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -13289,31 +13261,59 @@
       </c>
       <c r="AG114" t="b">
         <v>0</v>
+      </c>
+      <c r="AH114" t="inlineStr">
+        <is>
+          <t>Barrsumpskog</t>
+        </is>
+      </c>
+      <c r="AJ114" t="inlineStr">
+        <is>
+          <t>klibbal</t>
+        </is>
+      </c>
+      <c r="AK114" t="inlineStr">
+        <is>
+          <t>Alnus glutinosa</t>
+        </is>
+      </c>
+      <c r="AM114" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AN114" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO114" t="inlineStr">
+        <is>
+          <t>1 substratenheter # Bark on living woody plant # Alnus glutinosa</t>
+        </is>
       </c>
       <c r="AT114" t="inlineStr"/>
       <c r="AW114" t="inlineStr">
         <is>
-          <t>Boris Berglund</t>
+          <t>Michael Andersson</t>
         </is>
       </c>
       <c r="AX114" t="inlineStr">
         <is>
-          <t>Boris Berglund</t>
+          <t>Michael Andersson</t>
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
       <c r="AZ114" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/12692</t>
+          <t>https://artportalen.se/Sighting/136107679</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>96601406</v>
+        <v>12692</v>
       </c>
       <c r="B115" t="n">
-        <v>57141</v>
+        <v>56614</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -13321,21 +13321,21 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>100138</v>
+        <v>100084</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Hasselmus</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Muscardinus avellanarius</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
@@ -13343,27 +13343,29 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K115" t="inlineStr"/>
+      <c r="K115" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="L115" t="inlineStr">
         <is>
           <t>hane</t>
         </is>
       </c>
-      <c r="M115" t="inlineStr"/>
-      <c r="N115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
         <is>
-          <t>Blackstahyttan, Nrk</t>
+          <t>Skansberget, Kilsbergen, Nrk</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>499424</v>
+        <v>499263</v>
       </c>
       <c r="R115" t="n">
-        <v>6580779</v>
+        <v>6580923</v>
       </c>
       <c r="S115" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T115" t="inlineStr">
         <is>
@@ -13387,12 +13389,17 @@
       </c>
       <c r="Y115" t="inlineStr">
         <is>
-          <t>2021-10-09</t>
+          <t>2007-10-07</t>
         </is>
       </c>
       <c r="AA115" t="inlineStr">
         <is>
-          <t>2021-10-09</t>
+          <t>2007-10-07</t>
+        </is>
+      </c>
+      <c r="AC115" t="inlineStr">
+        <is>
+          <t>Lövrik sydostsluttning av Skansberget på blockrik mark, som här och var skapar naturliga gläntor. Vid fyndplatsen dominerar björk och rönn. Ett hanbo i liten enbuske, som står i skydd av högvuxen Calamagrostis.</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -13407,27 +13414,27 @@
       <c r="AT115" t="inlineStr"/>
       <c r="AW115" t="inlineStr">
         <is>
-          <t>Toni Berglund</t>
+          <t>Boris Berglund</t>
         </is>
       </c>
       <c r="AX115" t="inlineStr">
         <is>
-          <t>Toni Berglund</t>
+          <t>Boris Berglund</t>
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
       <c r="AZ115" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/96601406</t>
+          <t>https://artportalen.se/Sighting/12692</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>136107711</v>
+        <v>96601406</v>
       </c>
       <c r="B116" t="n">
-        <v>5182</v>
+        <v>57141</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -13435,54 +13442,49 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>100526</v>
+        <v>100138</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I116" t="inlineStr"/>
-      <c r="J116" t="inlineStr"/>
-      <c r="K116" t="inlineStr">
-        <is>
-          <t>larv/nymf</t>
-        </is>
-      </c>
-      <c r="L116" t="inlineStr"/>
-      <c r="M116" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N116" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K116" t="inlineStr"/>
+      <c r="L116" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M116" t="inlineStr"/>
+      <c r="N116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
           <t>Blackstahyttan, Nrk</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>499449</v>
+        <v>499424</v>
       </c>
       <c r="R116" t="n">
-        <v>6580856</v>
+        <v>6580779</v>
       </c>
       <c r="S116" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T116" t="inlineStr">
         <is>
@@ -13506,12 +13508,12 @@
       </c>
       <c r="Y116" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2021-10-09</t>
         </is>
       </c>
       <c r="AA116" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2021-10-09</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -13520,59 +13522,33 @@
       <c r="AE116" t="b">
         <v>0</v>
       </c>
-      <c r="AF116" t="inlineStr"/>
       <c r="AG116" t="b">
         <v>0</v>
-      </c>
-      <c r="AH116" t="inlineStr">
-        <is>
-          <t>Barrsumpskog</t>
-        </is>
-      </c>
-      <c r="AJ116" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK116" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM116" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, utan markontakt</t>
-        </is>
-      </c>
-      <c r="AO116" t="inlineStr">
-        <is>
-          <t>Horizontal, dead without ground contact # grov granlåga med kvarsittande bark # Picea abies</t>
-        </is>
       </c>
       <c r="AT116" t="inlineStr"/>
       <c r="AW116" t="inlineStr">
         <is>
-          <t>Michael Andersson</t>
+          <t>Toni Berglund</t>
         </is>
       </c>
       <c r="AX116" t="inlineStr">
         <is>
-          <t>Michael Andersson</t>
+          <t>Toni Berglund</t>
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
       <c r="AZ116" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136107711</t>
+          <t>https://artportalen.se/Sighting/96601406</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>128090297</v>
+        <v>136107711</v>
       </c>
       <c r="B117" t="n">
-        <v>58327</v>
+        <v>5182</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -13580,49 +13556,54 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>103015</v>
+        <v>100526</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I117" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K117" t="inlineStr"/>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr"/>
+      <c r="J117" t="inlineStr"/>
+      <c r="K117" t="inlineStr">
+        <is>
+          <t>larv/nymf</t>
+        </is>
+      </c>
       <c r="L117" t="inlineStr"/>
       <c r="M117" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N117" t="inlineStr"/>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N117" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P117" t="inlineStr">
         <is>
-          <t>Alvars väg, Nrk</t>
+          <t>Blackstahyttan, Nrk</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>499400</v>
+        <v>499449</v>
       </c>
       <c r="R117" t="n">
-        <v>6580831</v>
+        <v>6580856</v>
       </c>
       <c r="S117" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T117" t="inlineStr">
         <is>
@@ -13646,22 +13627,12 @@
       </c>
       <c r="Y117" t="inlineStr">
         <is>
-          <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="Z117" t="inlineStr">
-        <is>
-          <t>16:30</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="AA117" t="inlineStr">
         <is>
-          <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="AB117" t="inlineStr">
-        <is>
-          <t>16:30</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -13670,33 +13641,59 @@
       <c r="AE117" t="b">
         <v>0</v>
       </c>
+      <c r="AF117" t="inlineStr"/>
       <c r="AG117" t="b">
         <v>0</v>
+      </c>
+      <c r="AH117" t="inlineStr">
+        <is>
+          <t>Barrsumpskog</t>
+        </is>
+      </c>
+      <c r="AJ117" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK117" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM117" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, utan markontakt</t>
+        </is>
+      </c>
+      <c r="AO117" t="inlineStr">
+        <is>
+          <t>Horizontal, dead without ground contact # grov granlåga med kvarsittande bark # Picea abies</t>
+        </is>
       </c>
       <c r="AT117" t="inlineStr"/>
       <c r="AW117" t="inlineStr">
         <is>
-          <t>Anders Carlberg</t>
+          <t>Michael Andersson</t>
         </is>
       </c>
       <c r="AX117" t="inlineStr">
         <is>
-          <t>Anders Carlberg, Toni Berglund</t>
+          <t>Michael Andersson</t>
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
       <c r="AZ117" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128090297</t>
+          <t>https://artportalen.se/Sighting/136107711</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>136106670</v>
+        <v>128090297</v>
       </c>
       <c r="B118" t="n">
-        <v>98372</v>
+        <v>58327</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -13704,41 +13701,49 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>219815</v>
+        <v>103015</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Ekbräken</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Gymnocarpium dryopteris</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(L.) Newman</t>
-        </is>
-      </c>
-      <c r="I118" t="inlineStr"/>
-      <c r="J118" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K118" t="inlineStr"/>
       <c r="L118" t="inlineStr"/>
+      <c r="M118" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N118" t="inlineStr"/>
       <c r="P118" t="inlineStr">
         <is>
-          <t>Blackstahyttan, Nrk</t>
+          <t>Alvars väg, Nrk</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>499401</v>
+        <v>499400</v>
       </c>
       <c r="R118" t="n">
-        <v>6580883</v>
+        <v>6580831</v>
       </c>
       <c r="S118" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T118" t="inlineStr">
         <is>
@@ -13762,12 +13767,22 @@
       </c>
       <c r="Y118" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="Z118" t="inlineStr">
+        <is>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AA118" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AB118" t="inlineStr">
+        <is>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -13776,39 +13791,33 @@
       <c r="AE118" t="b">
         <v>0</v>
       </c>
-      <c r="AF118" t="inlineStr"/>
       <c r="AG118" t="b">
         <v>0</v>
-      </c>
-      <c r="AH118" t="inlineStr">
-        <is>
-          <t>Barrsumpskog</t>
-        </is>
       </c>
       <c r="AT118" t="inlineStr"/>
       <c r="AW118" t="inlineStr">
         <is>
-          <t>Michael Andersson</t>
+          <t>Anders Carlberg</t>
         </is>
       </c>
       <c r="AX118" t="inlineStr">
         <is>
-          <t>Michael Andersson, Toni Berglund</t>
+          <t>Anders Carlberg, Toni Berglund</t>
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
       <c r="AZ118" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136106670</t>
+          <t>https://artportalen.se/Sighting/128090297</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>136106545</v>
+        <v>136106670</v>
       </c>
       <c r="B119" t="n">
-        <v>108446</v>
+        <v>98372</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -13816,30 +13825,26 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>220102</v>
+        <v>219815</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Kärrfibbla</t>
+          <t>Ekbräken</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Crepis paludosa</t>
+          <t>Gymnocarpium dryopteris</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(L.) Moench</t>
+          <t>(L.) Newman</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
       <c r="J119" t="inlineStr"/>
-      <c r="K119" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+      <c r="K119" t="inlineStr"/>
       <c r="L119" t="inlineStr"/>
       <c r="N119" t="inlineStr"/>
       <c r="P119" t="inlineStr">
@@ -13848,10 +13853,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>499412</v>
+        <v>499401</v>
       </c>
       <c r="R119" t="n">
-        <v>6580878</v>
+        <v>6580883</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -13915,13 +13920,13 @@
       <c r="AY119" t="inlineStr"/>
       <c r="AZ119" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136106545</t>
+          <t>https://artportalen.se/Sighting/136106670</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>136106660</v>
+        <v>136106545</v>
       </c>
       <c r="B120" t="n">
         <v>108446</v>
@@ -13953,7 +13958,7 @@
       <c r="J120" t="inlineStr"/>
       <c r="K120" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="L120" t="inlineStr"/>
@@ -13964,10 +13969,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>499401</v>
+        <v>499412</v>
       </c>
       <c r="R120" t="n">
-        <v>6580883</v>
+        <v>6580878</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -14031,54 +14036,62 @@
       <c r="AY120" t="inlineStr"/>
       <c r="AZ120" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136106660</t>
+          <t>https://artportalen.se/Sighting/136106545</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>87880231</v>
+        <v>136106660</v>
       </c>
       <c r="B121" t="n">
-        <v>109815</v>
+        <v>108446</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>220204</v>
+        <v>220102</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Slåtterfibbla</t>
+          <t>Kärrfibbla</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Hypochaeris maculata</t>
+          <t>Crepis paludosa</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Moench</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
+      <c r="J121" t="inlineStr"/>
+      <c r="K121" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L121" t="inlineStr"/>
+      <c r="N121" t="inlineStr"/>
       <c r="P121" t="inlineStr">
         <is>
-          <t>Blackstahyttan, skog V om, Nrk</t>
+          <t>Blackstahyttan, Nrk</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>499536</v>
+        <v>499401</v>
       </c>
       <c r="R121" t="n">
-        <v>6580741</v>
+        <v>6580883</v>
       </c>
       <c r="S121" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T121" t="inlineStr">
         <is>
@@ -14102,12 +14115,12 @@
       </c>
       <c r="Y121" t="inlineStr">
         <is>
-          <t>2020-09-07</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="AA121" t="inlineStr">
         <is>
-          <t>2020-09-07</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -14116,59 +14129,56 @@
       <c r="AE121" t="b">
         <v>0</v>
       </c>
+      <c r="AF121" t="inlineStr"/>
       <c r="AG121" t="b">
         <v>0</v>
       </c>
-      <c r="AI121" t="inlineStr">
-        <is>
-          <t>kalkrik barrskog</t>
+      <c r="AH121" t="inlineStr">
+        <is>
+          <t>Barrsumpskog</t>
         </is>
       </c>
       <c r="AT121" t="inlineStr"/>
       <c r="AW121" t="inlineStr">
         <is>
-          <t>Hans Rydberg</t>
+          <t>Michael Andersson</t>
         </is>
       </c>
       <c r="AX121" t="inlineStr">
         <is>
-          <t>Hans Rydberg</t>
-        </is>
-      </c>
-      <c r="AY121" t="inlineStr">
-        <is>
-          <t>Länsstyrelsen i Örebro län, inventering</t>
-        </is>
-      </c>
+          <t>Michael Andersson, Toni Berglund</t>
+        </is>
+      </c>
+      <c r="AY121" t="inlineStr"/>
       <c r="AZ121" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/87880231</t>
+          <t>https://artportalen.se/Sighting/136106660</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>136103300</v>
+        <v>87880231</v>
       </c>
       <c r="B122" t="n">
-        <v>107062</v>
+        <v>109815</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>220785</v>
+        <v>220204</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Slåtterfibbla</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Hypochaeris maculata</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
@@ -14177,23 +14187,19 @@
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
-      <c r="J122" t="inlineStr"/>
-      <c r="K122" t="inlineStr"/>
-      <c r="L122" t="inlineStr"/>
-      <c r="N122" t="inlineStr"/>
       <c r="P122" t="inlineStr">
         <is>
-          <t>Gretefallet, Blackstahyttan, Nrk</t>
+          <t>Blackstahyttan, skog V om, Nrk</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>499594</v>
+        <v>499536</v>
       </c>
       <c r="R122" t="n">
-        <v>6580771</v>
+        <v>6580741</v>
       </c>
       <c r="S122" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T122" t="inlineStr">
         <is>
@@ -14217,12 +14223,12 @@
       </c>
       <c r="Y122" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2020-09-07</t>
         </is>
       </c>
       <c r="AA122" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2020-09-07</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -14231,61 +14237,64 @@
       <c r="AE122" t="b">
         <v>0</v>
       </c>
-      <c r="AF122" t="inlineStr"/>
       <c r="AG122" t="b">
         <v>0</v>
       </c>
-      <c r="AH122" t="inlineStr">
-        <is>
-          <t>Blandskog</t>
+      <c r="AI122" t="inlineStr">
+        <is>
+          <t>kalkrik barrskog</t>
         </is>
       </c>
       <c r="AT122" t="inlineStr"/>
       <c r="AW122" t="inlineStr">
         <is>
-          <t>Michael Andersson</t>
+          <t>Hans Rydberg</t>
         </is>
       </c>
       <c r="AX122" t="inlineStr">
         <is>
-          <t>Michael Andersson, Toni Berglund</t>
-        </is>
-      </c>
-      <c r="AY122" t="inlineStr"/>
+          <t>Hans Rydberg</t>
+        </is>
+      </c>
+      <c r="AY122" t="inlineStr">
+        <is>
+          <t>Länsstyrelsen i Örebro län, inventering</t>
+        </is>
+      </c>
       <c r="AZ122" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136103300</t>
+          <t>https://artportalen.se/Sighting/87880231</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>136106552</v>
+        <v>136103300</v>
       </c>
       <c r="B123" t="n">
-        <v>106367</v>
+        <v>107062</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>221154</v>
+        <v>220785</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Skogsstjärna</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Lysimachia europaea</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(L.) U. Manns &amp; Anderb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -14295,14 +14304,14 @@
       <c r="N123" t="inlineStr"/>
       <c r="P123" t="inlineStr">
         <is>
-          <t>Blackstahyttan, Nrk</t>
+          <t>Gretefallet, Blackstahyttan, Nrk</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>499412</v>
+        <v>499594</v>
       </c>
       <c r="R123" t="n">
-        <v>6580878</v>
+        <v>6580771</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -14349,7 +14358,7 @@
       </c>
       <c r="AH123" t="inlineStr">
         <is>
-          <t>Barrsumpskog</t>
+          <t>Blandskog</t>
         </is>
       </c>
       <c r="AT123" t="inlineStr"/>
@@ -14366,13 +14375,13 @@
       <c r="AY123" t="inlineStr"/>
       <c r="AZ123" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136106552</t>
+          <t>https://artportalen.se/Sighting/136103300</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>136106673</v>
+        <v>136106552</v>
       </c>
       <c r="B124" t="n">
         <v>106367</v>
@@ -14411,10 +14420,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>499401</v>
+        <v>499412</v>
       </c>
       <c r="R124" t="n">
-        <v>6580883</v>
+        <v>6580878</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -14478,13 +14487,13 @@
       <c r="AY124" t="inlineStr"/>
       <c r="AZ124" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136106673</t>
+          <t>https://artportalen.se/Sighting/136106552</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>136107698</v>
+        <v>136106673</v>
       </c>
       <c r="B125" t="n">
         <v>106367</v>
@@ -14523,10 +14532,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>499449</v>
+        <v>499401</v>
       </c>
       <c r="R125" t="n">
-        <v>6580856</v>
+        <v>6580883</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -14590,16 +14599,16 @@
       <c r="AY125" t="inlineStr"/>
       <c r="AZ125" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136107698</t>
+          <t>https://artportalen.se/Sighting/136106673</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>131900407</v>
+        <v>136107698</v>
       </c>
       <c r="B126" t="n">
-        <v>106358</v>
+        <v>106367</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -14607,30 +14616,26 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>221157</v>
+        <v>221154</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Blåbär</t>
+          <t>Skogsstjärna</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Vaccinium myrtillus</t>
+          <t>Lysimachia europaea</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) U. Manns &amp; Anderb.</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
       <c r="J126" t="inlineStr"/>
-      <c r="K126" t="inlineStr">
-        <is>
-          <t>vilstadium</t>
-        </is>
-      </c>
+      <c r="K126" t="inlineStr"/>
       <c r="L126" t="inlineStr"/>
       <c r="N126" t="inlineStr"/>
       <c r="P126" t="inlineStr">
@@ -14639,10 +14644,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>499349</v>
+        <v>499449</v>
       </c>
       <c r="R126" t="n">
-        <v>6580769</v>
+        <v>6580856</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -14669,12 +14674,12 @@
       </c>
       <c r="Y126" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="AA126" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="AD126" t="b">
@@ -14689,7 +14694,7 @@
       </c>
       <c r="AH126" t="inlineStr">
         <is>
-          <t>Blåbärsbarrskog</t>
+          <t>Barrsumpskog</t>
         </is>
       </c>
       <c r="AT126" t="inlineStr"/>
@@ -14700,22 +14705,22 @@
       </c>
       <c r="AX126" t="inlineStr">
         <is>
-          <t>Michael Andersson</t>
+          <t>Michael Andersson, Toni Berglund</t>
         </is>
       </c>
       <c r="AY126" t="inlineStr"/>
       <c r="AZ126" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131900407</t>
+          <t>https://artportalen.se/Sighting/136107698</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>136103391</v>
+        <v>131900407</v>
       </c>
       <c r="B127" t="n">
-        <v>106526</v>
+        <v>106358</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -14744,7 +14749,7 @@
       <c r="J127" t="inlineStr"/>
       <c r="K127" t="inlineStr">
         <is>
-          <t>i frukt</t>
+          <t>vilstadium</t>
         </is>
       </c>
       <c r="L127" t="inlineStr"/>
@@ -14755,10 +14760,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>499508</v>
+        <v>499349</v>
       </c>
       <c r="R127" t="n">
-        <v>6580852</v>
+        <v>6580769</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -14785,12 +14790,12 @@
       </c>
       <c r="Y127" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="AA127" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="AD127" t="b">
@@ -14816,19 +14821,19 @@
       </c>
       <c r="AX127" t="inlineStr">
         <is>
-          <t>Michael Andersson, Toni Berglund</t>
+          <t>Michael Andersson</t>
         </is>
       </c>
       <c r="AY127" t="inlineStr"/>
       <c r="AZ127" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136103391</t>
+          <t>https://artportalen.se/Sighting/131900407</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>136107643</v>
+        <v>136103391</v>
       </c>
       <c r="B128" t="n">
         <v>106526</v>
@@ -14858,7 +14863,11 @@
       </c>
       <c r="I128" t="inlineStr"/>
       <c r="J128" t="inlineStr"/>
-      <c r="K128" t="inlineStr"/>
+      <c r="K128" t="inlineStr">
+        <is>
+          <t>i frukt</t>
+        </is>
+      </c>
       <c r="L128" t="inlineStr"/>
       <c r="N128" t="inlineStr"/>
       <c r="P128" t="inlineStr">
@@ -14867,10 +14876,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>499449</v>
+        <v>499508</v>
       </c>
       <c r="R128" t="n">
-        <v>6580856</v>
+        <v>6580852</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -14917,7 +14926,7 @@
       </c>
       <c r="AH128" t="inlineStr">
         <is>
-          <t>Barrsumpskog</t>
+          <t>Blåbärsbarrskog</t>
         </is>
       </c>
       <c r="AT128" t="inlineStr"/>
@@ -14934,33 +14943,33 @@
       <c r="AY128" t="inlineStr"/>
       <c r="AZ128" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136107643</t>
+          <t>https://artportalen.se/Sighting/136103391</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>136103972</v>
+        <v>136107643</v>
       </c>
       <c r="B129" t="n">
-        <v>100113</v>
+        <v>106526</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>222361</v>
+        <v>221157</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Loppstarr</t>
+          <t>Blåbär</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Carex pulicaris</t>
+          <t>Vaccinium myrtillus</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
@@ -14970,11 +14979,7 @@
       </c>
       <c r="I129" t="inlineStr"/>
       <c r="J129" t="inlineStr"/>
-      <c r="K129" t="inlineStr">
-        <is>
-          <t>i frukt</t>
-        </is>
-      </c>
+      <c r="K129" t="inlineStr"/>
       <c r="L129" t="inlineStr"/>
       <c r="N129" t="inlineStr"/>
       <c r="P129" t="inlineStr">
@@ -14983,10 +14988,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>499433</v>
+        <v>499449</v>
       </c>
       <c r="R129" t="n">
-        <v>6580754</v>
+        <v>6580856</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -15033,12 +15038,7 @@
       </c>
       <c r="AH129" t="inlineStr">
         <is>
-          <t>Blåbärsbarrskog</t>
-        </is>
-      </c>
-      <c r="AI129" t="inlineStr">
-        <is>
-          <t>på traktorspår i fuktig terrängsvacka</t>
+          <t>Barrsumpskog</t>
         </is>
       </c>
       <c r="AT129" t="inlineStr"/>
@@ -15055,13 +15055,13 @@
       <c r="AY129" t="inlineStr"/>
       <c r="AZ129" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136103972</t>
+          <t>https://artportalen.se/Sighting/136107643</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>136106473</v>
+        <v>136103972</v>
       </c>
       <c r="B130" t="n">
         <v>100113</v>
@@ -15089,37 +15089,25 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I130" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J130" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+      <c r="I130" t="inlineStr"/>
+      <c r="J130" t="inlineStr"/>
       <c r="K130" t="inlineStr">
         <is>
           <t>i frukt</t>
         </is>
       </c>
       <c r="L130" t="inlineStr"/>
-      <c r="N130" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N130" t="inlineStr"/>
       <c r="P130" t="inlineStr">
         <is>
           <t>Blackstahyttan, Nrk</t>
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>499436</v>
+        <v>499433</v>
       </c>
       <c r="R130" t="n">
-        <v>6580862</v>
+        <v>6580754</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -15166,7 +15154,12 @@
       </c>
       <c r="AH130" t="inlineStr">
         <is>
-          <t>Barrsumpskog</t>
+          <t>Blåbärsbarrskog</t>
+        </is>
+      </c>
+      <c r="AI130" t="inlineStr">
+        <is>
+          <t>på traktorspår i fuktig terrängsvacka</t>
         </is>
       </c>
       <c r="AT130" t="inlineStr"/>
@@ -15183,13 +15176,13 @@
       <c r="AY130" t="inlineStr"/>
       <c r="AZ130" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136106473</t>
+          <t>https://artportalen.se/Sighting/136103972</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>136107586</v>
+        <v>136106473</v>
       </c>
       <c r="B131" t="n">
         <v>100113</v>
@@ -15219,7 +15212,7 @@
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J131" t="inlineStr">
@@ -15233,17 +15226,21 @@
         </is>
       </c>
       <c r="L131" t="inlineStr"/>
-      <c r="N131" t="inlineStr"/>
+      <c r="N131" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P131" t="inlineStr">
         <is>
           <t>Blackstahyttan, Nrk</t>
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>499449</v>
+        <v>499436</v>
       </c>
       <c r="R131" t="n">
-        <v>6580856</v>
+        <v>6580862</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -15307,54 +15304,70 @@
       <c r="AY131" t="inlineStr"/>
       <c r="AZ131" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136107586</t>
+          <t>https://artportalen.se/Sighting/136106473</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>88151816</v>
+        <v>136107586</v>
       </c>
       <c r="B132" t="n">
-        <v>101326</v>
+        <v>100113</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>222498</v>
+        <v>222361</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Loppstarr</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Carex pulicaris</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I132" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J132" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K132" t="inlineStr">
+        <is>
+          <t>i frukt</t>
+        </is>
+      </c>
+      <c r="L132" t="inlineStr"/>
+      <c r="N132" t="inlineStr"/>
       <c r="P132" t="inlineStr">
         <is>
           <t>Blackstahyttan, Nrk</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>499398</v>
+        <v>499449</v>
       </c>
       <c r="R132" t="n">
-        <v>6580897</v>
+        <v>6580856</v>
       </c>
       <c r="S132" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T132" t="inlineStr">
         <is>
@@ -15378,12 +15391,12 @@
       </c>
       <c r="Y132" t="inlineStr">
         <is>
-          <t>2020-09-23</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="AA132" t="inlineStr">
         <is>
-          <t>2020-09-23</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="AD132" t="b">
@@ -15392,39 +15405,36 @@
       <c r="AE132" t="b">
         <v>0</v>
       </c>
+      <c r="AF132" t="inlineStr"/>
       <c r="AG132" t="b">
         <v>0</v>
       </c>
-      <c r="AI132" t="inlineStr">
-        <is>
-          <t>gammal barrskog</t>
+      <c r="AH132" t="inlineStr">
+        <is>
+          <t>Barrsumpskog</t>
         </is>
       </c>
       <c r="AT132" t="inlineStr"/>
       <c r="AW132" t="inlineStr">
         <is>
-          <t>Hans Rydberg</t>
+          <t>Michael Andersson</t>
         </is>
       </c>
       <c r="AX132" t="inlineStr">
         <is>
-          <t>Hans Rydberg</t>
-        </is>
-      </c>
-      <c r="AY132" t="inlineStr">
-        <is>
-          <t>Länsstyrelsen i Örebro län, inventering</t>
-        </is>
-      </c>
+          <t>Michael Andersson, Toni Berglund</t>
+        </is>
+      </c>
+      <c r="AY132" t="inlineStr"/>
       <c r="AZ132" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/88151816</t>
+          <t>https://artportalen.se/Sighting/136107586</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>96195962</v>
+        <v>88151816</v>
       </c>
       <c r="B133" t="n">
         <v>101326</v>
@@ -15453,23 +15463,19 @@
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
-      <c r="J133" t="inlineStr"/>
-      <c r="K133" t="inlineStr"/>
-      <c r="L133" t="inlineStr"/>
-      <c r="N133" t="inlineStr"/>
       <c r="P133" t="inlineStr">
         <is>
-          <t>Alvars väg, Blackstahyttan, Nrk</t>
+          <t>Blackstahyttan, Nrk</t>
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>499353</v>
+        <v>499398</v>
       </c>
       <c r="R133" t="n">
-        <v>6580961</v>
+        <v>6580897</v>
       </c>
       <c r="S133" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T133" t="inlineStr">
         <is>
@@ -15493,12 +15499,12 @@
       </c>
       <c r="Y133" t="inlineStr">
         <is>
-          <t>2021-09-19</t>
+          <t>2020-09-23</t>
         </is>
       </c>
       <c r="AA133" t="inlineStr">
         <is>
-          <t>2021-09-19</t>
+          <t>2020-09-23</t>
         </is>
       </c>
       <c r="AD133" t="b">
@@ -15507,36 +15513,39 @@
       <c r="AE133" t="b">
         <v>0</v>
       </c>
-      <c r="AF133" t="inlineStr"/>
       <c r="AG133" t="b">
         <v>0</v>
       </c>
       <c r="AI133" t="inlineStr">
         <is>
-          <t>gammal kalkbarrskog</t>
+          <t>gammal barrskog</t>
         </is>
       </c>
       <c r="AT133" t="inlineStr"/>
       <c r="AW133" t="inlineStr">
         <is>
-          <t>Michael Andersson</t>
+          <t>Hans Rydberg</t>
         </is>
       </c>
       <c r="AX133" t="inlineStr">
         <is>
-          <t>Michael Andersson, Toni Berglund</t>
-        </is>
-      </c>
-      <c r="AY133" t="inlineStr"/>
+          <t>Hans Rydberg</t>
+        </is>
+      </c>
+      <c r="AY133" t="inlineStr">
+        <is>
+          <t>Länsstyrelsen i Örebro län, inventering</t>
+        </is>
+      </c>
       <c r="AZ133" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/96195962</t>
+          <t>https://artportalen.se/Sighting/88151816</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>111858066</v>
+        <v>96195962</v>
       </c>
       <c r="B134" t="n">
         <v>101326</v>
@@ -15571,14 +15580,14 @@
       <c r="N134" t="inlineStr"/>
       <c r="P134" t="inlineStr">
         <is>
-          <t>Blackstahyttan, Nrk</t>
+          <t>Alvars väg, Blackstahyttan, Nrk</t>
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>499456</v>
+        <v>499353</v>
       </c>
       <c r="R134" t="n">
-        <v>6580855</v>
+        <v>6580961</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -15605,12 +15614,12 @@
       </c>
       <c r="Y134" t="inlineStr">
         <is>
-          <t>2023-09-02</t>
+          <t>2021-09-19</t>
         </is>
       </c>
       <c r="AA134" t="inlineStr">
         <is>
-          <t>2023-09-02</t>
+          <t>2021-09-19</t>
         </is>
       </c>
       <c r="AD134" t="b">
@@ -15623,30 +15632,35 @@
       <c r="AG134" t="b">
         <v>0</v>
       </c>
+      <c r="AI134" t="inlineStr">
+        <is>
+          <t>gammal kalkbarrskog</t>
+        </is>
+      </c>
       <c r="AT134" t="inlineStr"/>
       <c r="AW134" t="inlineStr">
         <is>
-          <t>Toni Berglund</t>
+          <t>Michael Andersson</t>
         </is>
       </c>
       <c r="AX134" t="inlineStr">
         <is>
-          <t>Toni Berglund</t>
+          <t>Michael Andersson, Toni Berglund</t>
         </is>
       </c>
       <c r="AY134" t="inlineStr"/>
       <c r="AZ134" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/111858066</t>
+          <t>https://artportalen.se/Sighting/96195962</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>131900406</v>
+        <v>111858066</v>
       </c>
       <c r="B135" t="n">
-        <v>101403</v>
+        <v>101326</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -15673,11 +15687,7 @@
       </c>
       <c r="I135" t="inlineStr"/>
       <c r="J135" t="inlineStr"/>
-      <c r="K135" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="K135" t="inlineStr"/>
       <c r="L135" t="inlineStr"/>
       <c r="N135" t="inlineStr"/>
       <c r="P135" t="inlineStr">
@@ -15686,10 +15696,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>499349</v>
+        <v>499456</v>
       </c>
       <c r="R135" t="n">
-        <v>6580769</v>
+        <v>6580855</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -15716,12 +15726,12 @@
       </c>
       <c r="Y135" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2023-09-02</t>
         </is>
       </c>
       <c r="AA135" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2023-09-02</t>
         </is>
       </c>
       <c r="AD135" t="b">
@@ -15734,35 +15744,30 @@
       <c r="AG135" t="b">
         <v>0</v>
       </c>
-      <c r="AH135" t="inlineStr">
-        <is>
-          <t>Blåbärsbarrskog</t>
-        </is>
-      </c>
       <c r="AT135" t="inlineStr"/>
       <c r="AW135" t="inlineStr">
         <is>
-          <t>Michael Andersson</t>
+          <t>Toni Berglund</t>
         </is>
       </c>
       <c r="AX135" t="inlineStr">
         <is>
-          <t>Michael Andersson</t>
+          <t>Toni Berglund</t>
         </is>
       </c>
       <c r="AY135" t="inlineStr"/>
       <c r="AZ135" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131900406</t>
+          <t>https://artportalen.se/Sighting/111858066</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>136103341</v>
+        <v>131900406</v>
       </c>
       <c r="B136" t="n">
-        <v>101561</v>
+        <v>101403</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -15802,10 +15807,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>499508</v>
+        <v>499349</v>
       </c>
       <c r="R136" t="n">
-        <v>6580852</v>
+        <v>6580769</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -15832,12 +15837,12 @@
       </c>
       <c r="Y136" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="AA136" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="AD136" t="b">
@@ -15863,19 +15868,19 @@
       </c>
       <c r="AX136" t="inlineStr">
         <is>
-          <t>Michael Andersson, Toni Berglund</t>
+          <t>Michael Andersson</t>
         </is>
       </c>
       <c r="AY136" t="inlineStr"/>
       <c r="AZ136" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136103341</t>
+          <t>https://artportalen.se/Sighting/131900406</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>136104024</v>
+        <v>136103341</v>
       </c>
       <c r="B137" t="n">
         <v>101561</v>
@@ -15918,10 +15923,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>499395</v>
+        <v>499508</v>
       </c>
       <c r="R137" t="n">
-        <v>6580882</v>
+        <v>6580852</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -15971,11 +15976,6 @@
           <t>Blåbärsbarrskog</t>
         </is>
       </c>
-      <c r="AI137" t="inlineStr">
-        <is>
-          <t>stigkant</t>
-        </is>
-      </c>
       <c r="AT137" t="inlineStr"/>
       <c r="AW137" t="inlineStr">
         <is>
@@ -15990,13 +15990,13 @@
       <c r="AY137" t="inlineStr"/>
       <c r="AZ137" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136104024</t>
+          <t>https://artportalen.se/Sighting/136103341</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>136106482</v>
+        <v>136104024</v>
       </c>
       <c r="B138" t="n">
         <v>101561</v>
@@ -16032,21 +16032,17 @@
         </is>
       </c>
       <c r="L138" t="inlineStr"/>
-      <c r="N138" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N138" t="inlineStr"/>
       <c r="P138" t="inlineStr">
         <is>
           <t>Blackstahyttan, Nrk</t>
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>499436</v>
+        <v>499395</v>
       </c>
       <c r="R138" t="n">
-        <v>6580862</v>
+        <v>6580882</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -16093,7 +16089,12 @@
       </c>
       <c r="AH138" t="inlineStr">
         <is>
-          <t>Barrsumpskog</t>
+          <t>Blåbärsbarrskog</t>
+        </is>
+      </c>
+      <c r="AI138" t="inlineStr">
+        <is>
+          <t>stigkant</t>
         </is>
       </c>
       <c r="AT138" t="inlineStr"/>
@@ -16110,13 +16111,13 @@
       <c r="AY138" t="inlineStr"/>
       <c r="AZ138" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136106482</t>
+          <t>https://artportalen.se/Sighting/136104024</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>136106695</v>
+        <v>136106482</v>
       </c>
       <c r="B139" t="n">
         <v>101561</v>
@@ -16152,17 +16153,21 @@
         </is>
       </c>
       <c r="L139" t="inlineStr"/>
-      <c r="N139" t="inlineStr"/>
+      <c r="N139" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P139" t="inlineStr">
         <is>
           <t>Blackstahyttan, Nrk</t>
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>499406</v>
+        <v>499436</v>
       </c>
       <c r="R139" t="n">
-        <v>6580906</v>
+        <v>6580862</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -16209,7 +16214,7 @@
       </c>
       <c r="AH139" t="inlineStr">
         <is>
-          <t>Blåbärsgranskog</t>
+          <t>Barrsumpskog</t>
         </is>
       </c>
       <c r="AT139" t="inlineStr"/>
@@ -16226,13 +16231,13 @@
       <c r="AY139" t="inlineStr"/>
       <c r="AZ139" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136106695</t>
+          <t>https://artportalen.se/Sighting/136106482</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>136107556</v>
+        <v>136106695</v>
       </c>
       <c r="B140" t="n">
         <v>101561</v>
@@ -16275,10 +16280,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>499462</v>
+        <v>499406</v>
       </c>
       <c r="R140" t="n">
-        <v>6580861</v>
+        <v>6580906</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -16325,7 +16330,7 @@
       </c>
       <c r="AH140" t="inlineStr">
         <is>
-          <t>Barrsumpskog</t>
+          <t>Blåbärsgranskog</t>
         </is>
       </c>
       <c r="AT140" t="inlineStr"/>
@@ -16342,16 +16347,16 @@
       <c r="AY140" t="inlineStr"/>
       <c r="AZ140" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136107556</t>
+          <t>https://artportalen.se/Sighting/136106695</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>80046503</v>
+        <v>136107556</v>
       </c>
       <c r="B141" t="n">
-        <v>101228</v>
+        <v>101561</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -16359,37 +16364,45 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>222771</v>
+        <v>222498</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
+      <c r="J141" t="inlineStr"/>
+      <c r="K141" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L141" t="inlineStr"/>
+      <c r="N141" t="inlineStr"/>
       <c r="P141" t="inlineStr">
         <is>
           <t>Blackstahyttan, Nrk</t>
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>499235</v>
+        <v>499462</v>
       </c>
       <c r="R141" t="n">
-        <v>6580819</v>
+        <v>6580861</v>
       </c>
       <c r="S141" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T141" t="inlineStr">
         <is>
@@ -16413,17 +16426,12 @@
       </c>
       <c r="Y141" t="inlineStr">
         <is>
-          <t>2019-09-21</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="AA141" t="inlineStr">
         <is>
-          <t>2019-09-21</t>
-        </is>
-      </c>
-      <c r="AC141" t="inlineStr">
-        <is>
-          <t>NA</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="AD141" t="b">
@@ -16432,33 +16440,39 @@
       <c r="AE141" t="b">
         <v>0</v>
       </c>
+      <c r="AF141" t="inlineStr"/>
       <c r="AG141" t="b">
         <v>0</v>
+      </c>
+      <c r="AH141" t="inlineStr">
+        <is>
+          <t>Barrsumpskog</t>
+        </is>
       </c>
       <c r="AT141" t="inlineStr"/>
       <c r="AW141" t="inlineStr">
         <is>
-          <t>Barbara Kühn</t>
+          <t>Michael Andersson</t>
         </is>
       </c>
       <c r="AX141" t="inlineStr">
         <is>
-          <t>Barbara Kühn, David Tverling, Helena Björnström, Josefina Jansson, Anna Hammar, Anders Carlberg</t>
+          <t>Michael Andersson, Toni Berglund</t>
         </is>
       </c>
       <c r="AY141" t="inlineStr"/>
       <c r="AZ141" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/80046503</t>
+          <t>https://artportalen.se/Sighting/136107556</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>136106667</v>
+        <v>80046503</v>
       </c>
       <c r="B142" t="n">
-        <v>101482</v>
+        <v>101228</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -16466,16 +16480,16 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>222782</v>
+        <v>222771</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Vitsippa</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Anemone nemorosa</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
@@ -16484,27 +16498,19 @@
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
-      <c r="J142" t="inlineStr"/>
-      <c r="K142" t="inlineStr">
-        <is>
-          <t>gulnande löv/blad</t>
-        </is>
-      </c>
-      <c r="L142" t="inlineStr"/>
-      <c r="N142" t="inlineStr"/>
       <c r="P142" t="inlineStr">
         <is>
           <t>Blackstahyttan, Nrk</t>
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>499401</v>
+        <v>499235</v>
       </c>
       <c r="R142" t="n">
-        <v>6580883</v>
+        <v>6580819</v>
       </c>
       <c r="S142" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T142" t="inlineStr">
         <is>
@@ -16528,12 +16534,17 @@
       </c>
       <c r="Y142" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2019-09-21</t>
         </is>
       </c>
       <c r="AA142" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2019-09-21</t>
+        </is>
+      </c>
+      <c r="AC142" t="inlineStr">
+        <is>
+          <t>NA</t>
         </is>
       </c>
       <c r="AD142" t="b">
@@ -16542,39 +16553,33 @@
       <c r="AE142" t="b">
         <v>0</v>
       </c>
-      <c r="AF142" t="inlineStr"/>
       <c r="AG142" t="b">
         <v>0</v>
-      </c>
-      <c r="AH142" t="inlineStr">
-        <is>
-          <t>Barrsumpskog</t>
-        </is>
       </c>
       <c r="AT142" t="inlineStr"/>
       <c r="AW142" t="inlineStr">
         <is>
-          <t>Michael Andersson</t>
+          <t>Barbara Kühn</t>
         </is>
       </c>
       <c r="AX142" t="inlineStr">
         <is>
-          <t>Michael Andersson, Toni Berglund</t>
+          <t>Barbara Kühn, David Tverling, Helena Björnström, Josefina Jansson, Anna Hammar, Anders Carlberg</t>
         </is>
       </c>
       <c r="AY142" t="inlineStr"/>
       <c r="AZ142" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136106667</t>
+          <t>https://artportalen.se/Sighting/80046503</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>136107703</v>
+        <v>136106667</v>
       </c>
       <c r="B143" t="n">
-        <v>99628</v>
+        <v>101482</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -16582,16 +16587,16 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>222812</v>
+        <v>222782</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Liljekonvalj</t>
+          <t>Vitsippa</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Convallaria majalis</t>
+          <t>Anemone nemorosa</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
@@ -16603,7 +16608,7 @@
       <c r="J143" t="inlineStr"/>
       <c r="K143" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>gulnande löv/blad</t>
         </is>
       </c>
       <c r="L143" t="inlineStr"/>
@@ -16614,10 +16619,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>499449</v>
+        <v>499401</v>
       </c>
       <c r="R143" t="n">
-        <v>6580856</v>
+        <v>6580883</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -16681,16 +16686,16 @@
       <c r="AY143" t="inlineStr"/>
       <c r="AZ143" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136107703</t>
+          <t>https://artportalen.se/Sighting/136106667</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>136107647</v>
+        <v>136107703</v>
       </c>
       <c r="B144" t="n">
-        <v>99660</v>
+        <v>99628</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -16698,21 +16703,21 @@
         </is>
       </c>
       <c r="E144" t="n">
-        <v>222857</v>
+        <v>222812</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Ekorrbär</t>
+          <t>Liljekonvalj</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Maianthemum bifolium</t>
+          <t>Convallaria majalis</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(L.) F. W. Schmidt</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
@@ -16797,16 +16802,16 @@
       <c r="AY144" t="inlineStr"/>
       <c r="AZ144" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136107647</t>
+          <t>https://artportalen.se/Sighting/136107703</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>136103347</v>
+        <v>136107647</v>
       </c>
       <c r="B145" t="n">
-        <v>98402</v>
+        <v>99660</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -16814,26 +16819,30 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>223358</v>
+        <v>222857</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Hultbräken</t>
+          <t>Ekorrbär</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Phegopteris connectilis</t>
+          <t>Maianthemum bifolium</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(Michx.) Watt</t>
+          <t>(L.) F. W. Schmidt</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
       <c r="J145" t="inlineStr"/>
-      <c r="K145" t="inlineStr"/>
+      <c r="K145" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L145" t="inlineStr"/>
       <c r="N145" t="inlineStr"/>
       <c r="P145" t="inlineStr">
@@ -16842,10 +16851,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>499508</v>
+        <v>499449</v>
       </c>
       <c r="R145" t="n">
-        <v>6580852</v>
+        <v>6580856</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -16892,7 +16901,7 @@
       </c>
       <c r="AH145" t="inlineStr">
         <is>
-          <t>Blåbärsbarrskog</t>
+          <t>Barrsumpskog</t>
         </is>
       </c>
       <c r="AT145" t="inlineStr"/>
@@ -16909,13 +16918,13 @@
       <c r="AY145" t="inlineStr"/>
       <c r="AZ145" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136103347</t>
+          <t>https://artportalen.se/Sighting/136107647</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>136107617</v>
+        <v>136103347</v>
       </c>
       <c r="B146" t="n">
         <v>98402</v>
@@ -16954,10 +16963,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>499449</v>
+        <v>499508</v>
       </c>
       <c r="R146" t="n">
-        <v>6580856</v>
+        <v>6580852</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -17004,7 +17013,7 @@
       </c>
       <c r="AH146" t="inlineStr">
         <is>
-          <t>Barrsumpskog</t>
+          <t>Blåbärsbarrskog</t>
         </is>
       </c>
       <c r="AT146" t="inlineStr"/>
@@ -17021,16 +17030,16 @@
       <c r="AY146" t="inlineStr"/>
       <c r="AZ146" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136107617</t>
+          <t>https://artportalen.se/Sighting/136103347</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>96368447</v>
+        <v>136107617</v>
       </c>
       <c r="B147" t="n">
-        <v>89079</v>
+        <v>98402</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -17038,24 +17047,28 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>239209</v>
+        <v>223358</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Kantarellvaxing</t>
+          <t>Hultbräken</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Hygrocybe cantharellus</t>
+          <t>Phegopteris connectilis</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Michx.) Watt</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
+      <c r="J147" t="inlineStr"/>
+      <c r="K147" t="inlineStr"/>
+      <c r="L147" t="inlineStr"/>
+      <c r="N147" t="inlineStr"/>
       <c r="P147" t="inlineStr">
         <is>
           <t>Blackstahyttan, Nrk</t>
@@ -17065,7 +17078,7 @@
         <v>499449</v>
       </c>
       <c r="R147" t="n">
-        <v>6580861</v>
+        <v>6580856</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -17092,12 +17105,12 @@
       </c>
       <c r="Y147" t="inlineStr">
         <is>
-          <t>2021-09-27</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="AA147" t="inlineStr">
         <is>
-          <t>2021-09-27</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="AD147" t="b">
@@ -17106,64 +17119,61 @@
       <c r="AE147" t="b">
         <v>0</v>
       </c>
+      <c r="AF147" t="inlineStr"/>
       <c r="AG147" t="b">
         <v>0</v>
       </c>
-      <c r="AI147" t="inlineStr">
-        <is>
-          <t>barrskog</t>
+      <c r="AH147" t="inlineStr">
+        <is>
+          <t>Barrsumpskog</t>
         </is>
       </c>
       <c r="AT147" t="inlineStr"/>
       <c r="AW147" t="inlineStr">
         <is>
-          <t>Hans Rydberg</t>
+          <t>Michael Andersson</t>
         </is>
       </c>
       <c r="AX147" t="inlineStr">
         <is>
-          <t>Hans Rydberg</t>
-        </is>
-      </c>
-      <c r="AY147" t="inlineStr">
-        <is>
-          <t>Länsstyrelsen i Örebro län, inventering</t>
-        </is>
-      </c>
+          <t>Michael Andersson, Toni Berglund</t>
+        </is>
+      </c>
+      <c r="AY147" t="inlineStr"/>
       <c r="AZ147" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/96368447</t>
+          <t>https://artportalen.se/Sighting/136107617</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>75733782</v>
+        <v>96368447</v>
       </c>
       <c r="B148" t="n">
-        <v>91428</v>
+        <v>89079</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E148" t="n">
-        <v>256756</v>
+        <v>239209</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Blek fingersvamp</t>
+          <t>Kantarellvaxing</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Ramaria pallida</t>
+          <t>Hygrocybe cantharellus</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(Schaeff.) Ricken</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
@@ -17173,10 +17183,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>499237</v>
+        <v>499449</v>
       </c>
       <c r="R148" t="n">
-        <v>6580806</v>
+        <v>6580861</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -17203,12 +17213,12 @@
       </c>
       <c r="Y148" t="inlineStr">
         <is>
-          <t>2018-10-13</t>
+          <t>2021-09-27</t>
         </is>
       </c>
       <c r="AA148" t="inlineStr">
         <is>
-          <t>2018-10-13</t>
+          <t>2021-09-27</t>
         </is>
       </c>
       <c r="AD148" t="b">
@@ -17219,16 +17229,21 @@
       </c>
       <c r="AG148" t="b">
         <v>0</v>
+      </c>
+      <c r="AI148" t="inlineStr">
+        <is>
+          <t>barrskog</t>
+        </is>
       </c>
       <c r="AT148" t="inlineStr"/>
       <c r="AW148" t="inlineStr">
         <is>
-          <t>Helena Björnström</t>
+          <t>Hans Rydberg</t>
         </is>
       </c>
       <c r="AX148" t="inlineStr">
         <is>
-          <t>Helena Björnström</t>
+          <t>Hans Rydberg</t>
         </is>
       </c>
       <c r="AY148" t="inlineStr">
@@ -17238,13 +17253,13 @@
       </c>
       <c r="AZ148" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/75733782</t>
+          <t>https://artportalen.se/Sighting/96368447</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>96195231</v>
+        <v>75733782</v>
       </c>
       <c r="B149" t="n">
         <v>91428</v>
@@ -17272,28 +17287,17 @@
           <t>(Schaeff.) Ricken</t>
         </is>
       </c>
-      <c r="I149" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J149" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
-      <c r="K149" t="inlineStr"/>
-      <c r="N149" t="inlineStr"/>
+      <c r="I149" t="inlineStr"/>
       <c r="P149" t="inlineStr">
         <is>
-          <t>Alvars väg, Blackstahyttan, Nrk</t>
+          <t>Blackstahyttan, Nrk</t>
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>499328</v>
+        <v>499237</v>
       </c>
       <c r="R149" t="n">
-        <v>6580771</v>
+        <v>6580806</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -17320,12 +17324,12 @@
       </c>
       <c r="Y149" t="inlineStr">
         <is>
-          <t>2021-09-19</t>
+          <t>2018-10-13</t>
         </is>
       </c>
       <c r="AA149" t="inlineStr">
         <is>
-          <t>2021-09-19</t>
+          <t>2018-10-13</t>
         </is>
       </c>
       <c r="AD149" t="b">
@@ -17334,36 +17338,34 @@
       <c r="AE149" t="b">
         <v>0</v>
       </c>
-      <c r="AF149" t="inlineStr"/>
       <c r="AG149" t="b">
         <v>0</v>
-      </c>
-      <c r="AI149" t="inlineStr">
-        <is>
-          <t>gammal kalkbarrskog</t>
-        </is>
       </c>
       <c r="AT149" t="inlineStr"/>
       <c r="AW149" t="inlineStr">
         <is>
-          <t>Michael Andersson</t>
+          <t>Helena Björnström</t>
         </is>
       </c>
       <c r="AX149" t="inlineStr">
         <is>
-          <t>Michael Andersson, Toni Berglund</t>
-        </is>
-      </c>
-      <c r="AY149" t="inlineStr"/>
+          <t>Helena Björnström</t>
+        </is>
+      </c>
+      <c r="AY149" t="inlineStr">
+        <is>
+          <t>Länsstyrelsen i Örebro län, inventering</t>
+        </is>
+      </c>
       <c r="AZ149" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/96195231</t>
+          <t>https://artportalen.se/Sighting/75733782</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>128198743</v>
+        <v>96195231</v>
       </c>
       <c r="B150" t="n">
         <v>91428</v>
@@ -17391,20 +17393,28 @@
           <t>(Schaeff.) Ricken</t>
         </is>
       </c>
-      <c r="I150" t="inlineStr"/>
-      <c r="J150" t="inlineStr"/>
+      <c r="I150" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J150" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="K150" t="inlineStr"/>
       <c r="N150" t="inlineStr"/>
       <c r="P150" t="inlineStr">
         <is>
-          <t>Alvars väg, Nrk</t>
+          <t>Alvars väg, Blackstahyttan, Nrk</t>
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>499358</v>
+        <v>499328</v>
       </c>
       <c r="R150" t="n">
-        <v>6580971</v>
+        <v>6580771</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -17431,12 +17441,12 @@
       </c>
       <c r="Y150" t="inlineStr">
         <is>
-          <t>2025-09-01</t>
+          <t>2021-09-19</t>
         </is>
       </c>
       <c r="AA150" t="inlineStr">
         <is>
-          <t>2025-09-01</t>
+          <t>2021-09-19</t>
         </is>
       </c>
       <c r="AD150" t="b">
@@ -17449,27 +17459,32 @@
       <c r="AG150" t="b">
         <v>0</v>
       </c>
+      <c r="AI150" t="inlineStr">
+        <is>
+          <t>gammal kalkbarrskog</t>
+        </is>
+      </c>
       <c r="AT150" t="inlineStr"/>
       <c r="AW150" t="inlineStr">
         <is>
-          <t>Toni Berglund</t>
+          <t>Michael Andersson</t>
         </is>
       </c>
       <c r="AX150" t="inlineStr">
         <is>
-          <t>Toni Berglund</t>
+          <t>Michael Andersson, Toni Berglund</t>
         </is>
       </c>
       <c r="AY150" t="inlineStr"/>
       <c r="AZ150" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128198743</t>
+          <t>https://artportalen.se/Sighting/96195231</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>128198755</v>
+        <v>128198743</v>
       </c>
       <c r="B151" t="n">
         <v>91428</v>
@@ -17503,14 +17518,14 @@
       <c r="N151" t="inlineStr"/>
       <c r="P151" t="inlineStr">
         <is>
-          <t>Blackstahyttan, Nrk</t>
+          <t>Alvars väg, Nrk</t>
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>499290</v>
+        <v>499358</v>
       </c>
       <c r="R151" t="n">
-        <v>6580799</v>
+        <v>6580971</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -17569,16 +17584,16 @@
       <c r="AY151" t="inlineStr"/>
       <c r="AZ151" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128198755</t>
+          <t>https://artportalen.se/Sighting/128198743</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>136738638</v>
+        <v>128198755</v>
       </c>
       <c r="B152" t="n">
-        <v>91613</v>
+        <v>91428</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -17603,16 +17618,8 @@
           <t>(Schaeff.) Ricken</t>
         </is>
       </c>
-      <c r="I152" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J152" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="I152" t="inlineStr"/>
+      <c r="J152" t="inlineStr"/>
       <c r="K152" t="inlineStr"/>
       <c r="N152" t="inlineStr"/>
       <c r="P152" t="inlineStr">
@@ -17624,7 +17631,7 @@
         <v>499290</v>
       </c>
       <c r="R152" t="n">
-        <v>6580794</v>
+        <v>6580799</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -17651,12 +17658,12 @@
       </c>
       <c r="Y152" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2025-09-01</t>
         </is>
       </c>
       <c r="AA152" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2025-09-01</t>
         </is>
       </c>
       <c r="AD152" t="b">
@@ -17665,6 +17672,7 @@
       <c r="AE152" t="b">
         <v>0</v>
       </c>
+      <c r="AF152" t="inlineStr"/>
       <c r="AG152" t="b">
         <v>0</v>
       </c>
@@ -17682,42 +17690,50 @@
       <c r="AY152" t="inlineStr"/>
       <c r="AZ152" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136738638</t>
+          <t>https://artportalen.se/Sighting/128198755</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>111857904</v>
+        <v>136738638</v>
       </c>
       <c r="B153" t="n">
-        <v>87297</v>
+        <v>91613</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E153" t="n">
-        <v>6003296</v>
+        <v>256756</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Stor odörspindling</t>
+          <t>Blek fingersvamp</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Cortinarius mussivus</t>
+          <t>Ramaria pallida</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(Fr.) Melot</t>
-        </is>
-      </c>
-      <c r="I153" t="inlineStr"/>
-      <c r="J153" t="inlineStr"/>
+          <t>(Schaeff.) Ricken</t>
+        </is>
+      </c>
+      <c r="I153" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J153" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K153" t="inlineStr"/>
       <c r="N153" t="inlineStr"/>
       <c r="P153" t="inlineStr">
@@ -17726,10 +17742,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>499392</v>
+        <v>499290</v>
       </c>
       <c r="R153" t="n">
-        <v>6580908</v>
+        <v>6580794</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -17756,17 +17772,12 @@
       </c>
       <c r="Y153" t="inlineStr">
         <is>
-          <t>2023-09-02</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="AA153" t="inlineStr">
         <is>
-          <t>2023-09-02</t>
-        </is>
-      </c>
-      <c r="AC153" t="inlineStr">
-        <is>
-          <t>16 fruktkroppar.</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="AD153" t="b">
@@ -17775,7 +17786,6 @@
       <c r="AE153" t="b">
         <v>0</v>
       </c>
-      <c r="AF153" t="inlineStr"/>
       <c r="AG153" t="b">
         <v>0</v>
       </c>
@@ -17787,19 +17797,19 @@
       </c>
       <c r="AX153" t="inlineStr">
         <is>
-          <t>Toni Berglund, Lotta Sörman, Anneli Sjöstrand</t>
+          <t>Toni Berglund</t>
         </is>
       </c>
       <c r="AY153" t="inlineStr"/>
       <c r="AZ153" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/111857904</t>
+          <t>https://artportalen.se/Sighting/136738638</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>128078934</v>
+        <v>111857904</v>
       </c>
       <c r="B154" t="n">
         <v>87297</v>
@@ -17828,16 +17838,19 @@
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
+      <c r="J154" t="inlineStr"/>
+      <c r="K154" t="inlineStr"/>
+      <c r="N154" t="inlineStr"/>
       <c r="P154" t="inlineStr">
         <is>
-          <t>Alvars väg, Nrk</t>
+          <t>Blackstahyttan, Nrk</t>
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>499401</v>
+        <v>499392</v>
       </c>
       <c r="R154" t="n">
-        <v>6580907</v>
+        <v>6580908</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -17864,22 +17877,17 @@
       </c>
       <c r="Y154" t="inlineStr">
         <is>
-          <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="Z154" t="inlineStr">
-        <is>
-          <t>15:28</t>
+          <t>2023-09-02</t>
         </is>
       </c>
       <c r="AA154" t="inlineStr">
         <is>
-          <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="AB154" t="inlineStr">
-        <is>
-          <t>15:28</t>
+          <t>2023-09-02</t>
+        </is>
+      </c>
+      <c r="AC154" t="inlineStr">
+        <is>
+          <t>16 fruktkroppar.</t>
         </is>
       </c>
       <c r="AD154" t="b">
@@ -17888,76 +17896,66 @@
       <c r="AE154" t="b">
         <v>0</v>
       </c>
+      <c r="AF154" t="inlineStr"/>
       <c r="AG154" t="b">
         <v>0</v>
       </c>
       <c r="AT154" t="inlineStr"/>
       <c r="AW154" t="inlineStr">
         <is>
-          <t>Anders Carlberg</t>
+          <t>Toni Berglund</t>
         </is>
       </c>
       <c r="AX154" t="inlineStr">
         <is>
-          <t>Anders Carlberg, Toni Berglund</t>
+          <t>Toni Berglund, Lotta Sörman, Anneli Sjöstrand</t>
         </is>
       </c>
       <c r="AY154" t="inlineStr"/>
       <c r="AZ154" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128078934</t>
+          <t>https://artportalen.se/Sighting/111857904</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>96359797</v>
+        <v>128078934</v>
       </c>
       <c r="B155" t="n">
-        <v>93200</v>
+        <v>87297</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E155" t="n">
-        <v>6003297</v>
+        <v>6003296</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Spricktaggsvamp</t>
+          <t>Stor odörspindling</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Hydnellum glaucopus</t>
+          <t>Cortinarius mussivus</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(Maas Geest. &amp; Nannf.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
-        </is>
-      </c>
-      <c r="I155" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J155" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K155" t="inlineStr"/>
-      <c r="N155" t="inlineStr"/>
+          <t>(Fr.) Melot</t>
+        </is>
+      </c>
+      <c r="I155" t="inlineStr"/>
       <c r="P155" t="inlineStr">
         <is>
-          <t>Alvars väg, Blackstahyttan, Nrk</t>
+          <t>Alvars väg, Nrk</t>
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>499400</v>
+        <v>499401</v>
       </c>
       <c r="R155" t="n">
         <v>6580907</v>
@@ -17987,12 +17985,22 @@
       </c>
       <c r="Y155" t="inlineStr">
         <is>
-          <t>2021-09-19</t>
+          <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="Z155" t="inlineStr">
+        <is>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AA155" t="inlineStr">
         <is>
-          <t>2021-09-19</t>
+          <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AB155" t="inlineStr">
+        <is>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AD155" t="b">
@@ -18001,36 +18009,30 @@
       <c r="AE155" t="b">
         <v>0</v>
       </c>
-      <c r="AF155" t="inlineStr"/>
       <c r="AG155" t="b">
         <v>0</v>
-      </c>
-      <c r="AI155" t="inlineStr">
-        <is>
-          <t>under gran i gammal kalkbarrskog</t>
-        </is>
       </c>
       <c r="AT155" t="inlineStr"/>
       <c r="AW155" t="inlineStr">
         <is>
-          <t>Michael Andersson</t>
+          <t>Anders Carlberg</t>
         </is>
       </c>
       <c r="AX155" t="inlineStr">
         <is>
-          <t>Michael Andersson, Toni Berglund</t>
+          <t>Anders Carlberg, Toni Berglund</t>
         </is>
       </c>
       <c r="AY155" t="inlineStr"/>
       <c r="AZ155" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/96359797</t>
+          <t>https://artportalen.se/Sighting/128078934</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>128079275</v>
+        <v>96359797</v>
       </c>
       <c r="B156" t="n">
         <v>93200</v>
@@ -18058,17 +18060,25 @@
           <t>(Maas Geest. &amp; Nannf.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
-      <c r="I156" t="inlineStr"/>
-      <c r="J156" t="inlineStr"/>
+      <c r="I156" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J156" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K156" t="inlineStr"/>
       <c r="N156" t="inlineStr"/>
       <c r="P156" t="inlineStr">
         <is>
-          <t>Alvars väg, Nrk</t>
+          <t>Alvars väg, Blackstahyttan, Nrk</t>
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>499401</v>
+        <v>499400</v>
       </c>
       <c r="R156" t="n">
         <v>6580907</v>
@@ -18098,58 +18108,53 @@
       </c>
       <c r="Y156" t="inlineStr">
         <is>
-          <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="Z156" t="inlineStr">
-        <is>
-          <t>15:28</t>
+          <t>2021-09-19</t>
         </is>
       </c>
       <c r="AA156" t="inlineStr">
         <is>
-          <t>2025-08-30</t>
-        </is>
-      </c>
-      <c r="AB156" t="inlineStr">
-        <is>
-          <t>15:28</t>
+          <t>2021-09-19</t>
         </is>
       </c>
       <c r="AD156" t="b">
         <v>0</v>
       </c>
       <c r="AE156" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF156" t="inlineStr"/>
       <c r="AG156" t="b">
         <v>0</v>
       </c>
+      <c r="AI156" t="inlineStr">
+        <is>
+          <t>under gran i gammal kalkbarrskog</t>
+        </is>
+      </c>
       <c r="AT156" t="inlineStr"/>
       <c r="AW156" t="inlineStr">
         <is>
-          <t>Anders Carlberg</t>
+          <t>Michael Andersson</t>
         </is>
       </c>
       <c r="AX156" t="inlineStr">
         <is>
-          <t>Anders Carlberg, Toni Berglund</t>
+          <t>Michael Andersson, Toni Berglund</t>
         </is>
       </c>
       <c r="AY156" t="inlineStr"/>
       <c r="AZ156" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128079275</t>
+          <t>https://artportalen.se/Sighting/96359797</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>136104021</v>
+        <v>128079275</v>
       </c>
       <c r="B157" t="n">
-        <v>93412</v>
+        <v>93200</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -18174,28 +18179,20 @@
           <t>(Maas Geest. &amp; Nannf.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
-      <c r="I157" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J157" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="I157" t="inlineStr"/>
+      <c r="J157" t="inlineStr"/>
       <c r="K157" t="inlineStr"/>
       <c r="N157" t="inlineStr"/>
       <c r="P157" t="inlineStr">
         <is>
-          <t>Blackstahyttan, Nrk</t>
+          <t>Alvars väg, Nrk</t>
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>499395</v>
+        <v>499401</v>
       </c>
       <c r="R157" t="n">
-        <v>6580882</v>
+        <v>6580907</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -18222,55 +18219,55 @@
       </c>
       <c r="Y157" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="Z157" t="inlineStr">
+        <is>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AA157" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AB157" t="inlineStr">
+        <is>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AD157" t="b">
         <v>0</v>
       </c>
       <c r="AE157" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF157" t="inlineStr"/>
       <c r="AG157" t="b">
         <v>0</v>
       </c>
-      <c r="AH157" t="inlineStr">
-        <is>
-          <t>Blåbärsbarrskog</t>
-        </is>
-      </c>
-      <c r="AI157" t="inlineStr">
-        <is>
-          <t>stigkant</t>
-        </is>
-      </c>
       <c r="AT157" t="inlineStr"/>
       <c r="AW157" t="inlineStr">
         <is>
-          <t>Michael Andersson</t>
+          <t>Anders Carlberg</t>
         </is>
       </c>
       <c r="AX157" t="inlineStr">
         <is>
-          <t>Michael Andersson, Toni Berglund</t>
+          <t>Anders Carlberg, Toni Berglund</t>
         </is>
       </c>
       <c r="AY157" t="inlineStr"/>
       <c r="AZ157" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136104021</t>
+          <t>https://artportalen.se/Sighting/128079275</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>136107324</v>
+        <v>136104021</v>
       </c>
       <c r="B158" t="n">
         <v>93412</v>
@@ -18316,10 +18313,10 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>499495</v>
+        <v>499395</v>
       </c>
       <c r="R158" t="n">
-        <v>6580853</v>
+        <v>6580882</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -18371,7 +18368,7 @@
       </c>
       <c r="AI158" t="inlineStr">
         <is>
-          <t>kalkbarrskog invid bäck</t>
+          <t>stigkant</t>
         </is>
       </c>
       <c r="AT158" t="inlineStr"/>
@@ -18388,50 +18385,62 @@
       <c r="AY158" t="inlineStr"/>
       <c r="AZ158" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136107324</t>
+          <t>https://artportalen.se/Sighting/136104021</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>136599222</v>
+        <v>136107324</v>
       </c>
       <c r="B159" t="n">
-        <v>93425</v>
+        <v>93412</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E159" t="n">
-        <v>6047725</v>
+        <v>6003297</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Rödfläckig zontaggsvamp</t>
+          <t>Spricktaggsvamp</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Hydnellum rufoconcrescens nom.prov.</t>
-        </is>
-      </c>
-      <c r="H159" t="inlineStr"/>
-      <c r="I159" t="inlineStr"/>
-      <c r="J159" t="inlineStr"/>
+          <t>Hydnellum glaucopus</t>
+        </is>
+      </c>
+      <c r="H159" t="inlineStr">
+        <is>
+          <t>(Maas Geest. &amp; Nannf.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+        </is>
+      </c>
+      <c r="I159" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J159" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K159" t="inlineStr"/>
       <c r="N159" t="inlineStr"/>
       <c r="P159" t="inlineStr">
         <is>
-          <t>Västantorp, Västantorp, Nrk</t>
+          <t>Blackstahyttan, Nrk</t>
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>499491</v>
+        <v>499495</v>
       </c>
       <c r="R159" t="n">
-        <v>6580841</v>
+        <v>6580853</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -18458,17 +18467,12 @@
       </c>
       <c r="Y159" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="AA159" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
-        </is>
-      </c>
-      <c r="AC159" t="inlineStr">
-        <is>
-          <t>Vid stigen kors Bäck. Med svartvit tagg, P niger och bockspindling.</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="AD159" t="b">
@@ -18481,30 +18485,40 @@
       <c r="AG159" t="b">
         <v>0</v>
       </c>
+      <c r="AH159" t="inlineStr">
+        <is>
+          <t>Blåbärsbarrskog</t>
+        </is>
+      </c>
+      <c r="AI159" t="inlineStr">
+        <is>
+          <t>kalkbarrskog invid bäck</t>
+        </is>
+      </c>
       <c r="AT159" t="inlineStr"/>
       <c r="AW159" t="inlineStr">
         <is>
-          <t>Erik Göthlin</t>
+          <t>Michael Andersson</t>
         </is>
       </c>
       <c r="AX159" t="inlineStr">
         <is>
-          <t>Erik Göthlin</t>
+          <t>Michael Andersson, Toni Berglund</t>
         </is>
       </c>
       <c r="AY159" t="inlineStr"/>
       <c r="AZ159" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136599222</t>
+          <t>https://artportalen.se/Sighting/136107324</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>136597788</v>
+        <v>136599222</v>
       </c>
       <c r="B160" t="n">
-        <v>93439</v>
+        <v>93425</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -18512,34 +18526,33 @@
         </is>
       </c>
       <c r="E160" t="n">
-        <v>6332770</v>
+        <v>6047725</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Rödfläckig zontaggsvamp</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
-        </is>
-      </c>
-      <c r="H160" t="inlineStr">
-        <is>
-          <t>(Fr.) P.Karst.</t>
-        </is>
-      </c>
+          <t>Hydnellum rufoconcrescens nom.prov.</t>
+        </is>
+      </c>
+      <c r="H160" t="inlineStr"/>
       <c r="I160" t="inlineStr"/>
+      <c r="J160" t="inlineStr"/>
+      <c r="K160" t="inlineStr"/>
+      <c r="N160" t="inlineStr"/>
       <c r="P160" t="inlineStr">
         <is>
-          <t>Gretefallet, Gretefallet, Nrk</t>
+          <t>Västantorp, Västantorp, Nrk</t>
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>499525</v>
+        <v>499491</v>
       </c>
       <c r="R160" t="n">
-        <v>6580853</v>
+        <v>6580841</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -18574,12 +18587,18 @@
           <t>2026-09-13</t>
         </is>
       </c>
+      <c r="AC160" t="inlineStr">
+        <is>
+          <t>Vid stigen kors Bäck. Med svartvit tagg, P niger och bockspindling.</t>
+        </is>
+      </c>
       <c r="AD160" t="b">
         <v>0</v>
       </c>
       <c r="AE160" t="b">
         <v>0</v>
       </c>
+      <c r="AF160" t="inlineStr"/>
       <c r="AG160" t="b">
         <v>0</v>
       </c>
@@ -18597,13 +18616,13 @@
       <c r="AY160" t="inlineStr"/>
       <c r="AZ160" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136597788</t>
+          <t>https://artportalen.se/Sighting/136599222</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>136609580</v>
+        <v>136597788</v>
       </c>
       <c r="B161" t="n">
         <v>93439</v>
@@ -18632,19 +18651,16 @@
         </is>
       </c>
       <c r="I161" t="inlineStr"/>
-      <c r="J161" t="inlineStr"/>
-      <c r="K161" t="inlineStr"/>
-      <c r="N161" t="inlineStr"/>
       <c r="P161" t="inlineStr">
         <is>
-          <t>NV Blackstahyttan, Nrk</t>
+          <t>Gretefallet, Gretefallet, Nrk</t>
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>499533</v>
+        <v>499525</v>
       </c>
       <c r="R161" t="n">
-        <v>6580838</v>
+        <v>6580853</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -18685,7 +18701,6 @@
       <c r="AE161" t="b">
         <v>0</v>
       </c>
-      <c r="AF161" t="inlineStr"/>
       <c r="AG161" t="b">
         <v>0</v>
       </c>
@@ -18702,6 +18717,112 @@
       </c>
       <c r="AY161" t="inlineStr"/>
       <c r="AZ161" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136597788</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="n">
+        <v>136609580</v>
+      </c>
+      <c r="B162" t="n">
+        <v>93439</v>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E162" t="n">
+        <v>6332770</v>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>Svart taggsvamp</t>
+        </is>
+      </c>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>Phellodon niger</t>
+        </is>
+      </c>
+      <c r="H162" t="inlineStr">
+        <is>
+          <t>(Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I162" t="inlineStr"/>
+      <c r="J162" t="inlineStr"/>
+      <c r="K162" t="inlineStr"/>
+      <c r="N162" t="inlineStr"/>
+      <c r="P162" t="inlineStr">
+        <is>
+          <t>NV Blackstahyttan, Nrk</t>
+        </is>
+      </c>
+      <c r="Q162" t="n">
+        <v>499533</v>
+      </c>
+      <c r="R162" t="n">
+        <v>6580838</v>
+      </c>
+      <c r="S162" t="n">
+        <v>10</v>
+      </c>
+      <c r="T162" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U162" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="V162" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W162" t="inlineStr">
+        <is>
+          <t>Kil</t>
+        </is>
+      </c>
+      <c r="Y162" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="AA162" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="AD162" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE162" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF162" t="inlineStr"/>
+      <c r="AG162" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT162" t="inlineStr"/>
+      <c r="AW162" t="inlineStr">
+        <is>
+          <t>Erik Göthlin</t>
+        </is>
+      </c>
+      <c r="AX162" t="inlineStr">
+        <is>
+          <t>Erik Göthlin</t>
+        </is>
+      </c>
+      <c r="AY162" t="inlineStr"/>
+      <c r="AZ162" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/136609580</t>
         </is>
@@ -18869,6 +18990,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ159" r:id="rId158"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ160" r:id="rId159"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ161" r:id="rId160"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ162" r:id="rId161"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/S 3548-2025 artfynd.xlsx
+++ b/artfynd/S 3548-2025 artfynd.xlsx
@@ -8274,7 +8274,7 @@
         <v>137007784</v>
       </c>
       <c r="B70" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -9156,7 +9156,7 @@
         <v>136597825</v>
       </c>
       <c r="B78" t="n">
-        <v>93423</v>
+        <v>93425</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -10571,7 +10571,7 @@
         <v>136597260</v>
       </c>
       <c r="B91" t="n">
-        <v>93437</v>
+        <v>93439</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10685,7 +10685,7 @@
         <v>136609571</v>
       </c>
       <c r="B92" t="n">
-        <v>93437</v>
+        <v>93439</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -12581,7 +12581,7 @@
         <v>136597853</v>
       </c>
       <c r="B109" t="n">
-        <v>93447</v>
+        <v>93449</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -17699,7 +17699,7 @@
         <v>136738638</v>
       </c>
       <c r="B153" t="n">
-        <v>91613</v>
+        <v>91615</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -18518,7 +18518,7 @@
         <v>136599222</v>
       </c>
       <c r="B160" t="n">
-        <v>93425</v>
+        <v>93427</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -18625,7 +18625,7 @@
         <v>136597788</v>
       </c>
       <c r="B161" t="n">
-        <v>93439</v>
+        <v>93441</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -18727,7 +18727,7 @@
         <v>136609580</v>
       </c>
       <c r="B162" t="n">
-        <v>93439</v>
+        <v>93441</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>

--- a/artfynd/S 3548-2025 artfynd.xlsx
+++ b/artfynd/S 3548-2025 artfynd.xlsx
@@ -8274,7 +8274,7 @@
         <v>137007784</v>
       </c>
       <c r="B70" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -9156,7 +9156,7 @@
         <v>136597825</v>
       </c>
       <c r="B78" t="n">
-        <v>93425</v>
+        <v>93427</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -10571,7 +10571,7 @@
         <v>136597260</v>
       </c>
       <c r="B91" t="n">
-        <v>93439</v>
+        <v>93441</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10685,7 +10685,7 @@
         <v>136609571</v>
       </c>
       <c r="B92" t="n">
-        <v>93439</v>
+        <v>93441</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -12581,7 +12581,7 @@
         <v>136597853</v>
       </c>
       <c r="B109" t="n">
-        <v>93449</v>
+        <v>93451</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -17699,7 +17699,7 @@
         <v>136738638</v>
       </c>
       <c r="B153" t="n">
-        <v>91615</v>
+        <v>91617</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -18518,7 +18518,7 @@
         <v>136599222</v>
       </c>
       <c r="B160" t="n">
-        <v>93427</v>
+        <v>93429</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -18625,7 +18625,7 @@
         <v>136597788</v>
       </c>
       <c r="B161" t="n">
-        <v>93441</v>
+        <v>93443</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -18727,7 +18727,7 @@
         <v>136609580</v>
       </c>
       <c r="B162" t="n">
-        <v>93441</v>
+        <v>93443</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>

--- a/artfynd/S 3548-2025 artfynd.xlsx
+++ b/artfynd/S 3548-2025 artfynd.xlsx
@@ -8274,7 +8274,7 @@
         <v>137007784</v>
       </c>
       <c r="B70" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -9156,7 +9156,7 @@
         <v>136597825</v>
       </c>
       <c r="B78" t="n">
-        <v>93427</v>
+        <v>93428</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -10571,7 +10571,7 @@
         <v>136597260</v>
       </c>
       <c r="B91" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10685,7 +10685,7 @@
         <v>136609571</v>
       </c>
       <c r="B92" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -12581,7 +12581,7 @@
         <v>136597853</v>
       </c>
       <c r="B109" t="n">
-        <v>93451</v>
+        <v>93452</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -17699,7 +17699,7 @@
         <v>136738638</v>
       </c>
       <c r="B153" t="n">
-        <v>91617</v>
+        <v>91618</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -18518,7 +18518,7 @@
         <v>136599222</v>
       </c>
       <c r="B160" t="n">
-        <v>93429</v>
+        <v>93430</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -18625,7 +18625,7 @@
         <v>136597788</v>
       </c>
       <c r="B161" t="n">
-        <v>93443</v>
+        <v>93444</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -18727,7 +18727,7 @@
         <v>136609580</v>
       </c>
       <c r="B162" t="n">
-        <v>93443</v>
+        <v>93444</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>

--- a/artfynd/S 3548-2025 artfynd.xlsx
+++ b/artfynd/S 3548-2025 artfynd.xlsx
@@ -8274,7 +8274,7 @@
         <v>137007784</v>
       </c>
       <c r="B70" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -9156,7 +9156,7 @@
         <v>136597825</v>
       </c>
       <c r="B78" t="n">
-        <v>93428</v>
+        <v>93434</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -10571,7 +10571,7 @@
         <v>136597260</v>
       </c>
       <c r="B91" t="n">
-        <v>93442</v>
+        <v>93448</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10685,7 +10685,7 @@
         <v>136609571</v>
       </c>
       <c r="B92" t="n">
-        <v>93442</v>
+        <v>93448</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -12581,7 +12581,7 @@
         <v>136597853</v>
       </c>
       <c r="B109" t="n">
-        <v>93452</v>
+        <v>93458</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -17699,7 +17699,7 @@
         <v>136738638</v>
       </c>
       <c r="B153" t="n">
-        <v>91618</v>
+        <v>91624</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -18518,7 +18518,7 @@
         <v>136599222</v>
       </c>
       <c r="B160" t="n">
-        <v>93430</v>
+        <v>93436</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -18625,7 +18625,7 @@
         <v>136597788</v>
       </c>
       <c r="B161" t="n">
-        <v>93444</v>
+        <v>93450</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -18727,7 +18727,7 @@
         <v>136609580</v>
       </c>
       <c r="B162" t="n">
-        <v>93444</v>
+        <v>93450</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>

--- a/artfynd/S 3548-2025 artfynd.xlsx
+++ b/artfynd/S 3548-2025 artfynd.xlsx
@@ -8274,7 +8274,7 @@
         <v>137007784</v>
       </c>
       <c r="B70" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -9156,7 +9156,7 @@
         <v>136597825</v>
       </c>
       <c r="B78" t="n">
-        <v>93434</v>
+        <v>93438</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -10571,7 +10571,7 @@
         <v>136597260</v>
       </c>
       <c r="B91" t="n">
-        <v>93448</v>
+        <v>93452</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10685,7 +10685,7 @@
         <v>136609571</v>
       </c>
       <c r="B92" t="n">
-        <v>93448</v>
+        <v>93452</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -12581,7 +12581,7 @@
         <v>136597853</v>
       </c>
       <c r="B109" t="n">
-        <v>93458</v>
+        <v>93462</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -17699,7 +17699,7 @@
         <v>136738638</v>
       </c>
       <c r="B153" t="n">
-        <v>91624</v>
+        <v>91628</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -18518,7 +18518,7 @@
         <v>136599222</v>
       </c>
       <c r="B160" t="n">
-        <v>93436</v>
+        <v>93440</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -18625,7 +18625,7 @@
         <v>136597788</v>
       </c>
       <c r="B161" t="n">
-        <v>93450</v>
+        <v>93454</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -18727,7 +18727,7 @@
         <v>136609580</v>
       </c>
       <c r="B162" t="n">
-        <v>93450</v>
+        <v>93454</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>

--- a/artfynd/S 3548-2025 artfynd.xlsx
+++ b/artfynd/S 3548-2025 artfynd.xlsx
@@ -8274,7 +8274,7 @@
         <v>137007784</v>
       </c>
       <c r="B70" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -9156,7 +9156,7 @@
         <v>136597825</v>
       </c>
       <c r="B78" t="n">
-        <v>93438</v>
+        <v>93440</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -10571,7 +10571,7 @@
         <v>136597260</v>
       </c>
       <c r="B91" t="n">
-        <v>93452</v>
+        <v>93454</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10685,7 +10685,7 @@
         <v>136609571</v>
       </c>
       <c r="B92" t="n">
-        <v>93452</v>
+        <v>93454</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -12581,7 +12581,7 @@
         <v>136597853</v>
       </c>
       <c r="B109" t="n">
-        <v>93462</v>
+        <v>93464</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -17699,7 +17699,7 @@
         <v>136738638</v>
       </c>
       <c r="B153" t="n">
-        <v>91628</v>
+        <v>91630</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -18518,7 +18518,7 @@
         <v>136599222</v>
       </c>
       <c r="B160" t="n">
-        <v>93440</v>
+        <v>93442</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -18625,7 +18625,7 @@
         <v>136597788</v>
       </c>
       <c r="B161" t="n">
-        <v>93454</v>
+        <v>93456</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -18727,7 +18727,7 @@
         <v>136609580</v>
       </c>
       <c r="B162" t="n">
-        <v>93454</v>
+        <v>93456</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>

--- a/artfynd/S 3548-2025 artfynd.xlsx
+++ b/artfynd/S 3548-2025 artfynd.xlsx
@@ -8274,7 +8274,7 @@
         <v>137007784</v>
       </c>
       <c r="B70" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -9156,7 +9156,7 @@
         <v>136597825</v>
       </c>
       <c r="B78" t="n">
-        <v>93440</v>
+        <v>93453</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -10571,7 +10571,7 @@
         <v>136597260</v>
       </c>
       <c r="B91" t="n">
-        <v>93454</v>
+        <v>93467</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10685,7 +10685,7 @@
         <v>136609571</v>
       </c>
       <c r="B92" t="n">
-        <v>93454</v>
+        <v>93467</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -12581,7 +12581,7 @@
         <v>136597853</v>
       </c>
       <c r="B109" t="n">
-        <v>93464</v>
+        <v>93477</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -17699,7 +17699,7 @@
         <v>136738638</v>
       </c>
       <c r="B153" t="n">
-        <v>91630</v>
+        <v>91643</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -18518,7 +18518,7 @@
         <v>136599222</v>
       </c>
       <c r="B160" t="n">
-        <v>93442</v>
+        <v>93455</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -18625,7 +18625,7 @@
         <v>136597788</v>
       </c>
       <c r="B161" t="n">
-        <v>93456</v>
+        <v>93469</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -18727,7 +18727,7 @@
         <v>136609580</v>
       </c>
       <c r="B162" t="n">
-        <v>93456</v>
+        <v>93469</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>

--- a/artfynd/S 3548-2025 artfynd.xlsx
+++ b/artfynd/S 3548-2025 artfynd.xlsx
@@ -8274,7 +8274,7 @@
         <v>137007784</v>
       </c>
       <c r="B70" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -17699,7 +17699,7 @@
         <v>136738638</v>
       </c>
       <c r="B153" t="n">
-        <v>91643</v>
+        <v>91645</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>

--- a/artfynd/S 3548-2025 artfynd.xlsx
+++ b/artfynd/S 3548-2025 artfynd.xlsx
@@ -8274,7 +8274,7 @@
         <v>137007784</v>
       </c>
       <c r="B70" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -17699,7 +17699,7 @@
         <v>136738638</v>
       </c>
       <c r="B153" t="n">
-        <v>91645</v>
+        <v>91648</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>

--- a/artfynd/S 3548-2025 artfynd.xlsx
+++ b/artfynd/S 3548-2025 artfynd.xlsx
@@ -8274,7 +8274,7 @@
         <v>137007784</v>
       </c>
       <c r="B70" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -17699,7 +17699,7 @@
         <v>136738638</v>
       </c>
       <c r="B153" t="n">
-        <v>91648</v>
+        <v>91658</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>

--- a/artfynd/S 3548-2025 artfynd.xlsx
+++ b/artfynd/S 3548-2025 artfynd.xlsx
@@ -8274,7 +8274,7 @@
         <v>137007784</v>
       </c>
       <c r="B70" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -17699,7 +17699,7 @@
         <v>136738638</v>
       </c>
       <c r="B153" t="n">
-        <v>91658</v>
+        <v>91659</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>

--- a/artfynd/S 3548-2025 artfynd.xlsx
+++ b/artfynd/S 3548-2025 artfynd.xlsx
@@ -8274,7 +8274,7 @@
         <v>137007784</v>
       </c>
       <c r="B70" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>

--- a/artfynd/S 3548-2025 artfynd.xlsx
+++ b/artfynd/S 3548-2025 artfynd.xlsx
@@ -8274,7 +8274,7 @@
         <v>137007784</v>
       </c>
       <c r="B70" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>

--- a/artfynd/S 3548-2025 artfynd.xlsx
+++ b/artfynd/S 3548-2025 artfynd.xlsx
@@ -8274,7 +8274,7 @@
         <v>137007784</v>
       </c>
       <c r="B70" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>

--- a/artfynd/S 3548-2025 artfynd.xlsx
+++ b/artfynd/S 3548-2025 artfynd.xlsx
@@ -8274,7 +8274,7 @@
         <v>137007784</v>
       </c>
       <c r="B70" t="n">
-        <v>93469</v>
+        <v>93481</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>

--- a/artfynd/S 3548-2025 artfynd.xlsx
+++ b/artfynd/S 3548-2025 artfynd.xlsx
@@ -8274,7 +8274,7 @@
         <v>137007784</v>
       </c>
       <c r="B70" t="n">
-        <v>93481</v>
+        <v>93482</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>

--- a/artfynd/S 3548-2025 artfynd.xlsx
+++ b/artfynd/S 3548-2025 artfynd.xlsx
@@ -8274,7 +8274,7 @@
         <v>137007784</v>
       </c>
       <c r="B70" t="n">
-        <v>93482</v>
+        <v>93485</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>

--- a/artfynd/S 3548-2025 artfynd.xlsx
+++ b/artfynd/S 3548-2025 artfynd.xlsx
@@ -8274,7 +8274,7 @@
         <v>137007784</v>
       </c>
       <c r="B70" t="n">
-        <v>93485</v>
+        <v>93486</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>

--- a/artfynd/S 3548-2025 artfynd.xlsx
+++ b/artfynd/S 3548-2025 artfynd.xlsx
@@ -8274,7 +8274,7 @@
         <v>137007784</v>
       </c>
       <c r="B70" t="n">
-        <v>93486</v>
+        <v>93489</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
